--- a/leads/kinderlee/kinderlee_leads_europe.xlsx
+++ b/leads/kinderlee/kinderlee_leads_europe.xlsx
@@ -63,7 +63,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -71,6 +71,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -48724,5425 +48725,5921 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>decision_maker_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>decision_maker_title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>org_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>known_email</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>likely_email_patterns_UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>decision_maker_linkedin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>general_email</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>lead_score</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Dr. Kurt Berlin</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Geschäftsführer (KTS Verwaltungs GmbH / Stepke; German preschool platform)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>AcadeMedia Deutschland (brands: Joki Kinderbetreuung, Espira Kinderbetreuung, Kita Luna/KTS Verwaltungs GmbH, Stepke-KiTas)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://academedia.se</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>kurt.berlin@academedia.se; k.berlin@academedia.se; kurt@academedia.se</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>academedia.se</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Christophe Fond</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Geschäftsführer (Managing Director Germany)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Babilou Family Deutschland GmbH (brands: Denk mit! Kita, Little Giants/Kleine Riesen/Petits Géants, Wichtel Akademie, MiniMax Kids)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>christophe.fond@babilou-family.de; c.fond@babilou-family.de; christophe@babilou-family.de</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>babilou-family.de</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/babilou-family-deutschland-gmbh</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>https://babilou-family.de</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Stefan Spieker</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Geschäftsführer (CEO)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>FRÖBEL Bildung und Erziehung gGmbH</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>info@froebel-gruppe.de</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>stefan.spieker@froebel-gruppe.de; s.spieker@froebel-gruppe.de; stefan@froebel-gruppe.de</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>froebel-gruppe.de</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/froebel-bildung-und-erziehung</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>info@froebel-gruppe.de</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>+49 30 21235-0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.froebel-gruppe.de</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Dr. Jürgen Reul</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Geschäftsführer (Vorsitz) / founder</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>kitea (merger of Kinderzentren Kunterbunt gGmbH + Villa Luna Kindertagesstätten) - Klett Gruppe</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>info@kinderzentren.de</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>jurgen.reul@kitea-kids.de; j.reul@kitea-kids.de; jurgen@kitea-kids.de</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kitea-kids.de</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/kinderzentren-kunterbunt-ggmbh</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>info@kinderzentren.de</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>+49 911 470500-0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://kitea-kids.de</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Héctor Díaz Reimóndez</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Consejero Delegado (CEO) / Administrador Único</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Nemomarlin Escuelas Infantiles (Nemomarlin Franchise S.L.)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.escuelanemomarlin.com</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hector.reimondez@escuelanemomarlin.com; h.reimondez@escuelanemomarlin.com; hector@escuelanemomarlin.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>escuelanemomarlin.com</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Xavier Ouvrard</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>PDG / CEO, Babilou Family</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Babilou Family (Babilou / Evancia)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.babilou.fr</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>xavier.ouvrard@babilou.fr; x.ouvrard@babilou.fr; xavier@babilou.fr</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>babilou.fr</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Christophe Fond</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Group CEO (since July 2024)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Babilou Family (Babilou, Evancia, educcare, Kleine Riesen/Little Giants, Babilou Family Deutschland)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>christophe.fond@babilou-family.com; c.fond@babilou-family.com; christophe@babilou-family.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>babilou-family.com</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/cfond/</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://babilou-family.com/</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Jean-Emmanuel Rodocanachi</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Founder &amp; Group CEO</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Grandir Group (Les Petits Chaperons Rouges / Grandir UK / Grandir Deutschland / Liveli)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>contact@grandir.com (unverified)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>jean.rodocanachi@grandir.com; j.rodocanachi@grandir.com; jean@grandir.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>grandir.com</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/in/rodocanachi</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>contact@grandir.com (unverified)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.grandir.com/</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Sacha Tikhomiroff</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Directeur Général, Les Petits Chaperons Rouges</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Grandir – Les Petits Chaperons Rouges (LPCR)</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lpcr.fr</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sacha.tikhomiroff@lpcr.fr; s.tikhomiroff@lpcr.fr; sacha@lpcr.fr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lpcr.fr</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Antonia Ryckbosch</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Co-founder &amp; Directrice Générale / Managing Director</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>La Maison Bleue</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.la-maison-bleue.fr</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>antonia.ryckbosch@la-maison-bleue.fr; a.ryckbosch@la-maison-bleue.fr; antonia@la-maison-bleue.fr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>la-maison-bleue.fr</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Peter Gowers</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Group CEO (since 8 July 2025)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Busy Bees Nurseries (Busy Bees Group, incl. Giraffe Childcare IE, Busy Bees Italy, Canada, US, AU, NZ, SG, MY, VN)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.busybeeschildcare.co.uk/</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>peter.gowers@busybeeschildcare.co.uk; p.gowers@busybeeschildcare.co.uk; peter@busybeeschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>busybeeschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Tomas Deržanauskas</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Director (UAB director)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Vaikystės sodas (UAB Vaikystės sodas) - Globeducate</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>info@vaikystes-sodas.lt</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>+370 699 87949</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>https://vaikystes-sodas.lt</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>tomas.derzanauskas@vaikystes-sodas.lt; t.derzanauskas@vaikystes-sodas.lt; tomas@vaikystes-sodas.lt</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>vaikystes-sodas.lt</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Daina Kājiņa</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Head of CreaKids / board member</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>CreaKids (Dibber Latvia)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.creakids.lv</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>daina.kajina@creakids.lv; d.kajina@creakids.lv; daina@creakids.lv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>creakids.lv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Robin Alma</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Bestuurder</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Humankind (ex Kinderopvang Humanitas)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.humankind.nl</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>robin.alma@humankind.nl; r.alma@humankind.nl; robin@humankind.nl</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>humankind.nl</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Jeanine Lemmens</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>CEO / bestuursvoorzitter Partou (verify still in role 2026)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Partou Group (Partou NL, Partou UK, Partou Germany)</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.partou.nl/</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jeanine.lemmens@partou.nl; j.lemmens@partou.nl; jeanine@partou.nl</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>partou.nl</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Jeanine Lemmens</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Algemeen Directeur</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Smallsteps</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.smallsteps.nl</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jeanine.lemmens@smallsteps.nl; j.lemmens@smallsteps.nl; jeanine@smallsteps.nl</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>smallsteps.nl</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Hans Jacob Sundby</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>CEO &amp; co-founder, Dibber</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Dibber AS (international HQ)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>https://dibber.com</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>hans.sundby@dibber.com; h.sundby@dibber.com; hans@dibber.com</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>dibber.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Morten Vårdal</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Group CEO, Dibber</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Dibber Group / Læringsverkstedet</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dibber.com/</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>morten.vardal@dibber.com; m.vardal@dibber.com; morten@dibber.com</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>dibber.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Marit Lambrechts</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Administrerende direktør, Espira</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Espira Gruppen AS (AcadeMedia Norge)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>https://espira.no</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>marit.lambrechts@espira.no; m.lambrechts@espira.no; marit@espira.no</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>espira.no</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Eli Sævareid</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Founder &amp; CEO, Trygge Barnehager (owner of FUS)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>FUS barnehagene / Trygge Barnehager AS</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>https://fus.no</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>eli.svareid@fus.no; e.svareid@fus.no; eli@fus.no</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>fus.no</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Adam Därnemyr</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Daglig leder (CEO), Læringsverkstedet, from 10 Aug 2025 (succeeded Trude Moen Sydtangen)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Læringsverkstedet AS (Dibber Norway)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>adam.darnemyr@laringsverkstedet.no; a.darnemyr@laringsverkstedet.no; adam@laringsverkstedet.no</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>laringsverkstedet.no</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/adamdarnemyr/</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://laringsverkstedet.no</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Kristin Voldsnes</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Divisjonsdirektør (Division Director), Norlandia Barnehagene; also chair of Norlandia Förskolor AB</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Norlandia Barnehagene (Norlandia Preschools AS)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>+47 416 92 791 (Voldsnes)</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>https://norlandiabarnehagene.no</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>kristin.voldsnes@norlandiabarnehagene.no; k.voldsnes@norlandiabarnehagene.no; kristin@norlandiabarnehagene.no</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>norlandiabarnehagene.no</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Karina Trafna</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Founder &amp; CEO / Prezes Zarządu</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>KIDS&amp;Co. (Międzynarodowe Dwujęzyczne Przedszkola i Żłobki KIDS&amp;Co.)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>https://kids-co.pl</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>karina.trafna@kids-co.pl; k.trafna@kids-co.pl; karina@kids-co.pl</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>kids-co.pl</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Marcus Strömberg</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>VD och koncernchef, AcadeMedia</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>AcadeMedia AB (group)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>https://academedia.se</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>marcus.stromberg@academedia.se; m.stromberg@academedia.se; marcus@academedia.se</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>academedia.se</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Johan Kyllerman</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>VD, Atvexa AB</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Atvexa AB (publ)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.atvexa.se</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>johan.kyllerman@atvexa.se; j.kyllerman@atvexa.se; johan@atvexa.se</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>atvexa.se</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Volodymyr Kozlenko (Володимир Козленко)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Owner / founder</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>KMDS (КМДШ) / Clever Kids by KMDS</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>UA</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>https://kmds.ua</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>volodymyr.kozlenko@kmds.ua; v.kozlenko@kmds.ua; volodymyr@kmds.ua</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>kmds.ua</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Alexandra Schuster</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>CEO Deutschland (LinkedIn); registered GF: Patrick Gottesleben (2026), Benoit Lamezec (2025), Christophe Fond</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Babilou Family Deutschland GmbH (educcare, Kleine Riesen/Little Giants, littlebigFuture)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>alexandra.schuster@babilou-family.de; a.schuster@babilou-family.de; alexandra@babilou-family.de</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>babilou-family.de</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/alexandra-schuster-323641137/</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>https://babilou-family.de/</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Alfons Scheitz</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Geschäftsführer &amp; Inhaber</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Impuls Soziales Management GmbH &amp; Co. KG</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>alfons.scheitz@e-impuls.de; a.scheitz@e-impuls.de; alfons@e-impuls.de</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>e-impuls.de</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/impuls-soziales-management</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.e-impuls.de</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Till Bremen</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>KinderHut GmbH / gGmbH</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>till.bremen@kinderhut.de; t.bremen@kinderhut.de; till@kinderhut.de</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>kinderhut.de</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/kinderhut</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kinderhut.de</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Antje Bostelmann</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Gründerin &amp; Geschäftsführerin (CEO Klax Gruppe)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Klax Gruppe (Klax Berlin gGmbH)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>https://klax.de</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>antje.bostelmann@klax.de; a.bostelmann@klax.de; antje@klax.de</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>klax.de</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Thomas Frenzel</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Geschäftsführender Direktor (strategy, business development &amp; IT)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Phorms Education SE</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.phorms.de</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>thomas.frenzel@phorms.de; t.frenzel@phorms.de; thomas@phorms.de</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>phorms.de</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Dr. Kurt Berlin</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Stepke-KiTas (Step Kids KiTas gGmbH) - AcadeMedia</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.stepke-kitas.de</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>kurt.berlin@stepke-kitas.de; k.berlin@stepke-kitas.de; kurt@stepke-kitas.de</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>stepke-kitas.de</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Marcus Bracht</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>educcare Bildungskindertagesstätten gGmbH</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>https://educcare.de</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>marcus.bracht@educcare.de; m.bracht@educcare.de; marcus@educcare.de</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>educcare.de</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Annette Holtmann</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Geschäftsführerin (Villa Luna &amp; Kinderzentren Kunterbunt / kitea)</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>kitea (Villa Luna Kindertagesstätten + Kinderzentren Kunterbunt, Klett Group)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>https://kinderzentren.de/</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>annette.holtmann@kinderzentren.de; a.holtmann@kinderzentren.de; annette@kinderzentren.de</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>kinderzentren.de</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Dr. Daniel Erler</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>CEO (since 1 May 2026, succeeding Alexa Ahmad)</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>pme Familienservice Gruppe (Kita brands incl. Kids &amp; Co., Lernwelten)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familienservice.de</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>daniel.erler@familienservice.de; d.erler@familienservice.de; daniel@familienservice.de</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>familienservice.de</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Signe Suurväli</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Director (juhataja)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Kalli-kalli lasteaed</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>https://kalli.ee</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>signe.suurvali@kalli.ee; s.suurvali@kalli.ee; signe@kalli.ee</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>kalli.ee</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Frédéric Thomas</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Président fondateur</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Groupe Léa &amp; Léo</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.leaetleo.com</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>frederic.thomas@leaetleo.com; f.thomas@leaetleo.com; frederic@leaetleo.com</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>leaetleo.com</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Sylvain Forestier</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Founder &amp; President/CEO</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>La Maison Bleue (incl. Kids&amp;Co UK?, Pop e Poppa CH?, Luxembourg)</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.la-maison-bleue.fr/</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>sylvain.forestier@la-maison-bleue.fr; s.forestier@la-maison-bleue.fr; sylvain@la-maison-bleue.fr</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>la-maison-bleue.fr</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Sébastien Martin</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Co-founder &amp; Directeur Général</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Les Petites Canailles</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lespetitescanailles.fr</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>sebastien.martin@lespetitescanailles.fr; s.martin@lespetitescanailles.fr; sebastien@lespetitescanailles.fr</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>lespetitescanailles.fr</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Marc Jouannic</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Directeur Général, Liveli</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Liveli by Sodexo (ex Crèche Attitude / Crèches de France)</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.liveli.fr</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>marc.jouannic@liveli.fr; m.jouannic@liveli.fr; marc@liveli.fr</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>liveli.fr</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Audric Anselmi</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Directeur Général (since Sept 2025)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Rigolo Comme La Vie (IDKIDS group)</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rigolocommelavie.org</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>audric.anselmi@rigolocommelavie.org; a.anselmi@rigolocommelavie.org; audric@rigolocommelavie.org</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>rigolocommelavie.org</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Mark Bates</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Co-founder &amp; Managing Director</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Banana Moon Day Nurseries (franchise)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bananamoonfranchise.com</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>mark.bates@bananamoonfranchise.com; m.bates@bananamoonfranchise.com; mark@bananamoonfranchise.com</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>bananamoonfranchise.com</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Christopher McCandless</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Chief Executive Officer (appointed Sept 2025)</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Busy Bees Nurseries</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>info@busybees.com (generic, not confirmed)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)1543 711 200 (head office, not confirmed)</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.busybeeschildcare.co.uk</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>christopher.mccandless@busybeeschildcare.co.uk; c.mccandless@busybeeschildcare.co.uk; christopher@busybeeschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>busybeeschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Emma Rooney</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Childbase Partnership</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>info@childbase.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)1908 224400 (not confirmed)</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>https://childbasepartnership.com</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>emma.rooney@childbasepartnership.com; e.rooney@childbasepartnership.com; emma@childbasepartnership.com</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>childbasepartnership.com</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Tony Page</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Chief Executive Officer (joined Dec 2023)</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Family First Nurseries Group</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familyfirstnurseries.co.uk</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>tony.page@familyfirstnurseries.co.uk; t.page@familyfirstnurseries.co.uk; tony@familyfirstnurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>familyfirstnurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Steven Fenn</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Fennies Nurseries</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>info@fennies.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fennies.com</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>steven.fenn@fennies.com; s.fenn@fennies.com; steven@fennies.com</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>fennies.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Lydia Hopper</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Chief Executive Officer, Grandir UK</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Grandir UK (Kiddi Caru, Dicky Birds, Co-op Childcare heritage, Hungry Caterpillars etc.)</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>info@grandiruk.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.grandiruk.com</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>lydia.hopper@grandiruk.com; l.hopper@grandiruk.com; lydia@grandiruk.com</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>grandiruk.com</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Kim Herbert</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Happy Days Nurseries &amp; Pre-Schools</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>https://happydaysnurseries.com</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>kim.herbert@happydaysnurseries.com; k.herbert@happydaysnurseries.com; kim@happydaysnurseries.com</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>happydaysnurseries.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Clare Roberts</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>CEO &amp; Co-founder</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Kids Planet Day Nurseries</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>info@kidsplanetdaynurseries.co.uk (not confirmed)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>clare.roberts@kidsplanetdaynurseries.co.uk; c.roberts@kidsplanetdaynurseries.co.uk; clare@kidsplanetdaynurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>kidsplanetdaynurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://uk.linkedin.com/company/kids-planet-day-nurseries (company page)</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>info@kidsplanetdaynurseries.co.uk (not confirmed)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)1925 594 300 (not confirmed)</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kidsplanetdaynurseries.co.uk/</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Ruth Pimentel</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Kindred Nurseries (Kindred Education)</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kindrednurseries.co.uk</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ruth.pimentel@kindrednurseries.co.uk; r.pimentel@kindrednurseries.co.uk; ruth@kindrednurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>kindrednurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Dr June O'Sullivan OBE</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Chief Executive</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>London Early Years Foundation (LEYF)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>info@leyf.org.uk (not confirmed)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)20 7834 8679 (not confirmed)</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.leyf.org.uk</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>june.osullivan@leyf.org.uk; j.osullivan@leyf.org.uk; june@leyf.org.uk</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>leyf.org.uk</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Richard Blunden</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Monkey Puzzle Day Nurseries (franchise)</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>https://monkeypuzzledaynurseries.com</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>richard.blunden@monkeypuzzledaynurseries.com; r.blunden@monkeypuzzledaynurseries.com; richard@monkeypuzzledaynurseries.com</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>monkeypuzzledaynurseries.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Samantha Rhodes</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>UK Managing Director</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Partou UK</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>https://partou.co.uk/</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>samantha.rhodes@partou.co.uk; s.rhodes@partou.co.uk; samantha@partou.co.uk</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>partou.co.uk</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Samantha Rhodes</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Managing Director / CEO, Partou UK</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Partou UK (formerly Just Childcare + All About Children)</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>hello@partou.co.uk (not confirmed)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>https://partou.co.uk</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>samantha.rhodes@partou.co.uk; s.rhodes@partou.co.uk; samantha@partou.co.uk</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>partou.co.uk</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Sarah Mackenzie</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Storal (Storal Learning / Storal Nurseries)</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>hello@storal.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.storal.com</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>sarah.mackenzie@storal.com; s.mackenzie@storal.com; sarah@storal.com</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>storal.com</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Adelle Taylor</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>The Old Station Nursery Group (part of La Maison Bleue)</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>info@theoldstationnursery.co.uk (not confirmed)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.theoldstationnursery.co.uk</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>adelle.taylor@theoldstationnursery.co.uk; a.taylor@theoldstationnursery.co.uk; adelle@theoldstationnursery.co.uk</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>theoldstationnursery.co.uk</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Inga Dimante-Ansone</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Head / Director (vadītāja)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Zemenīte ABC (SIA Zemenīte ABC)</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>https://zemenite.lv</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>inga.ansone@zemenite.lv; i.ansone@zemenite.lv; inga@zemenite.lv</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>zemenite.lv</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Remko Berkel</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>CEO Babilou Family Nederland</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>BLOS kinderopvang (Babilou Family Nederland)</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.blos.nl</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>remko.berkel@blos.nl; r.berkel@blos.nl; remko@blos.nl</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>blos.nl</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Elly Brand</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Directeur-bestuurder</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Kibeo</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kibeo.nl</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>elly.brand@kibeo.nl; e.brand@kibeo.nl; elly@kibeo.nl</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>kibeo.nl</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Nicole Krabbenborg</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Algemeen Directeur</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Kindergarden (Bright Horizons)</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kindergarden.nl</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>nicole.krabbenborg@kindergarden.nl; n.krabbenborg@kindergarden.nl; nicole@kindergarden.nl</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>kindergarden.nl</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Yngvar Tov Herbjørnssønn</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Daglig leder (CEO), Norlandia Health &amp; Care Group AS</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Norlandia Health &amp; Care Group AS</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>yngvar.herbjrnssnn@nhcgroup.no; y.herbjrnssnn@nhcgroup.no; yngvar@nhcgroup.no</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>nhcgroup.no</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/yngvar-tov-herbj%C3%B8rnss%C3%B8nn-03833322/</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://nhcgroup.no</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Yngvar Tov Herbjørnssønn</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>CEO Norlandia / Chair Norlandia Preschools AS</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Norlandia Preschools / Norlandia Health &amp; Care Group (Kidsa Barnehager, Norlandia Förskolor, Norlandia Päiväkodit, Norlandia Przedszkola, Norlandia Kinderopvang)</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.norlandia.com/</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>yngvar.herbjrnssnn@norlandia.com; y.herbjrnssnn@norlandia.com; yngvar@norlandia.com</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>norlandia.com</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Jørn-Tommy Schjelderup</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Administrerende direktør, PBL</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>PBL - Private Barnehagers Landsforbund</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>+47 75 55 37 00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>https://pbl.no</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>jrn.schjelderup@pbl.no; j.schjelderup@pbl.no; jrn@pbl.no</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>pbl.no</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Robert Ullmann</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Daglig leder (CEO), Stiftelsen Kanvas</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Stiftelsen Kanvas</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kanvas.no</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>robert.ullmann@kanvas.no; r.ullmann@kanvas.no; robert@kanvas.no</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>kanvas.no</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Dagmara Osman</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Founder / Director (dyrektor)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Happy Kids (Przedszkola i Żłobki Happy Kids, Kraków)</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>https://przedszkole-happykids.pl</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>dagmara.osman@przedszkole-happykids.pl; d.osman@przedszkole-happykids.pl; dagmara@przedszkole-happykids.pl</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>przedszkole-happykids.pl</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Justyna Pacuła</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Owner (właścicielka)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Pod Magnolią – Niepubliczne Przedszkola Językowe</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>https://podmagnolia.pl</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>justyna.pacua@podmagnolia.pl; j.pacua@podmagnolia.pl; justyna@podmagnolia.pl</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>podmagnolia.pl</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Małgorzata (Małgosia) Tarnowska</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>Owner &amp; Founder; AMI Montessori Guide</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Warsaw Montessori Family (Casa dei Bambini Warsaw Montessori School)</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>https://wmf.edu.pl</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>magorzata.tarnowska@wmf.edu.pl; m.tarnowska@wmf.edu.pl; magorzata@wmf.edu.pl</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>wmf.edu.pl</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Tatjana Rackov Sinadinović</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>Founder and Director</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Happy Kids (Privatna predškolska ustanova Happy Kids)</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>https://happykidsvrtic.rs</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>tatjana.sinadinovic@happykidsvrtic.rs; t.sinadinovic@happykidsvrtic.rs; tatjana@happykidsvrtic.rs</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>happykidsvrtic.rs</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Marcus Strömberg</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>President &amp; CEO AcadeMedia</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>AcadeMedia AB (Pysslingen Förskolor, Espira, Joki, Stepke, Kita Luna, Noblaschool, Montessori Mondial)</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>https://academedia.se/</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>marcus.stromberg@academedia.se; m.stromberg@academedia.se; marcus@academedia.se</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>academedia.se</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Johannes Stiigh</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>VD (extern), Dibber Sverige AB (per 2025 bokslut); earlier source names Mari Puoskari</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Dibber Sverige AB</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>https://dibber.se</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>johannes.stiigh@dibber.se; j.stiigh@dibber.se; johannes@dibber.se</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>dibber.se</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Bijan Fahimi</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>VD, Tellusgruppen (parent of Tellusbarn)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Tellusbarn / Tellusgruppen AB</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>https://tellusbarn.se</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>bijan.fahimi@tellusbarn.se; b.fahimi@tellusbarn.se; bijan@tellusbarn.se</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>tellusbarn.se</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Melita Kordeš Demšar</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Direktorica (mag.)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Inštitut montessori (Zavod za pomoč staršem pri razvoju otrok)</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Stephen Kramer</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>CEO (Bright Horizons Family Solutions)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Bright Horizons Family Solutions (UK: Bright Horizons UK; NL: Kindergarden)</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.brighthorizons.com/</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>stephen.kramer@brighthorizons.com; s.kramer@brighthorizons.com; stephen@brighthorizons.com</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>brighthorizons.com</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Dr. Sonja Christina Bürger</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>Geschäftsführerin</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Infanterix Multilinguale Krippen &amp; Kindergärten (Infanterix GmbH / Infanterix Bayern GmbH)</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>sonja.burger@infanterix.de; s.burger@infanterix.de; sonja@infanterix.de</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>infanterix.de</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>https://de.linkedin.com/company/infanterix-multilinguale-krippen-&amp;-kinderg%C3%A4rten</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>https://www.infanterix.de</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Eva Harmat</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Geschäftsführerin</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Kinderland PLUS gGmbH</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kinderland-plus.de</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>eva.harmat@kinderland-plus.de; e.harmat@kinderland-plus.de; eva@kinderland-plus.de</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>kinderland-plus.de</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Dr. Kurt Berlin</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Kita Luna (KTS Verwaltungs GmbH) - AcadeMedia</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kita-luna.de</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>kurt.berlin@kita-luna.de; k.berlin@kita-luna.de; kurt@kita-luna.de</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>kita-luna.de</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Patrick Gottesleben</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Little Giants / Kleine Riesen / Petits Géants (Giant Leap GmbH &amp; Co. KG, Babilou brand)</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.littlegiants.de</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>patrick.gottesleben@littlegiants.de; p.gottesleben@littlegiants.de; patrick@littlegiants.de</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>littlegiants.de</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Christophe Fond</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Geschäftsführer</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Wichtel Akademie München GmbH (Babilou brand)</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wichtel-muenchen.com</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>christophe.fond@wichtel-muenchen.com; c.fond@wichtel-muenchen.com; christophe@wichtel-muenchen.com</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>wichtel-muenchen.com</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Dr. Daniel Erler</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Geschäftsführer (since 1 May 2026, succeeding Alexa Ahmad)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>pme Familienservice Gruppe</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familienservice.de/</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>daniel.erler@familienservice.de; d.erler@familienservice.de; daniel@familienservice.de</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>familienservice.de</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Ana Rojo Guisasola</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Kids&amp;Us (Kids &amp; Us English S.L.)</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ana.guisasola@kidsandus.es; a.guisasola@kidsandus.es; ana@kidsandus.es</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>kidsandus.es</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/ana-rojo-guisasola-2b242316/</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kidsandus.es</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Alain Rauscher</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Co-founder, Chairman &amp; CEO (prior knowledge - verify)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Antin Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.antin-ip.com/</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>alain.rauscher@antin-ip.com; a.rauscher@antin-ip.com; alain@antin-ip.com</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>antin-ip.com</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Claudia Kespy-Yahi</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>Fondatrice &amp; Présidente</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Cap Enfants</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>claudia.yahi@capenfants.com; c.yahi@capenfants.com; claudia@capenfants.com</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>capenfants.com</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/claudiakespyyahi/</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.capenfants.com</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Céline Legrain</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>Directrice Générale</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Crescendo (Groupe SOS)</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>crescendo@groupe-sos.org</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>+33 1 58 82 29 81</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crescendo.asso.fr</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>celine.legrain@crescendo.asso.fr; c.legrain@crescendo.asso.fr; celine@crescendo.asso.fr</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>crescendo.asso.fr</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Vincent Levita</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Founder &amp; CEO (prior knowledge - verify)</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>InfraVia Capital Partners</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://infraviacapital.com/</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>vincent.levita@infraviacapital.com; v.levita@infraviacapital.com; vincent@infraviacapital.com</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>infraviacapital.com</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Philippe Tapié</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>CEO (post-2024 restructuring management)</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>People&amp;Baby</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.people-and-baby.com</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>philippe.tapie@people-and-baby.com; p.tapie@people-and-baby.com; philippe@people-and-baby.com</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>people-and-baby.com</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Philip Smith</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>Managing Director, UK</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Bright Horizons Family Solutions UK</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>info@brighthorizons.co.uk (not confirmed)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)333 240 1090 (not confirmed)</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.brighthorizons.co.uk</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>philip.smith@brighthorizons.co.uk; p.smith@brighthorizons.co.uk; philip@brighthorizons.co.uk</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>brighthorizons.co.uk</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Laura Wardley-Smith</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>CEO (verify; Ruth Pimentel resigned 3 Sept 2025)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Kindred Education / Kindred Nurseries</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kindrednurseries.co.uk/</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>laura.smith@kindrednurseries.co.uk; l.smith@kindrednurseries.co.uk; laura@kindrednurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>kindrednurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Hayley Peacock</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Founder &amp; CEO (prior knowledge)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Little Barn Owls Nursery &amp; Farm School</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.littlebarnowls.co.uk</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>hayley.peacock@littlebarnowls.co.uk; h.peacock@littlebarnowls.co.uk; hayley@littlebarnowls.co.uk</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>littlebarnowls.co.uk</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" t="inlineStr">
         <is>
           <t>None confirmed</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Little Dukes (Dukes Education)</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dukeseducation.com/nurseries</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>none.confirmed@dukeseducation.com; n.confirmed@dukeseducation.com; none@dukeseducation.com</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>dukeseducation.com</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Leanna Barrett</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Co-founder &amp; CEO (prior knowledge)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Little Forest Folk</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.littleforestfolk.com</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>leanna.barrett@littleforestfolk.com; l.barrett@littleforestfolk.com; leanna@littleforestfolk.com</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>littleforestfolk.com</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Phil Sunderland</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Founder &amp; Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>N Family Club</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>hello@nfamilyclub.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>https://nfamilyclub.com</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>phil.sunderland@nfamilyclub.com; p.sunderland@nfamilyclub.com; phil@nfamilyclub.com</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>nfamilyclub.com</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Sarah Mackenzie</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>CEO (since 2022)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Storal (Storal Learning Ltd)</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.storal.com/</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>sarah.mackenzie@storal.com; s.mackenzie@storal.com; sarah@storal.com</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>storal.com</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Cary Rankin</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Chief Executive Officer (NOTE: Companies House shows his directorship terminated 29 Sept 2025 - successor not confirmed)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Thrive Childcare and Education (formerly Bertram Nursery Group)</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>info@thrivechildcare.com (not confirmed)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thrivechildcare.com</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>cary.rankin@thrivechildcare.com; c.rankin@thrivechildcare.com; cary@thrivechildcare.com</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>thrivechildcare.com</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Caroline Fooks</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Founder &amp; Chief Executive Officer</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Tommies Childcare</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tommieschildcare.co.uk</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>caroline.fooks@tommieschildcare.co.uk; c.fooks@tommieschildcare.co.uk; caroline@tommieschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>tommieschildcare.co.uk</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Cheryl Hadland MBE</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Founder / Chair (role post-EOT to verify)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Tops Day Nurseries (Hadland Care Group)</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>info@topsdaynurseries.co.uk (not confirmed)</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>+44 (0)1202 551553 (not confirmed)</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.topsdaynurseries.co.uk</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>cheryl.hadland@topsdaynurseries.co.uk; c.hadland@topsdaynurseries.co.uk; cheryl@topsdaynurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>topsdaynurseries.co.uk</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Amanda Sunderman</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>School Principal / Director</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>American International School of Vilnius (AISV)</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.aisv.lt</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>amanda.sunderman@aisv.lt; a.sunderman@aisv.lt; amanda@aisv.lt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>aisv.lt</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Rebecca Juras</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Vilnius International School (VIS)</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vischool.lt</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>rebecca.juras@vischool.lt; r.juras@vischool.lt; rebecca@vischool.lt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>vischool.lt</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Elizabeth Younk</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Elementary School Principal (oversees Early Years, from Aug 2025)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>International School of Latvia (ISL)</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://isl.edu.lv</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>elizabeth.younk@isl.edu.lv; e.younk@isl.edu.lv; elizabeth@isl.edu.lv</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>isl.edu.lv</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Monique Wittebol</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Voorzitter Raad van Bestuur</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Bink kinderopvang</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.binkkinderopvang.nl</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>monique.wittebol@binkkinderopvang.nl; m.wittebol@binkkinderopvang.nl; monique@binkkinderopvang.nl</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>binkkinderopvang.nl</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Jan Paul ten Brink</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Voorzitter Raad van Bestuur a.i. (2025)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>KION</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://kion.nl</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>jan.brink@kion.nl; j.brink@kion.nl; jan@kion.nl</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>kion.nl</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Nicole Krabbenborg</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Managing Director, Kindergarden Netherlands</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Kindergarden Nederland (Bright Horizons)</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kindergarden.nl/</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>nicole.krabbenborg@kindergarden.nl; n.krabbenborg@kindergarden.nl; nicole@kindergarden.nl</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>kindergarden.nl</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" t="inlineStr">
         <is>
           <t>Elise Rønholt</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>Daglig leder, Barnehagenett AS</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Barnehagenett AS</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>https://barnehagenett.no</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>elise.rnholt@barnehagenett.no; e.rnholt@barnehagenett.no; elise@barnehagenett.no</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>barnehagenett.no</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Katarzyna Tyza</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Owner &amp; Director</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Akademia Malucha (Biała Podlaska / Lubelskie network)</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr"/>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>https://terebelska.akademiamaluchabp.pl</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>katarzyna.tyza@terebelska.akademiamaluchabp.pl; k.tyza@terebelska.akademiamaluchabp.pl; katarzyna@terebelska.akademiamaluchabp.pl</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>terebelska.akademiamaluchabp.pl</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" t="inlineStr">
         <is>
           <t>Sabina Madej</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Owner &amp; Director (dyrektor)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Akademia Małych Einsteinów (Kraków)</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>https://akademiamalycheinsteinow.pl</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>sabina.madej@akademiamalycheinsteinow.pl; s.madej@akademiamalycheinsteinow.pl; sabina@akademiamalycheinsteinow.pl</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>akademiamalycheinsteinow.pl</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" t="inlineStr">
         <is>
           <t>Dr. Michelle Kleiss</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>School Director (Pre-K lead not confirmed)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>American School of Warsaw (Early Childhood / Pre-K)</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.aswarsaw.org</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>michelle.kleiss@aswarsaw.org; m.kleiss@aswarsaw.org; michelle@aswarsaw.org</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>aswarsaw.org</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" t="inlineStr">
         <is>
           <t>Mateusz Samborek</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Prezes Zarządu (President of the Board)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Baby Booom – Żłobki i Przedszkola</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>https://baby-booom.pl</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>mateusz.samborek@baby-booom.pl; m.samborek@baby-booom.pl; mateusz@baby-booom.pl</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>baby-booom.pl</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Katarzyna Kosakowska</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Founder / Director</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Baby City – międzynarodowe przedszkole i żłobek</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>https://baby-city.pl</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>katarzyna.kosakowska@baby-city.pl; k.kosakowska@baby-city.pl; katarzyna@baby-city.pl</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>baby-city.pl</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Anna Marek</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Director (dyrektor); Dominika Marek = owner/organ prowadzący</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Bright Child – Polsko-Angielskie Przedszkole (Kraków)</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>https://brightchild.pl</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>anna.marek@brightchild.pl; a.marek@brightchild.pl; anna@brightchild.pl</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>brightchild.pl</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>John Brett</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Principal (Early Years head not confirmed)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>The British School Warsaw (Nord Anglia) – Early Years Centre</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nordangliaeducation.com/tbsw-warsaw</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>john.brett@nordangliaeducation.com; j.brett@nordangliaeducation.com; john@nordangliaeducation.com</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>nordangliaeducation.com</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" t="inlineStr">
         <is>
           <t>Karol Michalski</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Founder &amp; Owner</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Tygrysek i Przyjaciele (żłobki i przedszkola)</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>https://tygrysekiprzyjaciele.pl</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>karol.michalski@tygrysekiprzyjaciele.pl; k.michalski@tygrysekiprzyjaciele.pl; karol@tygrysekiprzyjaciele.pl</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>tygrysekiprzyjaciele.pl</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" t="inlineStr">
         <is>
           <t>Diana Ciszewska</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Founder (Zielona Wieża Lublin) – network co-founder; verify for HQ</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Zielona Wieża (przedszkola i żłobki bliskościowe)</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>https://zielonawieza.pl</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>diana.ciszewska@zielonawieza.pl; d.ciszewska@zielonawieza.pl; diana@zielonawieza.pl</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>zielonawieza.pl</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Johan Kyllerman</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>VD / CEO</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Atvexa AB</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.atvexa.se/</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>johan.kyllerman@atvexa.se; j.kyllerman@atvexa.se; johan@atvexa.se</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>atvexa.se</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>Per Egon Johansson</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>VD, Raoul Wallenbergskolorna AB</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Raoul Wallenbergskolorna AB</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>https://raoulwallenbergskolan.se</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>per.johansson@raoulwallenbergskolan.se; p.johansson@raoulwallenbergskolan.se; per@raoulwallenbergskolan.se</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>raoulwallenbergskolan.se</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" t="inlineStr">
         <is>
           <t>Lea Sievers</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>Einrichtungsleitung</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Kids &amp; Co. Krippe (pme Familienservice), Frankfurt Westend</t>
         </is>
       </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familienservice.de/web/kids-co-krippe</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>lea.sievers@familienservice.de; l.sievers@familienservice.de; lea@familienservice.de</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>familienservice.de</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" t="inlineStr">
         <is>
           <t>Christof Blach</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Einrichtungsleitung</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Kids &amp; Co. Unterlindau (pme Familienservice), Frankfurt</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familienservice.de/web/kids-co-unterlindau</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>christof.blach@familienservice.de; c.blach@familienservice.de; christof@familienservice.de</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>familienservice.de</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Maren Jung</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>Geschäftsführerin</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>Kinderland im Kreis Saarlouis gGmbH</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kreis-saarlouis.de/Kita-Kinderland.htm</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>maren.jung@kreis-saarlouis.de; m.jung@kreis-saarlouis.de; maren@kreis-saarlouis.de</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>kreis-saarlouis.de</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Annette Heintz</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Kita-Leitung</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>nestwärme-Kita (nestwärme e.V. Deutschland), Trier</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nestwaerme.org/kita/</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>annette.heintz@nestwaerme.org; a.heintz@nestwaerme.org; annette@nestwaerme.org</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>nestwaerme.org</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Irene Espinosa</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Directora</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Escuela Infantil La Pecera (Ceuta) - managed by Koala/Clece</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr"/>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Elena Fernández</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Directora</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>Escuela Infantil Los Olivos (Alcalá de Guadaíra, Sevilla) - managed by Koala/Clece</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Óscar Fraga</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Franchise contact / founder (title not confirmed)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Trastes Centros de Educación Infantil (Trastes Desarrollo de Franquicias S.L.)</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>https://escuelainfantiltrastes.es</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>oscar.fraga@escuelainfantiltrastes.es; o.fraga@escuelainfantiltrastes.es; oscar@escuelainfantiltrastes.es</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>escuelainfantiltrastes.es</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" t="inlineStr">
         <is>
           <t>None confirmed</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
         <is>
           <t>Kido (Kido Education / Kido International)</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kido.school</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>none.confirmed@kido.school; n.confirmed@kido.school; none@kido.school</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>kido.school</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Claire Warden</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Founder (prior knowledge)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Nature Kindergarten (Auchlone) / Mindstretchers</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mindstretchers.co.uk</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>claire.warden@mindstretchers.co.uk; c.warden@mindstretchers.co.uk; claire@mindstretchers.co.uk</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>mindstretchers.co.uk</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Zrinka Junaković</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>Founder (osnivačica)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>Dječji vrtić FrFi</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vrtic-frfi.hr</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>zrinka.junakovic@vrtic-frfi.hr; z.junakovic@vrtic-frfi.hr; zrinka@vrtic-frfi.hr</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>vrtic-frfi.hr</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Ivana Prčić</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>Ravnateljica</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>Dječji vrtić Izvor</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vrtic-izvor-samobor.hr</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ivana.prcic@vrtic-izvor-samobor.hr; i.prcic@vrtic-izvor-samobor.hr; ivana@vrtic-izvor-samobor.hr</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>vrtic-izvor-samobor.hr</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Irena Burić</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Dječji vrtić Nemo</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vrtic-nemo.hr</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>irena.buric@vrtic-nemo.hr; i.buric@vrtic-nemo.hr; irena@vrtic-nemo.hr</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>vrtic-nemo.hr</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Sarma Dreimane</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Imanta branch manager (contact)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Burtu pasaulīte</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>sarma.dreimane@inbox.lv</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>+371 26882955</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>https://www.burtupasaulite.lv</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>sarma.dreimane@burtupasaulite.lv; s.dreimane@burtupasaulite.lv; sarma@burtupasaulite.lv</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>burtupasaulite.lv</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Solveiga Tiliba</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Kindergarten director</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Rotaļdārzs</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rotaldarzs.lv</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>solveiga.tiliba@rotaldarzs.lv; s.tiliba@rotaldarzs.lv; solveiga@rotaldarzs.lv</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>rotaldarzs.lv</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Edle Damm</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Akasia Sædalen barnehage</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr"/>
-      <c r="F129" s="2" t="inlineStr"/>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>https://www.proff.no/selskap/akasia-s%C3%A6dalen-barnehage/bergen/pleie-og-omsorgstjenester/IGBAFW610K7/</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>edle.damm@proff.no; e.damm@proff.no; edle@proff.no</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>proff.no</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Therese Young</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Daglig leder (since Sept 2022)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Bærumsmarka FUS barnehage AS</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
-      <c r="F130" s="2" t="inlineStr"/>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>https://fus.no/baerumsmarka</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>therese.young@fus.no; t.young@fus.no; therese@fus.no</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>fus.no</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Kristina Andreassen</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Fjordbyen barnehage (ULNA)</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
-      <c r="F131" s="2" t="inlineStr"/>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>https://fjordbyen.barnehage.no</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>kristina.andreassen@fjordbyen.barnehage.no; k.andreassen@fjordbyen.barnehage.no; kristina@fjordbyen.barnehage.no</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>fjordbyen.barnehage.no</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Gunn-Marte Hasund</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Gnist Barnehager Støylane (Norlandia)</t>
         </is>
       </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>https://www.1881.no/barnehage-og-barnepark/barnehage-og-barnepark-moere-og-romsdal/barnehage-og-barnepark-ulsteinvik/gnist-barnehager-stoeylane_101092802S1/</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>gunn.hasund@1881.no; g.hasund@1881.no; gunn@1881.no</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>1881.no</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" t="inlineStr">
         <is>
           <t>Anne Kristin Aaseth</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Daglig leder (since 2002)</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Prestagardskogen FUS barnehage</t>
         </is>
       </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>https://fus.no/prestagardskogen</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>anne.aaseth@fus.no; a.aaseth@fus.no; anne@fus.no</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>fus.no</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" t="inlineStr">
         <is>
           <t>Vera Søpstad</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Daglig leder, Trollskogen Barnehage (Alversund, hovedkontor)</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Trollskogen Barnehage (SA / chain)</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>+47 995 19 798</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>https://trollskogen.barnehage.no</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>vera.spstad@trollskogen.barnehage.no; v.spstad@trollskogen.barnehage.no; vera@trollskogen.barnehage.no</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>trollskogen.barnehage.no</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Lene Reed</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Trollskogen barnehage Måløy</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>+47 419 33 331</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>https://trollskogenmaaloy.barnehage.no</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>lene.reed@trollskogenmaaloy.barnehage.no; l.reed@trollskogenmaaloy.barnehage.no; lene@trollskogenmaaloy.barnehage.no</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>trollskogenmaaloy.barnehage.no</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Ann-Kristin Sandvik</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Trollskogen barnehage Oslo (Bjørndal)</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>+47 414 53 496</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>https://trollskogenoslo.barnehage.no</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ann.sandvik@trollskogenoslo.barnehage.no; a.sandvik@trollskogenoslo.barnehage.no; ann@trollskogenoslo.barnehage.no</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>trollskogenoslo.barnehage.no</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Lise Bjørkli Hilsen</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Trollskogen barnehage Raufoss</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>https://trollskogenraufoss.barnehage.no</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>lise.hilsen@trollskogenraufoss.barnehage.no; l.hilsen@trollskogenraufoss.barnehage.no; lise@trollskogenraufoss.barnehage.no</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>trollskogenraufoss.barnehage.no</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Christine Gleditsch</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>ULNA Vang aktivitetsbarnehage</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hamar.kommune.no/barnehagene/private-barnehager/ulna-vang-aktivitetsbarnehage/</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>christine.gleditsch@hamar.kommune.no; c.gleditsch@hamar.kommune.no; christine@hamar.kommune.no</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>hamar.kommune.no</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Katarzyna Lis</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>MOC Montessori (żłobek i przedszkole, Warszawa Białołęka)</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>https://mocmontessori.pl</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>katarzyna.lis@mocmontessori.pl; k.lis@mocmontessori.pl; katarzyna@mocmontessori.pl</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>mocmontessori.pl</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Karolina Czarnecka</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Head / Owner</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Montessori Stepping Stones (Warszawa)</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>https://www.montessoristeppingstones.pl</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>karolina.czarnecka@montessoristeppingstones.pl; k.czarnecka@montessoristeppingstones.pl; karolina@montessoristeppingstones.pl</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>montessoristeppingstones.pl</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Olga Gudynn</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Founder (title/current role not confirmed)</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Olga Gudynn International School (kindergarten + school)</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>https://www.olgagudynn.ro</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>olga.gudynn@olgagudynn.ro; o.gudynn@olgagudynn.ro; olga@olgagudynn.ro</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>olgagudynn.ro</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Mari Hannele Puoskari / Johannes Stiigh (conflicting sources)</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>VD</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Dibber Helianthus Förskola AB</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>https://dibber.se</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>mari.stiigh@dibber.se; m.stiigh@dibber.se; mari@dibber.se</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>dibber.se</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Danijel Janjevak</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Montessori - zavod zasebni vrtec Cinca Binca</t>
         </is>
       </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Nives Jurman</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Direktorica</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Zasebni vrtec Metulj</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Hamit Akçay</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Founder (Dr.)</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Kaşif Çocuk Akademisi</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Yusuf Tavukçuoğlu</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Kurucu Temsilcisi (founder representative)</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Özel Atacan Eğitim Kurumları</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr"/>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Idayra Beltrán</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Directora pedagógica</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Escuela Infantil Sanipeques - managed by Koala/Clece</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr"/>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Marta Illa</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Directora del centro</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Kids&amp;Us Manresa (flagship centre)</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kidsandus.es/en/academias-ingles/manresa</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>marta.illa@kidsandus.es; m.illa@kidsandus.es; marta@kidsandus.es</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>kidsandus.es</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr"/>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Cowgate Under 5's Centre</t>
         </is>
       </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>not.applicable@not confirmed; n.applicable@not confirmed; not@not confirmed</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>not confirmed</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" t="inlineStr">
         <is>
           <t>Cathrine (surname not shown in snippet)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Daglig leder</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Idun FUS barnehage (Sagene, Oslo)</t>
         </is>
       </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>https://fus.no/idun</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>fus.no</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
         <is>
           <t>1</t>
         </is>

--- a/leads/kinderlee/kinderlee_leads_europe.xlsx
+++ b/leads/kinderlee/kinderlee_leads_europe.xlsx
@@ -647,7 +647,7 @@
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>info@globegarden.org; familienservice@globegarden.org; humanresources@globegarden.org; career@globegarden.org; presse@globegarden.org</t>
+          <t>info@globegarden.org; familienservice@globegarden.org; humanresources@globegarden.org; career@globegarden.org; presse@globegarden.org; firmenservice@globegarden.org</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -685,11 +685,19 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>sabine.ambord@globegarden.org (Sabine Ambord, External prevention contact); karin.nagy@globegarden.org (Karin Nagy, Payroll administration)</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>first.last@globegarden.org</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>https://www.globegarden.ch/kontakt/anrufen; https://www.globegarden.ch/presse/media-kontakt; https://search.ch/tel/zuerich/spluegenstrasse-14/globegarden-gmbh</t>
+          <t>https://www.globegarden.ch/footer-copyright/impressum; https://www.globegarden.ch/fileadmin/user_upload/globegarden-geschaeftsleitung-de.pdf</t>
         </is>
       </c>
     </row>
@@ -897,7 +905,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/cfond/; https://babilou-family.com/leadership-community; https://babilou-family.com/en/legal-notices</t>
+          <t>https://babilou-family.com/leadership-community; https://www.linkedin.com/in/cfond/; https://babilou-family.com/en/legal-notices</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1437,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>https://www.babilou.fr/espace-presse/contact.html; https://www.babilou.fr/aide-contact/gestionnaire-de-creches; https://rocketreach.co/xavier-ouvrard-email_7552895</t>
+          <t>https://www.babilou.fr/espace-presse/xavier-ouvrard-nomme-president-directeur-general-de-babilou-family; https://www.babilou.fr/sites/default/files/2021-01/Nomination%20Xavier%20Ouvrard.pdf; https://www.babilou.fr/aide-contact</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2361,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>https://partou.nl/en/executive-board/; https://www.linkedin.com/in/marcello-iacono/; https://partougroup.com/; https://rocketreach.co/marcello-iacono-email_70168821</t>
+          <t>https://partou.nl/en/executive-board/; https://rocketreach.co/marcello-iacono-email_70168821</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2561,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>https://rocketreach.co/jeanine-lemmens-westerink-email_6622332</t>
+          <t>https://rocketreach.co/jeanine-lemmens-westerink-email_6622332; https://nl.linkedin.com/company/smallsteps-b-v-</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2629,11 @@
           <t>Randi Sundby - co-founder</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>contact@dibberfamily.com</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
@@ -2653,7 +2665,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>https://www.dibber.com/contact; https://contactout.com/company/Dibber-46479/headquarters</t>
+          <t>https://www.dibber.com/contact; https://www.dibber.com/about-us</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2981,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>https://fus.no/om-oss; https://www.dnb.com/business-directory/company-profiles/fus-as.cd323a333605bd34d459cef92cd6f4b0; https://www.utdanningsnytt.no/barnehagemilliardene-barnehagepolitikk-fus/barnehagefamilie-har-tatt-utbytter-pa-naer-400-millioner/426826</t>
+          <t>https://www.utdanningsforbundet.no/lonn-og-arbeidsvilkar/tariffavtaler/fus-trygge-barnehager/hva-skjer-i-fus; https://velferdsstaten.no/2025/08/29/norges-storste-velferdsprofitorer-3-fus-trygge-barnehager-sfr-holding-as/</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3053,11 @@
           <t>Hans Jacob Sundby - CEO Dibber (owner); Christine Tømte - Læringsverkstedet (LinkedIn found, role not confirmed)</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>kontor@laringsverkstedet.no</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
@@ -3073,7 +3089,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>https://www.barnehage.no/laeringsverkstedet/blir-daglig-leder-i-laeringsverkstedet/274218; https://laringsverkstedet.no/en/contact</t>
+          <t>https://laringsverkstedet.no/en/contact</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3265,11 @@
           <t>Company LinkedIn: https://pl.linkedin.com/company/przedszkolakidsco</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>biuro@kids-co.pl; marketing.kids@kids-co.pl</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr">
         <is>
@@ -3281,7 +3301,7 @@
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>https://kids-co.pl/en/contact/; https://equitin.pl/pl/aktualnosci-i-kontakt</t>
+          <t>https://kids-co.pl/en/contact/; https://www.ourkids.net/pl/przedszkole-kidsco-warszawa/519; https://pl.linkedin.com/company/przedszkolakidsco</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5669,7 @@
       <c r="Y51" s="2" t="inlineStr"/>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>https://kidsgarden.edu.es/contacto-institucional/; https://kidsgarden.edu.es/alicante/contacto/; https://kidsgarden.edu.es/santander/contacto/</t>
+          <t>https://kidsgarden.edu.es/contacto-institucional/; https://www.fomento.edu/en/the-schools/kids-garden/</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6129,7 @@
       <c r="Y56" s="2" t="inlineStr"/>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>https://www.la-maison-bleue.fr/contact-assistance; https://getprospect.com/business-directory/la-maison-bleue-fr; https://theorg.com/org/la-maison-bleue-sas/org-chart/sylvain-forestier</t>
+          <t>https://theorg.com/org/la-maison-bleue-sas/org-chart/sylvain-forestier; https://getprospect.com/business-directory/la-maison-bleue-fr</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6521,7 @@
       <c r="Y60" s="2" t="inlineStr"/>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>https://www.rigolocommelavie.org/wp-content/uploads/2025/09/Communique-de-presse-nomination-Audric-Anselmi.pdf; https://www.rigolocommelavie.org/2025/09/16/rigolo-comme-la-vie-renforce-son-equipe-de-direction-et-confirme-ses-ambitions-de-croissance-avec-larrivee-daudric-anselmi-en-tant-que-nouveau-directeur-general/; https://www.rigolocommelavie.org/espace-presse/</t>
+          <t>https://www.rigolocommelavie.org/wp-content/uploads/2025/09/Communique-de-presse-nomination-Audric-Anselmi.pdf; https://www.rigolocommelavie.org/espace-presse/</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6617,7 @@
       <c r="Y61" s="2" t="inlineStr"/>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>https://www.bananamoonfranchise.com/banana-moon-our-culture/meet-the-team/mark-bates/; https://www.linkedin.com/in/mark-bates-66845647/</t>
+          <t>https://www.bananamoonfranchise.com/banana-moon-our-culture/meet-the-team/mark-bates/; https://www.crunchbase.com/organization/banana-moon-day-nursery-limited</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6929,7 @@
       <c r="Y64" s="2" t="inlineStr"/>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>https://familyfirstnurseries.co.uk/contact-us; https://www.linkedin.com/in/tony-page-30a49910/</t>
+          <t>https://familyfirstnurseries.co.uk/contact-us; https://familyfirstnurseries.co.uk/leadership; https://www.linkedin.com/in/tony-page-30a49910/</t>
         </is>
       </c>
     </row>
@@ -7201,7 +7221,7 @@
       <c r="Y67" s="2" t="inlineStr"/>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>https://www.grandiruk.com/contact-us/; https://find-and-update.company-information.service.gov.uk/company/10519700/officers; https://rocketreach.co/matthew-moore-email_5633065</t>
+          <t>https://www.grandiruk.com/contact-us/; https://rocketreach.co/grandir-uk-email-format_b79f5d22c5e53f09; https://www.linkedin.com/in/aalayza/</t>
         </is>
       </c>
     </row>
@@ -7293,11 +7313,19 @@
           <t>uk_ie.json</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr"/>
-      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>kim.herbert@happydaysnurseries.com (Kim Herbert, Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>first.last@domain</t>
+        </is>
+      </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>https://happydaysnurseries.com/about-us/meet-the-team/; https://www.linkedin.com/in/kim-herbert-6635305a/; https://www.nurseryworld.co.uk/content/features/nursery-chains-directory-people-and-places-h-to-z-1</t>
+          <t>https://happydaysnurseries.com/news/new-acquisitions/; https://happydaysnurseries.com/about-us/meet-the-team/; https://www.linkedin.com/in/kim-herbert-6635305a/</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9129,11 @@
       </c>
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="inlineStr"/>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>info@compananny.nl</t>
+        </is>
+      </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>020 - 417 01 17</t>
@@ -9137,7 +9169,7 @@
       <c r="Y87" s="2" t="inlineStr"/>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>https://www.compananny.com/en/contact/; https://leadiq.com/c/compananny-nederland-bv/5a1d98632300005a0087124b; https://privateequityinfo.com/directory/private-equity-portfolio-company/1/compananny</t>
+          <t>https://www.compananny.com/en/contact/; https://leadiq.com/c/compananny-nederland-bv/5a1d98632300005a0087124b</t>
         </is>
       </c>
     </row>
@@ -9289,8 +9321,16 @@
       </c>
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr"/>
-      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>info@kindencoludens.nl</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>030 695 84 69</t>
+        </is>
+      </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
           <t>Kind &amp; Co Ludens is the merged organisation of KMN Kind &amp; Co and Ludens, ranked among the top five Dutch childcare organisations by number of places in the December 2025 Top 100. It operates KDV, peuteropvang and BSO across Utrecht and the central Netherlands as a non-profit. Leadership not confirmed in this session.</t>
@@ -9321,7 +9361,7 @@
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>https://kindencoludens.nl/nl/contact; https://nl.linkedin.com/company/kind-co-ludens</t>
+          <t>https://kindencoludens.nl/nl/contact; https://kindencoludens.nl/nl/onze-organisatie</t>
         </is>
       </c>
     </row>
@@ -9381,8 +9421,16 @@
       </c>
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr"/>
-      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>contact@kindergarden.nl</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>020 423 54 22</t>
+        </is>
+      </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
           <t>Kindergarden has been part of Bright Horizons since 2011 and operates 72+ KDV/BSO locations, recently taking over three sites in Hoofddorp, Lisserbroek and Nieuw-Vennep. It launched WorkFamily Solutions (employer benefits) in NL and partners with international childcare providers. Certified Great Place to Work for Women 2025. Hook: US-listed parent with global vendor standards; local director confirmed.</t>
@@ -9409,7 +9457,7 @@
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>https://www.kindergarden.nl/over-ons/managementteam; https://www.kinderopvangtotaal.nl/spreker/nicole-krabbenborg/</t>
+          <t>https://www.kindergarden.nl/contact; https://www.kindergarden.nl/over-ons/managementteam</t>
         </is>
       </c>
     </row>
@@ -9553,8 +9601,16 @@
       </c>
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr"/>
-      <c r="P92" s="2" t="inlineStr"/>
-      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>info@wijzijnjong.nl; stage@wijzijnjong.nl</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>(040) 294 89 40</t>
+        </is>
+      </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
           <t>Wij zijn JONG is a top-5 Dutch childcare organisation with roughly 200-240 locations and 3,000+ professionals, active in Utrecht province and beyond. It operates as a stichting focused on child development ('werken aan de toekomst van kinderen'). It appears in the Kinderopvang-Wijzer Top 100 (December 2025) among the largest groups. Leadership not confirmed in this session.</t>
@@ -9585,7 +9641,7 @@
       <c r="Y92" s="2" t="inlineStr"/>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>https://www.wijzijnjong.nl/pers/jaco-donselaar-nieuwe-bestuurder-wij-zijn-jong; https://www.wijzijnjong.nl/update/archief/nieuwe-bestuurder</t>
+          <t>https://www.wijzijnjong.nl/contact; https://www.wijzijnjong.nl/pers/jaco-donselaar-nieuwe-bestuurder-wij-zijn-jong</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10629,7 @@
       <c r="Y102" s="2" t="inlineStr"/>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>https://academedia.se/nyheter/vd-marcus-stromberg-vara-satsningar-ar-viktigare-an-nagonsin/; https://www.crunchbase.com/organization/academedia-ab/profiles_and_contacts</t>
+          <t>https://www.crunchbase.com/organization/academedia-ab/profiles_and_contacts; https://academedia.se/nyheter/vd-marcus-stromberg-vara-satsningar-ar-viktigare-an-nagonsin/</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11373,11 @@
           <t>name: Philip Smith; title: UK Managing Director (since early 2025) - confirmed; name: Nicole Krabbenborg; title: Managing Director, Kindergarden Netherlands - confirmed</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr"/>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>comms.team@brighthorizons.com</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="inlineStr"/>
       <c r="R110" s="2" t="inlineStr">
         <is>
@@ -11345,11 +11405,19 @@
           <t>paneuro.json</t>
         </is>
       </c>
-      <c r="X110" s="2" t="inlineStr"/>
-      <c r="Y110" s="2" t="inlineStr"/>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>iserpa@brighthorizons.com (Ilene Serpa, VP of Communications (2015 press release))</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>flast@brighthorizons.com</t>
+        </is>
+      </c>
       <c r="Z110" s="2" t="inlineStr">
         <is>
-          <t>https://www.zoominfo.com/p/Stephen-Kramer/786898162; https://www.brighthorizons.com/about/who-we-are/leadership/our-leadership/stephen-kramer</t>
+          <t>https://careers.brighthorizons.com/uk/en/contact-us; https://www.prnewswire.com/news-releases/bright-horizons-names-chief-development-officer-stephen-kramer-president-300196161.html; https://www.zoominfo.com/p/Stephen-Kramer/786898162</t>
         </is>
       </c>
     </row>
@@ -11401,8 +11469,16 @@
       <c r="M111" s="2" t="inlineStr"/>
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr"/>
-      <c r="P111" s="2" t="inlineStr"/>
-      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>info@agorainternationalandorra.com</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>+376 838 366</t>
+        </is>
+      </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
           <t>Agora Andorra is Globeducate's Andorran school with infant/early-years stages. Same group as Vaikystės sodas (Lithuania), enabling a cross-country group conversation. Decision maker not confirmed via search; verify on website/registry before outreach.</t>
@@ -11427,7 +11503,11 @@
       </c>
       <c r="X111" s="2" t="inlineStr"/>
       <c r="Y111" s="2" t="inlineStr"/>
-      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>https://andorra.agorainternationalschool.es/en/contact-and-admissions/contact; https://www.globeducate.com/our-schools/agora-internationsl-school-andorra/aisa</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -11473,8 +11553,16 @@
       <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="inlineStr"/>
-      <c r="Q112" s="2" t="inlineStr"/>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>office@hilfswerk.at; office@ooe.hilfswerk.at</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>01 / 40 57 500; Kinderbetreuung hotline 0800 800 820</t>
+        </is>
+      </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
           <t>Major welfare organisation; childcare is run by Landes-Hilfswerke. Hooks: Länder-level GF.</t>
@@ -11507,7 +11595,11 @@
       </c>
       <c r="X112" s="2" t="inlineStr"/>
       <c r="Y112" s="2" t="inlineStr"/>
-      <c r="Z112" s="2" t="inlineStr"/>
+      <c r="Z112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hilfswerk.at/oesterreich/impressum/</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -11557,8 +11649,16 @@
       <c r="M113" s="2" t="inlineStr"/>
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr"/>
-      <c r="P113" s="2" t="inlineStr"/>
-      <c r="Q113" s="2" t="inlineStr"/>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>office@kindercompany.at</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 961 9444</t>
+        </is>
+      </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
           <t>One of Vienna's largest private commercial Kindergarten chains, offering bilingual groups. Hooks: private operator with central management.</t>
@@ -11591,7 +11691,11 @@
       </c>
       <c r="X113" s="2" t="inlineStr"/>
       <c r="Y113" s="2" t="inlineStr"/>
-      <c r="Z113" s="2" t="inlineStr"/>
+      <c r="Z113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kindercompany.at/zentrale/; https://www.kindercompany.at/kontakt-platzanfragen/</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -11641,8 +11745,16 @@
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr"/>
-      <c r="P114" s="2" t="inlineStr"/>
-      <c r="Q114" s="2" t="inlineStr"/>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>office@wiki.at</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>0316 / 426565</t>
+        </is>
+      </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
           <t>Largest private childcare operator in Styria. Hooks: central management in Graz.</t>
@@ -11675,7 +11787,11 @@
       </c>
       <c r="X114" s="2" t="inlineStr"/>
       <c r="Y114" s="2" t="inlineStr"/>
-      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.familienberatung.gv.at/beratungsstellen/rechtstraeger/traeger/wiki-kinderbetreuungs-gmbh/; https://www.karriere.at/standort/wiki-kinderbetreuungs-gmbh</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -11725,8 +11841,16 @@
       <c r="M115" s="2" t="inlineStr"/>
       <c r="N115" s="2" t="inlineStr"/>
       <c r="O115" s="2" t="inlineStr"/>
-      <c r="P115" s="2" t="inlineStr"/>
-      <c r="Q115" s="2" t="inlineStr"/>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>post@ma10.wien.gv.at; sst12@ma10.wien.gv.at; sst16@ma10.wien.gv.at; sst22@ma10.wien.gv.at</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 277 55 55</t>
+        </is>
+      </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
           <t>Vienna's municipal kindergarten department, largest single operator in Austria. Hooks: public tender only.</t>
@@ -11759,7 +11883,11 @@
       </c>
       <c r="X115" s="2" t="inlineStr"/>
       <c r="Y115" s="2" t="inlineStr"/>
-      <c r="Z115" s="2" t="inlineStr"/>
+      <c r="Z115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wien.gv.at/english/education-research/service-centres-kindergarten.html; https://www.wien.gv.at/pdf/ma10/infoblatt-servicestellen-de.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -11813,8 +11941,16 @@
       </c>
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr"/>
-      <c r="P116" s="2" t="inlineStr"/>
-      <c r="Q116" s="2" t="inlineStr"/>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>sarajevo@qsi.org</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>+387 33 424 450</t>
+        </is>
+      </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
           <t>QSI Sarajevo is part of the Quality Schools International network and runs a preschool section. QSI also operates schools in Podgorica, Skopje, Tirana and Chișinău, so a network-level approach could cover several Balkan capitals. Decision maker not confirmed via search; verify on website/registry before outreach.</t>
@@ -11837,9 +11973,21 @@
           <t>other.json</t>
         </is>
       </c>
-      <c r="X116" s="2" t="inlineStr"/>
-      <c r="Y116" s="2" t="inlineStr"/>
-      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="X116" s="2" t="inlineStr">
+        <is>
+          <t>leah-jamele@sarajevo.qsi.org (Leah Jamele, School Director)</t>
+        </is>
+      </c>
+      <c r="Y116" s="2" t="inlineStr">
+        <is>
+          <t>first-last@sarajevo.qsi.org</t>
+        </is>
+      </c>
+      <c r="Z116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.state.gov/qsi-international-school-of-sarajevo-fact-sheet; https://www.qsi.org/connect/contact</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -11885,8 +12033,16 @@
       <c r="M117" s="2" t="inlineStr"/>
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="inlineStr"/>
-      <c r="Q117" s="2" t="inlineStr"/>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>traegerschaft@small-foot.ch</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>+41 41 210 21 20</t>
+        </is>
+      </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
           <t>Zurich Kita chain founded 2007 with nature-pedagogy and 'family-like' concept; expanding in Zurich/Zug. Hooks: growth-stage private chain.</t>
@@ -11919,7 +12075,11 @@
       </c>
       <c r="X117" s="2" t="inlineStr"/>
       <c r="Y117" s="2" t="inlineStr"/>
-      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.small-foot.ch/about/; https://www.moneyhouse.ch/en/company/small-foot-ag-4257128881</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -12057,7 +12217,11 @@
       <c r="M119" s="2" t="inlineStr"/>
       <c r="N119" s="2" t="inlineStr"/>
       <c r="O119" s="2" t="inlineStr"/>
-      <c r="P119" s="2" t="inlineStr"/>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>receptionES@sunnycanadian.cz; admissions@sunnycanadian.cz; hr@sunnycanadian.cz; activities@sunnycanadian.cz; zs@sunnycanadian.cz</t>
+        </is>
+      </c>
       <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr">
         <is>
@@ -12085,9 +12249,21 @@
           <t>cee.json</t>
         </is>
       </c>
-      <c r="X119" s="2" t="inlineStr"/>
-      <c r="Y119" s="2" t="inlineStr"/>
-      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>kosova@sunnycanadian.cz (Kosova (first name not shown), Kindergarten Principal); koznarova@sunnycanadian.cz (Koznarova (first name not shown), Elementary and High School Principal); marzian@sunnycanadian.cz (Marzian, Vice Principal of English Studies)</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>surname@sunnycanadian.cz</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sunnycanadian.cz/en/sunny/contact</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -12145,8 +12321,16 @@
           <t>name: Christophe Fond; title: MD Babilou Family Deutschland (group level)</t>
         </is>
       </c>
-      <c r="P120" s="2" t="inlineStr"/>
-      <c r="Q120" s="2" t="inlineStr"/>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>info@denk-mit.de; elternberatung@denk-mit.de; bewerbung@denk-mit.de</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 5126686-78</t>
+        </is>
+      </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
           <t>Denk mit! Kita is a South-German Kita chain that became part of Babilou Family Deutschland. It operates 56 facilities (over 50 in Bavaria and Baden-Württemberg) with 2,604 places and runs its own career site with active recruiting for 2026/27. Brand-level leadership is not confirmed; decisions on software are likely taken at Babilou group level. Hooks: staffing, parent communication across a large Munich cluster.</t>
@@ -12175,7 +12359,11 @@
       </c>
       <c r="X120" s="2" t="inlineStr"/>
       <c r="Y120" s="2" t="inlineStr"/>
-      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.denk-mit.de/ueber-uns/index.html; https://www.kita.de/traeger/97505; https://stadt.muenchen.de/service/info/denk-mit-kinderhaus/1085836/</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -12349,9 +12537,21 @@
           <t>paneuro.json</t>
         </is>
       </c>
-      <c r="X122" s="2" t="inlineStr"/>
-      <c r="Y122" s="2" t="inlineStr"/>
-      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>k.hecker@klett-gruppe.de (Karen Hecker, Leiterin Unternehmenskommunikation / Pressekontakt); d.barsch@klett-gruppe.de (D. Barsch, Unternehmenskommunikation)</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>f.last@klett-gruppe.de</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mynewsdesk.com/de/ernst-klett-ag/contact_people</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -12409,7 +12609,11 @@
       </c>
       <c r="N123" s="2" t="inlineStr"/>
       <c r="O123" s="2" t="inlineStr"/>
-      <c r="P123" s="2" t="inlineStr"/>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>info@froebel-gruppe.de</t>
+        </is>
+      </c>
       <c r="Q123" s="2" t="inlineStr"/>
       <c r="R123" s="2" t="inlineStr">
         <is>
@@ -12435,7 +12639,11 @@
       </c>
       <c r="X123" s="2" t="inlineStr"/>
       <c r="Y123" s="2" t="inlineStr"/>
-      <c r="Z123" s="2" t="inlineStr"/>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.froebel-gruppe.de/en/legal; https://www.froebel-gruppe.de/en/about-froebel/froebel-bildung-und-erziehung-ggmbh</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -12589,8 +12797,16 @@
       <c r="M125" s="2" t="inlineStr"/>
       <c r="N125" s="2" t="inlineStr"/>
       <c r="O125" s="2" t="inlineStr"/>
-      <c r="P125" s="2" t="inlineStr"/>
-      <c r="Q125" s="2" t="inlineStr"/>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>info@johanniter.de; kita.adlershof@johanniter.de</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>+49 30 26997-0 (Bund); 030 / 8169010 (RV Berlin)</t>
+        </is>
+      </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
           <t>One of the largest single non-profit Kita operators with more central structures than AWO/DRK; strong growth via new-build Kitas. Hooks: central digital strategy.</t>
@@ -12623,7 +12839,11 @@
       </c>
       <c r="X125" s="2" t="inlineStr"/>
       <c r="Y125" s="2" t="inlineStr"/>
-      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.johanniter.de/johanniter-unfall-hilfe/impressum/; https://www.adlershof.de/en/companies-institutes/directory/firma/detail/johanniter-unfall-hilfe-e-v-regionalverband-berlin-kita-adlershof</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -12673,8 +12893,16 @@
       <c r="M126" s="2" t="inlineStr"/>
       <c r="N126" s="2" t="inlineStr"/>
       <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="inlineStr"/>
-      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>info@kita-zweckverband.de</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>0201 3616927-110</t>
+        </is>
+      </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
           <t>Germany's largest single Catholic Kita operator, central HQ in Essen with unified IT. Hooks: very large central IT/parent-app decision.</t>
@@ -12707,7 +12935,11 @@
       </c>
       <c r="X126" s="2" t="inlineStr"/>
       <c r="Y126" s="2" t="inlineStr"/>
-      <c r="Z126" s="2" t="inlineStr"/>
+      <c r="Z126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kita-zweckverband.de/impressum</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -12957,8 +13189,16 @@
       <c r="M129" s="2" t="inlineStr"/>
       <c r="N129" s="2" t="inlineStr"/>
       <c r="O129" s="2" t="inlineStr"/>
-      <c r="P129" s="2" t="inlineStr"/>
-      <c r="Q129" s="2" t="inlineStr"/>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>kitaplatz@kmk-kinderzimmer.de; info@kita-kinderzimmer.de</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>040 8740 6666</t>
+        </is>
+      </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
           <t>kinderzimmer is one of Hamburg's fastest-growing private Kita chains, with over 35 locations in the city built since the mid-2010s. Known for design-led, standardised facilities and strong digital marketing. Ownership and leadership not confirmed in this session. Hooks: standardised operations, parent app rollout.</t>
@@ -12987,7 +13227,11 @@
       </c>
       <c r="X129" s="2" t="inlineStr"/>
       <c r="Y129" s="2" t="inlineStr"/>
-      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kita-kinderzimmer.de/impressum/; https://www.kita-kinderzimmer.de/kontakt/</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -13133,8 +13377,16 @@
       <c r="M131" s="2" t="inlineStr"/>
       <c r="N131" s="2" t="inlineStr"/>
       <c r="O131" s="2" t="inlineStr"/>
-      <c r="P131" s="2" t="inlineStr"/>
-      <c r="Q131" s="2" t="inlineStr"/>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>info@outlaw-ggmbh.de</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>0251 3835660</t>
+        </is>
+      </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
           <t>Outlaw is among the largest private Kita operators by facility count (ranked in pflegemarkt lists), active in NRW, Berlin, Saxony, Hamburg etc., and vocal in the NRW KiBiz reform debate. Hooks: multi-Land compliance, rapid growth.</t>
@@ -13167,7 +13419,11 @@
       </c>
       <c r="X131" s="2" t="inlineStr"/>
       <c r="Y131" s="2" t="inlineStr"/>
-      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.outlaw-ggmbh.de/impressum; https://www.outlaw-ggmbh.de/kontakt</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -13217,8 +13473,16 @@
       <c r="M132" s="2" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr"/>
       <c r="O132" s="2" t="inlineStr"/>
-      <c r="P132" s="2" t="inlineStr"/>
-      <c r="Q132" s="2" t="inlineStr"/>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>beschluss.kita.rbs@muenchen.de</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>+49 89 233-84099</t>
+        </is>
+      </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
           <t>Germany's largest municipal Kita operator; uses the city 'kita finder+' platform. Hooks: very large scale, public tender.</t>
@@ -13251,7 +13515,11 @@
       </c>
       <c r="X132" s="2" t="inlineStr"/>
       <c r="Y132" s="2" t="inlineStr"/>
-      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr">
+        <is>
+          <t>https://stadt.muenchen.de/service/info/geschaeftsbereich-kita-geschaeftsstelle-personal/1099431/; https://stadt.muenchen.de/service/info/referat-fur-bildung-und-sport/10223446/</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -13509,8 +13777,16 @@
       <c r="M135" s="2" t="inlineStr"/>
       <c r="N135" s="2" t="inlineStr"/>
       <c r="O135" s="2" t="inlineStr"/>
-      <c r="P135" s="2" t="inlineStr"/>
-      <c r="Q135" s="2" t="inlineStr"/>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>borneringen@borneringen.dk</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>+45 38 16 23 06</t>
+        </is>
+      </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
           <t>Paraplyorganisation for selvejende daginstitutioner primarily in Copenhagen area, providing administration and pedagogical support. Not verified in this session.</t>
@@ -13535,7 +13811,11 @@
       </c>
       <c r="X135" s="2" t="inlineStr"/>
       <c r="Y135" s="2" t="inlineStr"/>
-      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borneringen.dk/532/kontakt; https://www.krak.dk/b%C3%B8rneringen+valby/67220454/firma</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -13577,8 +13857,16 @@
       <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr"/>
-      <c r="P136" s="2" t="inlineStr"/>
-      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>info@fobu.dk</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>3324 8100</t>
+        </is>
+      </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
           <t>Association/administration body for private and self-owned daycare institutions (successor lineage of Frie Børnehaver og Fritidshjem). Not verified in this session.</t>
@@ -13603,7 +13891,11 @@
       </c>
       <c r="X136" s="2" t="inlineStr"/>
       <c r="Y136" s="2" t="inlineStr"/>
-      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>https://fobu.dk/om-fobu/kontakt/; https://fobu.dk/om-fobu/medarbejdere/</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -13645,8 +13937,16 @@
       <c r="M137" s="2" t="inlineStr"/>
       <c r="N137" s="2" t="inlineStr"/>
       <c r="O137" s="2" t="inlineStr"/>
-      <c r="P137" s="2" t="inlineStr"/>
-      <c r="Q137" s="2" t="inlineStr"/>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>ldd@ldd.dk</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>+45 32 95 32 30</t>
+        </is>
+      </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
           <t>Umbrella/administration organisation for selvejende and private daginstitutioner across Denmark, offering admin, payroll and consulting to member institutions. Not verified in this session.</t>
@@ -13671,7 +13971,11 @@
       </c>
       <c r="X137" s="2" t="inlineStr"/>
       <c r="Y137" s="2" t="inlineStr"/>
-      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr">
+        <is>
+          <t>https://danskedaginstitutioner.dk/kontakt/; https://www.proff.dk/firma/landsorganisationen-danske-daginstitutioner/aller%C3%B8d/kontor-og-teletjenester/0F1OXQI07SL</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -13713,8 +14017,16 @@
       <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr"/>
       <c r="O138" s="2" t="inlineStr"/>
-      <c r="P138" s="2" t="inlineStr"/>
-      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>info@fobu.dk</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>3324 8100</t>
+        </is>
+      </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
           <t>Umbrella for church-affiliated self-owned daginstitutioner in Denmark; provides administration and leadership development. Not verified in this session.</t>
@@ -13739,7 +14051,11 @@
       </c>
       <c r="X138" s="2" t="inlineStr"/>
       <c r="Y138" s="2" t="inlineStr"/>
-      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr">
+        <is>
+          <t>https://indsamling.folkekirken.dk/organisationer/fobu-tidligere-mdi; https://fobu.dk/om-fobu/fobus-historie/</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -13797,8 +14113,16 @@
           <t>Early Years programme (ages 3-6); state.gov fact sheet lists governance</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr"/>
-      <c r="Q139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>office@ise.edu.ee; admissions@ise.edu.ee; director@ise.edu.ee</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>+372 666 4380</t>
+        </is>
+      </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
           <t>ISE is Estonia's first IB World School, offering PYP from Early Years (ages 3-6) through the Diploma Programme. It is non-profit and governed by a board, with US State Department fact sheets published annually. The Early Years section is a small preschool inside the main campus. Decision maker not confirmed via search; verify on website/registry before outreach. Good target for premium school-photography given expatriate parent base. Single site but high-fee.</t>
@@ -13823,7 +14147,11 @@
       </c>
       <c r="X139" s="2" t="inlineStr"/>
       <c r="Y139" s="2" t="inlineStr"/>
-      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr">
+        <is>
+          <t>https://ise.edu.ee/contact/; https://www.state.gov/international-school-of-estonia-fact-sheet/</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -13881,7 +14209,11 @@
           <t>Staff page ist.ee/about-ist/our-staff</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>director@ist.ee</t>
+        </is>
+      </c>
       <c r="Q140" s="2" t="inlineStr"/>
       <c r="R140" s="2" t="inlineStr">
         <is>
@@ -13905,9 +14237,17 @@
           <t>other.json</t>
         </is>
       </c>
-      <c r="X140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>director@ist.ee (Olavi Otepalu, Director)</t>
+        </is>
+      </c>
       <c r="Y140" s="2" t="inlineStr"/>
-      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr">
+        <is>
+          <t>https://ist.ee/contact/contacts/</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -13957,8 +14297,16 @@
       <c r="M141" s="2" t="inlineStr"/>
       <c r="N141" s="2" t="inlineStr"/>
       <c r="O141" s="2" t="inlineStr"/>
-      <c r="P141" s="2" t="inlineStr"/>
-      <c r="Q141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>info@ramlasteaed.ee; post@ramkool.edu.ee</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
+          <t>+372 57560010 / 57560017</t>
+        </is>
+      </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
           <t>Rocca al Mare School is a well-known private school in Tallinn that operates the Veskimöldre kindergarten listed among Tallinn private kindergartens. The group is a premium private education provider. Decision maker not confirmed via search; verify on website/registry before outreach. A school-level marketing/communications contact would be the route. Mid priority.</t>
@@ -13983,7 +14331,11 @@
       </c>
       <c r="X141" s="2" t="inlineStr"/>
       <c r="Y141" s="2" t="inlineStr"/>
-      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr">
+        <is>
+          <t>https://piksel.ee/arno/rae/ee/lasteaiad/vaata/167; https://ramkool.edu.ee/lasteaed/vastuvott/; https://ramkool.edupage.org/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -14025,8 +14377,16 @@
       <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr"/>
       <c r="O142" s="2" t="inlineStr"/>
-      <c r="P142" s="2" t="inlineStr"/>
-      <c r="Q142" s="2" t="inlineStr"/>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>info@arasti.com; administracion@arasti.com; cadiz@arasti.com; santiago@arasti.com; coruna@arasti.com; igualdad@arasti.com</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>+34 947 257 690</t>
+        </is>
+      </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
           <t>Arasti Barca is a Cantabrian company that manages publicly owned escuelas infantiles under concession, with a significant presence in the Comunidad de Madrid's public 0-3 network and in Cantabria. It appears among the gestoras listed in Madrid open data. Centralised HR and purchasing.</t>
@@ -14053,9 +14413,21 @@
           <t>south.json</t>
         </is>
       </c>
-      <c r="X142" s="2" t="inlineStr"/>
-      <c r="Y142" s="2" t="inlineStr"/>
-      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr">
+        <is>
+          <t>pilar@arasti.com (Pilar (surname not shown), contact listed on arasti.com)</t>
+        </is>
+      </c>
+      <c r="Y142" s="2" t="inlineStr">
+        <is>
+          <t>firstname@arasti.com</t>
+        </is>
+      </c>
+      <c r="Z142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arasti.com/contacto/; https://www.arasti.com/quienes-somos/</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -14105,8 +14477,16 @@
       <c r="M143" s="2" t="inlineStr"/>
       <c r="N143" s="2" t="inlineStr"/>
       <c r="O143" s="2" t="inlineStr"/>
-      <c r="P143" s="2" t="inlineStr"/>
-      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>cavalldecartro@cavallcartro.cat</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>+34 937 793 305</t>
+        </is>
+      </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
           <t>Cavall de Cartró manages municipal nurseries and educational projects throughout Catalonia, for example Escola Bressol Municipal Mestre Jané in Sant Feliu de Codines. It also runs Espai Obert family programmes. The company publishes a map of its centres online. A mid-size concession operator worth qualifying.</t>
@@ -14135,7 +14515,11 @@
       </c>
       <c r="X143" s="2" t="inlineStr"/>
       <c r="Y143" s="2" t="inlineStr"/>
-      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavallcartro.cat/contacte; https://empresite.eleconomista.es/SERVEIS-EDUCATIUS-CAVALL-CARTRO.html</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -14177,8 +14561,16 @@
       <c r="M144" s="2" t="inlineStr"/>
       <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr"/>
-      <c r="P144" s="2" t="inlineStr"/>
-      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>spain@cognita.com; admisionescem@cognita.com</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>+34 93 647 70 00</t>
+        </is>
+      </c>
       <c r="R144" s="2" t="inlineStr">
         <is>
           <t>Cognita operates a cluster of bilingual/international schools in Spain (e.g. Colegio Europeo de Madrid, Hastings School, El Limonar International School) all with nursery/early-years sections. Purchasing is coordinated regionally from Madrid.</t>
@@ -14207,7 +14599,11 @@
       </c>
       <c r="X144" s="2" t="inlineStr"/>
       <c r="Y144" s="2" t="inlineStr"/>
-      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cognita.com/contact-us/; https://www.colegioeuropeodemadrid.com/en/contact-us/; https://rocketreach.co/cognita-schools-email-format_b5cd6d1ef42e0b11</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -14257,8 +14653,16 @@
       <c r="M145" s="2" t="inlineStr"/>
       <c r="N145" s="2" t="inlineStr"/>
       <c r="O145" s="2" t="inlineStr"/>
-      <c r="P145" s="2" t="inlineStr"/>
-      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>info@grupoeducare.es; dpd@grupoeducare.es</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>918595811</t>
+        </is>
+      </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
           <t>Grupo Educare promotes and manages private/concertado schools in the Madrid region, all offering early-years cycles from 0-1 years. Its five campuses sit in Torrelodones, Sanchinarro, Colmenar Viejo, Ensanche de Vallecas and Cerceda. Management is centralised in La Navata. Not linked to any 'Britannia' brand as far as could be verified.</t>
@@ -14287,7 +14691,11 @@
       </c>
       <c r="X145" s="2" t="inlineStr"/>
       <c r="Y145" s="2" t="inlineStr"/>
-      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr">
+        <is>
+          <t>https://grupoeducare.es/; https://grupoeducare.es/politica-privacidad/</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -14359,7 +14767,11 @@
       </c>
       <c r="X146" s="2" t="inlineStr"/>
       <c r="Y146" s="2" t="inlineStr"/>
-      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr">
+        <is>
+          <t>https://rocketreach.co/maximiliano-martin-email_87482788; https://www.highperformr.ai/company/inspired-ed</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -14429,8 +14841,16 @@
           <t>Natalia Perarnau - founder; Marta Illa - director Kids&amp;Us Manresa</t>
         </is>
       </c>
-      <c r="P147" s="2" t="inlineStr"/>
-      <c r="Q147" s="2" t="inlineStr"/>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>info@kidsandus.es; lasrosas@kidsandus.es</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>900 37 37 92</t>
+        </is>
+      </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
           <t>Kids&amp;Us is an English-teaching franchise founded in Manresa in 2003 whose method starts at age one; it is not a full-day nursery operator but partners with escuelas infantiles to deliver English inside them. It has grown past 700 centres in Europe, Asia and Latin America with 190,000 students and plans 300 more academies by 2028. Ana Rojo (ex-Douglas) leads the company as CEO under Corpfin Capital ownership. Relevant as a channel partner to nurseries rather than an end operator.</t>
@@ -14461,7 +14881,7 @@
       <c r="Y147" s="2" t="inlineStr"/>
       <c r="Z147" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidsandus.es/es; https://careers.kidsandus.com/</t>
+          <t>https://www.kidsandus.es/es/contacto; https://las-rosas.kidsandus.es/es/contacto/</t>
         </is>
       </c>
     </row>
@@ -14505,8 +14925,16 @@
       <c r="M148" s="2" t="inlineStr"/>
       <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr"/>
-      <c r="P148" s="2" t="inlineStr"/>
-      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>info@kidsco.es</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>+34 917 080 206</t>
+        </is>
+      </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
           <t>Kidsco designs and operates workplace nurseries for large employers and public bodies in Spain, and also runs its own escuelas infantiles. Its B2B model concentrates purchasing decisions in a single HQ.</t>
@@ -14535,7 +14963,11 @@
       </c>
       <c r="X148" s="2" t="inlineStr"/>
       <c r="Y148" s="2" t="inlineStr"/>
-      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidsco.es/donde-estamos</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -14589,7 +15021,11 @@
           <t>'Mónica' - founder and director (surname not confirmed)</t>
         </is>
       </c>
-      <c r="P149" s="2" t="inlineStr"/>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>hello@montessorivillage.es; comunicacion@montessorivillage.es; piovera@montessorivillage.es; alcala@montessorivillage.es; sarria@montessorivillage.es; lamoraleja@montessorivillage.es</t>
+        </is>
+      </c>
       <c r="Q149" s="2" t="inlineStr"/>
       <c r="R149" s="2" t="inlineStr">
         <is>
@@ -14619,7 +15055,11 @@
       </c>
       <c r="X149" s="2" t="inlineStr"/>
       <c r="Y149" s="2" t="inlineStr"/>
-      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montessorivillage.es/contacto/</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -14691,7 +15131,11 @@
       </c>
       <c r="X150" s="2" t="inlineStr"/>
       <c r="Y150" s="2" t="inlineStr"/>
-      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.asiakastieto.fi/yritykset/fi/dibber-early-education-finland-oy/31149019/rekisteritiedot; https://www.dibber.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -14733,8 +15177,16 @@
       <c r="M151" s="2" t="inlineStr"/>
       <c r="N151" s="2" t="inlineStr"/>
       <c r="O151" s="2" t="inlineStr"/>
-      <c r="P151" s="2" t="inlineStr"/>
-      <c r="Q151" s="2" t="inlineStr"/>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>info@heischools.com</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>+358 40 8600277</t>
+        </is>
+      </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
           <t>Finnish early-education concept licensed internationally (Asia, Middle East, Americas) with a few own units in Finland. Not verified in this session.</t>
@@ -14757,9 +15209,21 @@
           <t>nordics.json</t>
         </is>
       </c>
-      <c r="X151" s="2" t="inlineStr"/>
-      <c r="Y151" s="2" t="inlineStr"/>
-      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>heikki.vartia@heischools.com (Heikki Vartia, Director of Partnerships); aditi.katara@heischools.com (Aditi Katara, Partnerships Manager - Toolkit Curriculum); sami.makinen@heischools.com (Sami Makinen, Director of Partnerships); milla.kokko@heischools.com (Milla Kokko, ); inkeri.aimonen@heischools.com (Inkeri Aimonen, )</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr">
+        <is>
+          <t>first.last@domain</t>
+        </is>
+      </c>
+      <c r="Z151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.heischools.com/company/contact-us/; https://www.zoominfo.com/pic/hei-schools/449191694; https://www.finder.fi/Koulutukset+ja+koulutuspalvelut/Helsinki+International+Schools+Group+Oy/Helsinki/yhteystiedot/3102309</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -14801,8 +15265,16 @@
       <c r="M152" s="2" t="inlineStr"/>
       <c r="N152" s="2" t="inlineStr"/>
       <c r="O152" s="2" t="inlineStr"/>
-      <c r="P152" s="2" t="inlineStr"/>
-      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>hallinto@norlandia.com</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>010 8367200</t>
+        </is>
+      </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
           <t>Finnish preschool arm of Norlandia; group confirmed to operate in Finland. Unit count and Finnish MD not verified.</t>
@@ -14831,7 +15303,11 @@
       </c>
       <c r="X152" s="2" t="inlineStr"/>
       <c r="Y152" s="2" t="inlineStr"/>
-      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finder.fi/Yksityinen+p%C3%A4iv%C3%A4koti/Norlandia+P%C3%A4iv%C3%A4kodit+Oy/Espoo/yhteystiedot/346361</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -14897,7 +15373,11 @@
           <t>title: Partner leading Babilou Family investment - not confirmed</t>
         </is>
       </c>
-      <c r="P153" s="2" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>media@antin-ip.com; shareholders@antin-ip.com; antinip@brunswickgroup.com</t>
+        </is>
+      </c>
       <c r="Q153" s="2" t="inlineStr"/>
       <c r="R153" s="2" t="inlineStr">
         <is>
@@ -14929,7 +15409,7 @@
       <c r="Y153" s="2" t="inlineStr"/>
       <c r="Z153" s="2" t="inlineStr">
         <is>
-          <t>https://www.antin-ip.com/who-we-are/team/people/alain-rauscher; https://www.antin-ip.com/team</t>
+          <t>https://www.antin-ip.com/media/press; https://www.antin-ip.com/who-we-are/team/people/alain-rauscher; https://live.euronext.com/en/products/equities/company-news/2026-01-20-antin-announces-new-roles-within-its-senior-leadership</t>
         </is>
       </c>
     </row>
@@ -15201,8 +15681,16 @@
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr"/>
-      <c r="P156" s="2" t="inlineStr"/>
-      <c r="Q156" s="2" t="inlineStr"/>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>contact@ff-entreprises-creches.com</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>01 41 03 14 80; Elsa Hervy 06 38 54 49 73</t>
+        </is>
+      </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
           <t>FFEC is the trade body of private crèche companies in France (Babilou, LPCR, La Maison Bleue, People&amp;Baby, Liveli, Léa &amp; Léo and many SMEs). It lobbies on the 2025 reforms (micro-crèche decree, quality controls) and runs events attended by group executives. Useful as a channel to reach many operators at once. Leadership not confirmed in this session.</t>
@@ -15229,9 +15717,21 @@
           <t>fr_benelux.json</t>
         </is>
       </c>
-      <c r="X156" s="2" t="inlineStr"/>
-      <c r="Y156" s="2" t="inlineStr"/>
-      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>elsahervy@ff-entreprises-creches.com (Elsa Hervy, Déléguée Générale)</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr">
+        <is>
+          <t>firstlast@ff-entreprises-creches.com</t>
+        </is>
+      </c>
+      <c r="Z156" s="2" t="inlineStr">
+        <is>
+          <t>https://ff-entreprises-creches.com/contact/; https://ff-entreprises-creches.com/app/uploads/2024/09/2024-09-30-ffec-actions-plfss-2025.pdf; https://ff-entreprises-creches.com/presse/2023-04-igas/</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -15621,8 +16121,16 @@
       </c>
       <c r="N160" s="2" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr"/>
-      <c r="P160" s="2" t="inlineStr"/>
-      <c r="Q160" s="2" t="inlineStr"/>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>info@fremman.com; investorrelations@fremman.com</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>+44 (0) 20 7458 4626</t>
+        </is>
+      </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
           <t>Fremman Capital invested in Kids Planet in 2023 alongside Souter Investments and Tresmares, funding growth to 240-290 UK nurseries. Fremman is pan-European (London, Madrid, Paris, Munich), so a cross-border childcare platform is plausible. Sector partner: Kids Planet.</t>
@@ -15651,7 +16159,11 @@
       </c>
       <c r="X160" s="2" t="inlineStr"/>
       <c r="Y160" s="2" t="inlineStr"/>
-      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr">
+        <is>
+          <t>https://fremman.com/contact-us/; https://leadiq.com/c/fremman-capital/602410ba411f372b40c94414/email-format</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -15723,7 +16235,11 @@
       </c>
       <c r="X161" s="2" t="inlineStr"/>
       <c r="Y161" s="2" t="inlineStr"/>
-      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oakleycapital.com/news-and-insights/investment-in-icp-education; https://www.kirkland.com/news/press-release/2021/06/kirkland-advises-oakley-capital-on-investment-in-i</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -16109,7 +16625,7 @@
       <c r="Y165" s="2" t="inlineStr"/>
       <c r="Z165" s="2" t="inlineStr">
         <is>
-          <t>https://schoolsshow.co.uk/speakers/leanna-barrett; https://www.education-cities.com/little-forest-folk/</t>
+          <t>https://www.parenta.com/2017/06/30/little-forest-folk-finding-joy-in-the-great-outdoors/; https://www.education-cities.com/little-forest-folk/</t>
         </is>
       </c>
     </row>
@@ -16161,8 +16677,16 @@
       <c r="M166" s="2" t="inlineStr"/>
       <c r="N166" s="2" t="inlineStr"/>
       <c r="O166" s="2" t="inlineStr"/>
-      <c r="P166" s="2" t="inlineStr"/>
-      <c r="Q166" s="2" t="inlineStr"/>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>info@littlepioneers.coop; careers@littlepioneers.coop</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>0800 954 0669</t>
+        </is>
+      </c>
       <c r="R166" s="2" t="inlineStr">
         <is>
           <t>Childcare division of The Midcounties Co-operative, rebranded from Co-operative Childcare to Little Pioneers. Runs nurseries and out-of-school clubs across the Midlands, South and London, with co-operative values and strong employer benefits. Reported disposal of some sites to Grandir UK - verify. Decision making sits with the Co-op's Head of Childcare.</t>
@@ -16191,7 +16715,11 @@
       </c>
       <c r="X166" s="2" t="inlineStr"/>
       <c r="Y166" s="2" t="inlineStr"/>
-      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlepioneers.coop/contact-us/; https://rocketreach.co/justine-cope-email_224610151; https://leadiq.com/c/little-pioneers/5a1d95d22300005b00847e53/email-format</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -16241,8 +16769,16 @@
       <c r="M167" s="2" t="inlineStr"/>
       <c r="N167" s="2" t="inlineStr"/>
       <c r="O167" s="2" t="inlineStr"/>
-      <c r="P167" s="2" t="inlineStr"/>
-      <c r="Q167" s="2" t="inlineStr"/>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>info@mamabear.co.uk; opsdirector@mamabear.co.uk</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>+44 117 958 2030</t>
+        </is>
+      </c>
       <c r="R167" s="2" t="inlineStr">
         <is>
           <t>Family-run South West group known for its 'Mama Bear' brand and pre-schools; one of the larger regional independents. Verify current MD and count.</t>
@@ -16271,7 +16807,11 @@
       </c>
       <c r="X167" s="2" t="inlineStr"/>
       <c r="Y167" s="2" t="inlineStr"/>
-      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr">
+        <is>
+          <t>https://mamabear.co.uk/index.php/contact-us?nursery=downend-road---downend; https://mamabear.co.uk/policies</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -16477,7 +17017,7 @@
       <c r="Y169" s="2" t="inlineStr"/>
       <c r="Z169" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/sarah1mackenzie</t>
+          <t>https://www.nurseryworld.co.uk/news/article/sarah-mackenzie-starts-new-role-as-ceo-of-storal-learning; https://theorg.com/org/storal/org-chart/sarah-mackenzie</t>
         </is>
       </c>
     </row>
@@ -16833,7 +17373,11 @@
       <c r="M173" s="2" t="inlineStr"/>
       <c r="N173" s="2" t="inlineStr"/>
       <c r="O173" s="2" t="inlineStr"/>
-      <c r="P173" s="2" t="inlineStr"/>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>rainbowhouse@welcomenurseries.com; cowlersleylane@welcomenurseries.com; alfreton@welcomenurseries.com</t>
+        </is>
+      </c>
       <c r="Q173" s="2" t="inlineStr"/>
       <c r="R173" s="2" t="inlineStr">
         <is>
@@ -16863,7 +17407,11 @@
       </c>
       <c r="X173" s="2" t="inlineStr"/>
       <c r="Y173" s="2" t="inlineStr"/>
-      <c r="Z173" s="2" t="inlineStr"/>
+      <c r="Z173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bwd-localoffer.org.uk/kb5/blackburn/directory/service.page?id=UKiLTHjflCI&amp;localofferchannel=0; https://find-and-update.company-information.service.gov.uk/company/12027560; https://reports.ofsted.gov.uk/provider/49/2576357</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -16913,8 +17461,16 @@
       <c r="M174" s="2" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr"/>
-      <c r="P174" s="2" t="inlineStr"/>
-      <c r="Q174" s="2" t="inlineStr"/>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>info@doukas.gr; admissions@doukas.gr; dpo@doukas.gr</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>+30 210 6186000</t>
+        </is>
+      </c>
       <c r="R174" s="2" t="inlineStr">
         <is>
           <t>Doukas School offers pre-school (paidikos stathmos and nipiagogeio) through lyceum with a strong ed-tech profile. Family-owned single campus.</t>
@@ -16941,9 +17497,21 @@
           <t>south.json</t>
         </is>
       </c>
-      <c r="X174" s="2" t="inlineStr"/>
-      <c r="Y174" s="2" t="inlineStr"/>
-      <c r="Z174" s="2" t="inlineStr"/>
+      <c r="X174" s="2" t="inlineStr">
+        <is>
+          <t>t.iosifidis@doukas.gr (T. Iosifidis, Examinations Officer)</t>
+        </is>
+      </c>
+      <c r="Y174" s="2" t="inlineStr">
+        <is>
+          <t>f.last@doukas.gr</t>
+        </is>
+      </c>
+      <c r="Z174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.doukas.edu.gr/epikoinonia/; https://www.doukas.edu.gr/en/admissions/</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -16993,8 +17561,16 @@
       <c r="M175" s="2" t="inlineStr"/>
       <c r="N175" s="2" t="inlineStr"/>
       <c r="O175" s="2" t="inlineStr"/>
-      <c r="P175" s="2" t="inlineStr"/>
-      <c r="Q175" s="2" t="inlineStr"/>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>gumnasio@ea.gr</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
+          <t>210 8176700</t>
+        </is>
+      </c>
       <c r="R175" s="2" t="inlineStr">
         <is>
           <t>Ellinogermaniki Agogi is a large private school in eastern Attica with kindergarten through lyceum, known for research and innovation projects (R&amp;D department). Family-owned. Single large campus with substantial early-years intake.</t>
@@ -17021,9 +17597,21 @@
           <t>south.json</t>
         </is>
       </c>
-      <c r="X175" s="2" t="inlineStr"/>
-      <c r="Y175" s="2" t="inlineStr"/>
-      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="X175" s="2" t="inlineStr">
+        <is>
+          <t>sotiriou@ea.gr (Sotiriou (R&amp;D Department), R&amp;D Department contact)</t>
+        </is>
+      </c>
+      <c r="Y175" s="2" t="inlineStr">
+        <is>
+          <t>last@ea.gr</t>
+        </is>
+      </c>
+      <c r="Z175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ea.gr/en/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -17073,7 +17661,11 @@
       <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr"/>
-      <c r="P176" s="2" t="inlineStr"/>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>blanchardstown@brighthorizons.com; leopardstown@brighthorizons.com</t>
+        </is>
+      </c>
       <c r="Q176" s="2" t="inlineStr"/>
       <c r="R176" s="2" t="inlineStr">
         <is>
@@ -17103,7 +17695,11 @@
       </c>
       <c r="X176" s="2" t="inlineStr"/>
       <c r="Y176" s="2" t="inlineStr"/>
-      <c r="Z176" s="2" t="inlineStr"/>
+      <c r="Z176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mummypages.ie/childcare/dublin/blanchardstown/bright-horizons-family-solutions-blanchardstown; https://www.mummypages.ie/childcare/dublin/leopardstown/bright-horizons-at-leopardstown; https://www.solocheck.ie/Irish-Company/Bright-Horizons-Family-Solutions-Ireland-Limited-288883</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -17153,8 +17749,16 @@
       <c r="M177" s="2" t="inlineStr"/>
       <c r="N177" s="2" t="inlineStr"/>
       <c r="O177" s="2" t="inlineStr"/>
-      <c r="P177" s="2" t="inlineStr"/>
-      <c r="Q177" s="2" t="inlineStr"/>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>info@cocoonchildcare.ie; facebook@cocoonchildcare.ie</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>+353-1-419 9999</t>
+        </is>
+      </c>
       <c r="R177" s="2" t="inlineStr">
         <is>
           <t>Dublin/Leinster group; reports of acquisition by an international operator - verify.</t>
@@ -17183,7 +17787,11 @@
       </c>
       <c r="X177" s="2" t="inlineStr"/>
       <c r="Y177" s="2" t="inlineStr"/>
-      <c r="Z177" s="2" t="inlineStr"/>
+      <c r="Z177" s="2" t="inlineStr">
+        <is>
+          <t>https://cocoonchildcare.ie/get-touch; https://www.facebook.com/cocoonchildcare.ie/about</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -17234,7 +17842,11 @@
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr"/>
       <c r="P178" s="2" t="inlineStr"/>
-      <c r="Q178" s="2" t="inlineStr"/>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>+353 1 405 7100</t>
+        </is>
+      </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
           <t>National membership organisation for early years services in Ireland; not an operator but a key channel/partner (events, member offers). CEO Frances Byrne (prior knowledge).</t>
@@ -17261,9 +17873,21 @@
           <t>uk_ie.json</t>
         </is>
       </c>
-      <c r="X178" s="2" t="inlineStr"/>
-      <c r="Y178" s="2" t="inlineStr"/>
-      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>theeney@earlychildhoodireland.ie (Teresa Heeney, Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr">
+        <is>
+          <t>flast@earlychildhoodireland.ie</t>
+        </is>
+      </c>
+      <c r="Z178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.earlychildhoodireland.ie/wp-content/uploads/2024/03/Child-Safeguarding-Statement.pdf; https://www.earlychildhoodireland.ie/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -17313,8 +17937,16 @@
       <c r="M179" s="2" t="inlineStr"/>
       <c r="N179" s="2" t="inlineStr"/>
       <c r="O179" s="2" t="inlineStr"/>
-      <c r="P179" s="2" t="inlineStr"/>
-      <c r="Q179" s="2" t="inlineStr"/>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>info@linkschildcare.ie; recruitment@linkschildcare.ie</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>1800 93 00 88</t>
+        </is>
+      </c>
       <c r="R179" s="2" t="inlineStr">
         <is>
           <t>One of Dublin's larger creche groups. Verify ownership (reports of sale to an international group).</t>
@@ -17343,7 +17975,11 @@
       </c>
       <c r="X179" s="2" t="inlineStr"/>
       <c r="Y179" s="2" t="inlineStr"/>
-      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr">
+        <is>
+          <t>https://linkschildcare.ie/contact-us/; https://www.zoominfo.com/pic/links-childcare/372521794</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -17393,8 +18029,16 @@
       <c r="M180" s="2" t="inlineStr"/>
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr"/>
-      <c r="P180" s="2" t="inlineStr"/>
-      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>info@parkchildcare.ie; enquiries@parkchildcare.ie; recruitment@parkchildcare.ie</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
+          <t>1800 273 243</t>
+        </is>
+      </c>
       <c r="R180" s="2" t="inlineStr">
         <is>
           <t>Premium South Dublin group with Montessori/creche services. Verify leadership.</t>
@@ -17423,7 +18067,11 @@
       </c>
       <c r="X180" s="2" t="inlineStr"/>
       <c r="Y180" s="2" t="inlineStr"/>
-      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.parkchildcare.ie/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -17469,8 +18117,16 @@
       <c r="M181" s="2" t="inlineStr"/>
       <c r="N181" s="2" t="inlineStr"/>
       <c r="O181" s="2" t="inlineStr"/>
-      <c r="P181" s="2" t="inlineStr"/>
-      <c r="Q181" s="2" t="inlineStr"/>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>info@aldia.it; aldia@pec.confcooperative.it</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>0382529444</t>
+        </is>
+      </c>
       <c r="R181" s="2" t="inlineStr">
         <is>
           <t>Aldia manages municipal and corporate nidi and scuole dell'infanzia across Lombardy, Piedmont, Emilia and Lazio. Mid-large operator.</t>
@@ -17497,9 +18153,21 @@
           <t>south.json</t>
         </is>
       </c>
-      <c r="X181" s="2" t="inlineStr"/>
-      <c r="Y181" s="2" t="inlineStr"/>
-      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>mattia.affini@aldia.it (Mattia Affini, Legal representative); camilla.costa@aldia.it (Camilla Costa, Referente); cristina.mocchetto@aldia.it (Cristina Mocchetto, Psychology referent)</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr">
+        <is>
+          <t>first.last@aldia.it</t>
+        </is>
+      </c>
+      <c r="Z181" s="2" t="inlineStr">
+        <is>
+          <t>https://tirocini.opl.it/scheda-ente-pubblica.php?ide=33; https://www.portaledeigiovani.it/scheda-utente/29018; https://www.aldia.it/contatti/</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -17545,8 +18213,16 @@
       <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr"/>
-      <c r="P182" s="2" t="inlineStr"/>
-      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>info@societadolce.it; societadolce@pec.it</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>051 6441211 (Karabak Quattro)</t>
+        </is>
+      </c>
       <c r="R182" s="2" t="inlineStr">
         <is>
           <t>Karabak is a series of consortia set up in Bologna to design, build and run municipal nidi under project finance for 20-25 year concessions. Educational management is by CADIAI; catering by Camst. Relevant for long-term supply arrangements.</t>
@@ -17575,7 +18251,11 @@
       </c>
       <c r="X182" s="2" t="inlineStr"/>
       <c r="Y182" s="2" t="inlineStr"/>
-      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bolognazerodiciotto.it/profiles/profile-karabak; https://karabakquattro.it/; https://www.cadiai.it/consorzi</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -17621,8 +18301,16 @@
       <c r="M183" s="2" t="inlineStr"/>
       <c r="N183" s="2" t="inlineStr"/>
       <c r="O183" s="2" t="inlineStr"/>
-      <c r="P183" s="2" t="inlineStr"/>
-      <c r="Q183" s="2" t="inlineStr"/>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>info@fondazionemontessori.it; formazione@fondazionemontessori.it; consulenza@fondazionemontessori.it; amministrazione@fondazionemontessori.it; rivista@fondazionemontessori.it</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>+39 373 750 0051</t>
+        </is>
+      </c>
       <c r="R183" s="2" t="inlineStr">
         <is>
           <t>Fondazione Montessori Italia trains educators and certifies Montessori nidi and scuole (Rete Montessori). Influencer for product standards among affiliated nurseries.</t>
@@ -17651,7 +18339,11 @@
       </c>
       <c r="X183" s="2" t="inlineStr"/>
       <c r="Y183" s="2" t="inlineStr"/>
-      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fondazionemontessori.it/contatti/</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -17697,7 +18389,11 @@
       <c r="M184" s="2" t="inlineStr"/>
       <c r="N184" s="2" t="inlineStr"/>
       <c r="O184" s="2" t="inlineStr"/>
-      <c r="P184" s="2" t="inlineStr"/>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>istituzionescuolenidi@comune.re.it; reclutamento.istituzione@comune.re.it; ufficiotecnico.istituzione@comune.re.it; Martiri.SCI@comune.re.it</t>
+        </is>
+      </c>
       <c r="Q184" s="2" t="inlineStr"/>
       <c r="R184" s="2" t="inlineStr">
         <is>
@@ -17727,7 +18423,11 @@
       </c>
       <c r="X184" s="2" t="inlineStr"/>
       <c r="Y184" s="2" t="inlineStr"/>
-      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.comune.reggioemilia.it/amministrazione/uffici/istituzione-scuole-e-nidi-d-infanzia-ufficio-assunzioni; https://www.comune.re.it/amministrazione/uffici/istituzione-scuole-e-nidi-dinfanzia-ufficio-tecnico; https://www.scuolenidi.re.it/Sezione.jsp?titolo=Informazioni&amp;idSezione=34</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -17773,8 +18473,16 @@
       <c r="M185" s="2" t="inlineStr"/>
       <c r="N185" s="2" t="inlineStr"/>
       <c r="O185" s="2" t="inlineStr"/>
-      <c r="P185" s="2" t="inlineStr"/>
-      <c r="Q185" s="2" t="inlineStr"/>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>info@koinecoopsociale.it; prenotazioni@koinecoopsociale.it</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
+          <t>02 42292265</t>
+        </is>
+      </c>
       <c r="R185" s="2" t="inlineStr">
         <is>
           <t>Koinè manages nidi, scuole dell'infanzia and family services for municipalities and companies in the Milan area. Mid-size operator with central purchasing.</t>
@@ -17803,7 +18511,11 @@
       </c>
       <c r="X185" s="2" t="inlineStr"/>
       <c r="Y185" s="2" t="inlineStr"/>
-      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr">
+        <is>
+          <t>https://koinecoopsociale.it/en/contatti/; https://koinecoopsociale.it/en/contacts/</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -17849,8 +18561,16 @@
       <c r="M186" s="2" t="inlineStr"/>
       <c r="N186" s="2" t="inlineStr"/>
       <c r="O186" s="2" t="inlineStr"/>
-      <c r="P186" s="2" t="inlineStr"/>
-      <c r="Q186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>info@lacoccinella.coop; lacoccinellascs@pec.it</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
+          <t>+39 0463 600168</t>
+        </is>
+      </c>
       <c r="R186" s="2" t="inlineStr">
         <is>
           <t>La Coccinella runs a large share of municipal nidi in the Province of Trento and is a reference for the Trentino 0-3 model. Central HQ in Cles.</t>
@@ -17879,7 +18599,11 @@
       </c>
       <c r="X186" s="2" t="inlineStr"/>
       <c r="Y186" s="2" t="inlineStr"/>
-      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cooperazionetrentina.it/it/cooperative/la-coccinella-societa-cooperativa-sociale-onlus; https://www.lacoccinella.coop/content/organigramma</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -17925,8 +18649,16 @@
       <c r="M187" s="2" t="inlineStr"/>
       <c r="N187" s="2" t="inlineStr"/>
       <c r="O187" s="2" t="inlineStr"/>
-      <c r="P187" s="2" t="inlineStr"/>
-      <c r="Q187" s="2" t="inlineStr"/>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>segreteria@montessori.it; info@montessori.it; corsi@montessori.it; redazione.editoriale@montessori.it; amministrazione@montessori.it; biblioteca@montessori.it; operanazionalemontessori@pec.it</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>+39 06 584865</t>
+        </is>
+      </c>
       <c r="R187" s="2" t="inlineStr">
         <is>
           <t>ONM is the official Montessori body in Italy, accrediting schools and materials and running training. Influencer with reach into hundreds of Case dei Bambini.</t>
@@ -17955,7 +18687,11 @@
       </c>
       <c r="X187" s="2" t="inlineStr"/>
       <c r="Y187" s="2" t="inlineStr"/>
-      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr">
+        <is>
+          <t>https://operanazionalemontessori.it/contatti/; https://www.mim.gov.it/en/opera-nazionale-montessori</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -18289,8 +19025,16 @@
       <c r="M191" s="2" t="inlineStr"/>
       <c r="N191" s="2" t="inlineStr"/>
       <c r="O191" s="2" t="inlineStr"/>
-      <c r="P191" s="2" t="inlineStr"/>
-      <c r="Q191" s="2" t="inlineStr"/>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>contact@ismonaco.com; admissions@ismonaco.com</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
+          <t>+377 93 25 68 20</t>
+        </is>
+      </c>
       <c r="R191" s="2" t="inlineStr">
         <is>
           <t>ISM is Monaco's international school with an early-years section serving a high-net-worth parent base. Decision maker not confirmed via search; verify on website/registry before outreach. Premium single site.</t>
@@ -18313,9 +19057,21 @@
           <t>other.json</t>
         </is>
       </c>
-      <c r="X191" s="2" t="inlineStr"/>
-      <c r="Y191" s="2" t="inlineStr"/>
-      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="X191" s="2" t="inlineStr">
+        <is>
+          <t>marine.tixier@ismonaco.com (Marine Tixier, Head of Admissions &amp; Public Relations); laetitia.lefebvre@ismonaco.com (Laetitia Lefebvre, Admissions &amp; Public Relations Assistant)</t>
+        </is>
+      </c>
+      <c r="Y191" s="2" t="inlineStr">
+        <is>
+          <t>first.last@ismonaco.com</t>
+        </is>
+      </c>
+      <c r="Z191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ismonaco.org/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -18365,8 +19121,16 @@
       <c r="M192" s="2" t="inlineStr"/>
       <c r="N192" s="2" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr"/>
-      <c r="P192" s="2" t="inlineStr"/>
-      <c r="Q192" s="2" t="inlineStr"/>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>info@chs.edu.mt</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
+          <t>+356 21374396</t>
+        </is>
+      </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
           <t>Chiswick House School (kindergarten and junior) feeds St Martin's College; one of Malta's largest private school groups.</t>
@@ -18395,7 +19159,11 @@
       </c>
       <c r="X192" s="2" t="inlineStr"/>
       <c r="Y192" s="2" t="inlineStr"/>
-      <c r="Z192" s="2" t="inlineStr"/>
+      <c r="Z192" s="2" t="inlineStr">
+        <is>
+          <t>https://chs.edu.mt/contact/; https://chs.edu.mt/our-staff/</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -18553,7 +19321,11 @@
           <t>Sander Claus, Martijn Witvoet (Raad van Toezicht)</t>
         </is>
       </c>
-      <c r="P194" s="2" t="inlineStr"/>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>klantrelaties@kion.nl; communicatie@kion.nl; stage@kion.nl</t>
+        </is>
+      </c>
       <c r="Q194" s="2" t="inlineStr"/>
       <c r="R194" s="2" t="inlineStr">
         <is>
@@ -18579,7 +19351,11 @@
       </c>
       <c r="X194" s="2" t="inlineStr"/>
       <c r="Y194" s="2" t="inlineStr"/>
-      <c r="Z194" s="2" t="inlineStr"/>
+      <c r="Z194" s="2" t="inlineStr">
+        <is>
+          <t>https://kion.nl/service-contact/contact/; https://www.kion.nl/organisatie</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -18633,8 +19409,16 @@
       </c>
       <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr"/>
-      <c r="P195" s="2" t="inlineStr"/>
-      <c r="Q195" s="2" t="inlineStr"/>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>info@kinderdam.nl; klantadvies@kinderdam.nl</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
+          <t>(010) 44 300 33</t>
+        </is>
+      </c>
       <c r="R195" s="2" t="inlineStr">
         <is>
           <t>KindeRdam runs about 100 KDV, peuteropvang and BSO locations in Rotterdam, Capelle, Krimpen and Nieuwerkerk aan den IJssel. Leadership not confirmed in this session.</t>
@@ -18663,7 +19447,11 @@
       </c>
       <c r="X195" s="2" t="inlineStr"/>
       <c r="Y195" s="2" t="inlineStr"/>
-      <c r="Z195" s="2" t="inlineStr"/>
+      <c r="Z195" s="2" t="inlineStr">
+        <is>
+          <t>https://kinderdam.nl/contact; https://www.kinderdam.nl/contact/klantadvies</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -18809,8 +19597,16 @@
       </c>
       <c r="N197" s="2" t="inlineStr"/>
       <c r="O197" s="2" t="inlineStr"/>
-      <c r="P197" s="2" t="inlineStr"/>
-      <c r="Q197" s="2" t="inlineStr"/>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>info@korein.nl</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
+          <t>+31 (0)40 294 89 89</t>
+        </is>
+      </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
           <t>Korein, founded 1991, is the dominant childcare provider in the Eindhoven Brainport region with 89 locations in Eindhoven alone and 110-186 in total. It employs 1,000-5,000 staff. Leadership not confirmed in this session.</t>
@@ -18839,7 +19635,11 @@
       </c>
       <c r="X197" s="2" t="inlineStr"/>
       <c r="Y197" s="2" t="inlineStr"/>
-      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.korein.nl/en/contact/contact; https://www.korein.nl/ontdek-meer/nieuws/martijn-arts-nieuwe-directeur-korein; https://www.zoominfo.com/pic/korein-kinderplein-bv/425347784</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -18897,8 +19697,16 @@
       </c>
       <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr"/>
-      <c r="P198" s="2" t="inlineStr"/>
-      <c r="Q198" s="2" t="inlineStr"/>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>info@waterland.nu</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
+          <t>+31 35 694 1680</t>
+        </is>
+      </c>
       <c r="R198" s="2" t="inlineStr">
         <is>
           <t>Waterland built Partou through buy-and-build, merged it with Onex's KidsFoundation (2019-2020) and in 2022 moved it into a dedicated socially responsible Dutch fund after Onex exited. It also backs Partou's UK expansion. Sector partner: Partou Group. Hooks: Waterland's model favours platform-wide systems; also active in German/Polish care sectors.</t>
@@ -18927,7 +19735,11 @@
       </c>
       <c r="X198" s="2" t="inlineStr"/>
       <c r="Y198" s="2" t="inlineStr"/>
-      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.waterlandpe.com/contact-us/; https://www.waterlandpe.com/office/bussum/; https://leadiq.com/c/waterland-private-equity/5a1d8abc240000240064d47b/email-format</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -19081,8 +19893,16 @@
       </c>
       <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr"/>
-      <c r="P200" s="2" t="inlineStr"/>
-      <c r="Q200" s="2" t="inlineStr"/>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>kontakt@espira.no</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
+          <t>+47 21 08 80 88</t>
+        </is>
+      </c>
       <c r="R200" s="2" t="inlineStr">
         <is>
           <t>Espira is AcadeMedia's Norwegian kindergarten chain, acquired in 2014, and the brand was exported to Germany in 2018 with a Scandinavian outdoor-oriented concept. It is among Norway's largest private barnehage operators alongside Læringsverkstedet/Dibber, Norlandia and FUS. Norway's political debate on private kindergarten profits and the 2025 Fagforbundet campaigns create compliance and transparency demands. Vendor not confirmed (Norwegian chains commonly use Kidplan, Vigilo or MyKid). Hooks: Nordic-German cross-selling within AcadeMedia's preschool segment.</t>
@@ -19109,9 +19929,21 @@
           <t>paneuro.json</t>
         </is>
       </c>
-      <c r="X200" s="2" t="inlineStr"/>
-      <c r="Y200" s="2" t="inlineStr"/>
-      <c r="Z200" s="2" t="inlineStr"/>
+      <c r="X200" s="2" t="inlineStr">
+        <is>
+          <t>kjersti.oppen@espira.no (Kjersti Oppen, Direktør for myndighetskontakt og kommunikasjon)</t>
+        </is>
+      </c>
+      <c r="Y200" s="2" t="inlineStr">
+        <is>
+          <t>first.last@domain</t>
+        </is>
+      </c>
+      <c r="Z200" s="2" t="inlineStr">
+        <is>
+          <t>https://espira.no/om-espira/kontakt-oss; https://espira.no/om-espira/for-pressen; https://espira.no/om-espira</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -19157,8 +19989,16 @@
       <c r="M201" s="2" t="inlineStr"/>
       <c r="N201" s="2" t="inlineStr"/>
       <c r="O201" s="2" t="inlineStr"/>
-      <c r="P201" s="2" t="inlineStr"/>
-      <c r="Q201" s="2" t="inlineStr"/>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>slettebakken@kidsabarnehager.no; erleveien@kidsabarnehager.no; ovresedal@kidsabarnehager.no</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
+          <t>55 20 76 60</t>
+        </is>
+      </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
           <t>Kidsa is Bergen's largest private kindergarten operator with 28 units, part of Norlandia's preschool division. Frequently recruiting daglig ledere for individual units (Brønndalen, Olsvikfjellet, Breistein, Vågedalen). Org.nr 996 154 041. Decision making largely via Norlandia Barnehagene (Kristin Voldsnes).</t>
@@ -19187,7 +20027,11 @@
       </c>
       <c r="X201" s="2" t="inlineStr"/>
       <c r="Y201" s="2" t="inlineStr"/>
-      <c r="Z201" s="2" t="inlineStr"/>
+      <c r="Z201" s="2" t="inlineStr">
+        <is>
+          <t>https://utdanning.no/bedrift/996154041/; https://www.bergen.kommune.no/omkommunen/avdelinger/kidsa-slettebakken?vis=kontakt</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -19237,8 +20081,16 @@
           <t>Kristina Andreassen - daglig leder, Fjordbyen barnehage (ULNA); Christine Gleditsch - daglig leder, ULNA Vang aktivitetsbarnehage (Hamar)</t>
         </is>
       </c>
-      <c r="P202" s="2" t="inlineStr"/>
-      <c r="Q202" s="2" t="inlineStr"/>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>post@ulna.no</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
+          <t>48003300</t>
+        </is>
+      </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
           <t>ULNA runs ~25 barnehager mostly in Eastern and Southern Norway, plus Fauske and Bergen. Several units use barnehage.no-hosted sites (Fjordbyen, Villa Snøringsmoen, Lekeklossen). Company LinkedIn page exists. Central CEO not confirmed by search.</t>
@@ -19265,9 +20117,21 @@
           <t>nordics.json</t>
         </is>
       </c>
-      <c r="X202" s="2" t="inlineStr"/>
-      <c r="Y202" s="2" t="inlineStr"/>
-      <c r="Z202" s="2" t="inlineStr"/>
+      <c r="X202" s="2" t="inlineStr">
+        <is>
+          <t>laila.haugen@ulna.no (Laila Haugen, Daglig leder, ULNA AS); linda.herdlever@ulna.no (Linda Herdlevær, Daglig leder, Lekeklossen Løvåsen); Linn.kaardal@ulna.no (Linn-Therese Kårdal Vonen, Daglig leder, Lekeklossen Storhammeren); niklas.bjerke@ulna.no (Niklas Bjerke, Fung. daglig leder, Gjerdrum friluftsbarnehage)</t>
+        </is>
+      </c>
+      <c r="Y202" s="2" t="inlineStr">
+        <is>
+          <t>first.last@ulna.no</t>
+        </is>
+      </c>
+      <c r="Z202" s="2" t="inlineStr">
+        <is>
+          <t>https://loevaasen.barnehage.no/Informasjon/Kontakt; https://lekeklossen.barnehage.no/; https://www.gjerdrum.kommune.no/tjenester/barnehage/barnehagene-i-gjerdrum/; https://www.proff.no/selskap/ulna-barnehagene/nordkisa/skoler-og-undervisning/IGBY3OX10KR</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -19425,8 +20289,16 @@
       </c>
       <c r="N204" s="2" t="inlineStr"/>
       <c r="O204" s="2" t="inlineStr"/>
-      <c r="P204" s="2" t="inlineStr"/>
-      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>akademia.reduta@gmail.com; akademiamarcholta@gmail.com; akademia.kurzei1@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>+48 506 943 931</t>
+        </is>
+      </c>
       <c r="R204" s="2" t="inlineStr">
         <is>
           <t>Akademia Małych Einsteinów is a Kraków network of small, family-style preschools and pre-school points founded by a preschool teacher and speech therapist. It runs at least three sites in the Prądnik Czerwony / Mistrzejowice districts and emphasises daily English with native speakers (TPR method). Registered as a sole proprietorship under Sabina Madej, who is also director, so one person holds all purchasing decisions.</t>
@@ -19453,7 +20325,7 @@
       <c r="Y204" s="2" t="inlineStr"/>
       <c r="Z204" s="2" t="inlineStr">
         <is>
-          <t>https://akademiamalycheinsteinow.pl/</t>
+          <t>https://przedszkole-akademia.pl/kontakt/; https://www.gowork.pl/akademia-malych-einsteinow-sabina-madej,22979565/dane-kontaktowe-firmy</t>
         </is>
       </c>
     </row>
@@ -19897,8 +20769,16 @@
       <c r="M209" s="2" t="inlineStr"/>
       <c r="N209" s="2" t="inlineStr"/>
       <c r="O209" s="2" t="inlineStr"/>
-      <c r="P209" s="2" t="inlineStr"/>
-      <c r="Q209" s="2" t="inlineStr"/>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>dyrektor@edukacjajutra.eu</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>+48 535 555 080</t>
+        </is>
+      </c>
       <c r="R209" s="2" t="inlineStr">
         <is>
           <t>Mały Einstein is a Gdynia language-and-music preschool group founded in 2013 with three preschool sites, a nursery and a primary school, based in the Pomeranian Science &amp; Technology Park. It is an IB PYP candidate school and teaches English immersively for ages 2.5–6. Notable independent operator in Tricity.</t>
@@ -19927,7 +20807,11 @@
       </c>
       <c r="X209" s="2" t="inlineStr"/>
       <c r="Y209" s="2" t="inlineStr"/>
-      <c r="Z209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr">
+        <is>
+          <t>https://panoramafirm.pl/pomorskie,,gdynia,al._zwyci%C4%99stwa,96_lok._98/niepubliczne_przedszkole_jezykowo_muzyczne_maly_einstein-zbeiky_rjr.html; https://rankingmalucha.pl/przedszkole/przedszkole-gdynia-niepubliczne-przedszkole-jezykowo-muzyczne-maly-einstein-p-120267</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -19981,8 +20865,16 @@
       </c>
       <c r="N210" s="2" t="inlineStr"/>
       <c r="O210" s="2" t="inlineStr"/>
-      <c r="P210" s="2" t="inlineStr"/>
-      <c r="Q210" s="2" t="inlineStr"/>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>british@thebritishschool.pl</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>+48 22 646 77 77</t>
+        </is>
+      </c>
       <c r="R210" s="2" t="inlineStr">
         <is>
           <t>The British School Warsaw is a Nord Anglia school with a dedicated Early Years Centre following the EYFS curriculum and running regular Early Years open days. Principal John Brett leads the school; procurement is largely group-level (Nord Anglia). Useful as a reference account rather than a direct buyer.</t>
@@ -20009,7 +20901,7 @@
       <c r="Y210" s="2" t="inlineStr"/>
       <c r="Z210" s="2" t="inlineStr">
         <is>
-          <t>https://www.nordangliaeducation.com/tbsw-warsaw; https://www.nordangliaeducation.com/tbsw-warsaw/about-us</t>
+          <t>https://www.nordangliaeducation.com/tbsw-warsaw/contact-us; https://www.nordangliaeducation.com/tbsw-warsaw/campus/early-years-centre</t>
         </is>
       </c>
     </row>
@@ -20249,8 +21141,16 @@
       <c r="M213" s="2" t="inlineStr"/>
       <c r="N213" s="2" t="inlineStr"/>
       <c r="O213" s="2" t="inlineStr"/>
-      <c r="P213" s="2" t="inlineStr"/>
-      <c r="Q213" s="2" t="inlineStr"/>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>geral@colegioefanor.pt; cl.efanor@escolas.min-edu.pt</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>+351 220110000</t>
+        </is>
+      </c>
       <c r="R213" s="2" t="inlineStr">
         <is>
           <t>Colégio Efanor, linked to the Azevedo family/Sonae, is a premium private school north of Porto with creche from 4 months through secondary. Strong investment capacity.</t>
@@ -20279,7 +21179,11 @@
       </c>
       <c r="X213" s="2" t="inlineStr"/>
       <c r="Y213" s="2" t="inlineStr"/>
-      <c r="Z213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.escolapp.pt/escola/colegio-efanor/; https://www.zoominfo.com/c/cole%CC%81gio-efanor/471952416</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -20329,7 +21233,11 @@
       <c r="M214" s="2" t="inlineStr"/>
       <c r="N214" s="2" t="inlineStr"/>
       <c r="O214" s="2" t="inlineStr"/>
-      <c r="P214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>head@stjulians.com</t>
+        </is>
+      </c>
       <c r="Q214" s="2" t="inlineStr"/>
       <c r="R214" s="2" t="inlineStr">
         <is>
@@ -20357,9 +21265,17 @@
           <t>south.json</t>
         </is>
       </c>
-      <c r="X214" s="2" t="inlineStr"/>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>head@stjulians.com (Paul J. Morgan, Head of School)</t>
+        </is>
+      </c>
       <c r="Y214" s="2" t="inlineStr"/>
-      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stjulians.com/contact/; https://www.stjulians.com/about-us/welcome-from-the-head/</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -20405,8 +21321,16 @@
       <c r="M215" s="2" t="inlineStr"/>
       <c r="N215" s="2" t="inlineStr"/>
       <c r="O215" s="2" t="inlineStr"/>
-      <c r="P215" s="2" t="inlineStr"/>
-      <c r="Q215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>secretaria.geral@ump.pt; comunicacao@ump.pt; misericordias@ump.pt; assembleiageral@ump.pt; assuntos.juridicos@ump.pt; dpo@ump.pt; jornal@ump.pt</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>+351 218 110 540</t>
+        </is>
+      </c>
       <c r="R215" s="2" t="inlineStr">
         <is>
           <t>UMP federates ~390 Misericórdias, hundreds of which run creches and pré-escolar under cooperation agreements with the state (Creche Feliz programme). It is an influencer/aggregator rather than direct operator, useful for framework partnerships.</t>
@@ -20435,7 +21359,11 @@
       </c>
       <c r="X215" s="2" t="inlineStr"/>
       <c r="Y215" s="2" t="inlineStr"/>
-      <c r="Z215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ump.pt/Home/uniao/contactos/; https://www.ump.pt/Home/uniao/aviso-de-privacidade-informacao-de-contacto/</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -20601,8 +21529,16 @@
           <t>Peter Wallebo - styrelseledamot</t>
         </is>
       </c>
-      <c r="P217" s="2" t="inlineStr"/>
-      <c r="Q217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>info@friluftsforskolor.se</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>08-471 99 44</t>
+        </is>
+      </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
           <t>Outdoor-pedagogy preschool chain with 11 units and ~70 staff (org.nr 556561-0887). VD not confirmed.</t>
@@ -20629,9 +21565,21 @@
           <t>nordics.json</t>
         </is>
       </c>
-      <c r="X217" s="2" t="inlineStr"/>
-      <c r="Y217" s="2" t="inlineStr"/>
-      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>yann@friluftsforskolor.se (Yann Nyman, Rektor, Frilufts förskolor Dungen); annika@friluftsforskolor.se (Annika Alfredsson Thörewik, Biträdande rektor, Förskolan Riddersborg)</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr">
+        <is>
+          <t>firstname@friluftsforskolor.se</t>
+        </is>
+      </c>
+      <c r="Z217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.friluftsforskolor.se/kontaktaoss; https://forskola.stockholm/hitta-forskola/forskola/frilufts-forskolor-dungen; https://forskola.stockholm/hitta-forskola/forskola/frilufts-forskolor-riddersborg</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -20677,8 +21625,16 @@
       <c r="M218" s="2" t="inlineStr"/>
       <c r="N218" s="2" t="inlineStr"/>
       <c r="O218" s="2" t="inlineStr"/>
-      <c r="P218" s="2" t="inlineStr"/>
-      <c r="Q218" s="2" t="inlineStr"/>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>info@inspira-fos.se</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>08-684 468 00</t>
+        </is>
+      </c>
       <c r="R218" s="2" t="inlineStr">
         <is>
           <t>Inspira is one of Atvexa's largest subsidiaries with 39 förskolor and several schools in Stockholm county; awarded best workplace (Alecta). VD not confirmed by search.</t>
@@ -20707,7 +21663,11 @@
       </c>
       <c r="X218" s="2" t="inlineStr"/>
       <c r="Y218" s="2" t="inlineStr"/>
-      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr">
+        <is>
+          <t>http://www.inspira-fos.se/runborg/kontakt/; https://insynsverige.se/documentHandler.ashx?did=1721017</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -20849,8 +21809,16 @@
       <c r="M220" s="2" t="inlineStr"/>
       <c r="N220" s="2" t="inlineStr"/>
       <c r="O220" s="2" t="inlineStr"/>
-      <c r="P220" s="2" t="inlineStr"/>
-      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>info@bilfengroup.com</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>444 99 42</t>
+        </is>
+      </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
           <t>Bilfen runs private K-12 campuses in Istanbul with anaokulu sections. Decision maker not confirmed via search; verify on website/registry before outreach. Mid-large target.</t>
@@ -20875,7 +21843,11 @@
       </c>
       <c r="X220" s="2" t="inlineStr"/>
       <c r="Y220" s="2" t="inlineStr"/>
-      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr">
+        <is>
+          <t>https://bilfen.com/tr/iletisim; https://bilfen.com/tr/kurumsal/yonetim-kadrosu; https://www.bilfengroup.com/tr/iletisim</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -20925,7 +21897,11 @@
       <c r="M221" s="2" t="inlineStr"/>
       <c r="N221" s="2" t="inlineStr"/>
       <c r="O221" s="2" t="inlineStr"/>
-      <c r="P221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>bilgaziantep@bilkoleji.com.tr; bilesenyurt@bilkoleji.com.tr; bilaydin@bilkoleji.com.tr; bilbahcelievler@bilkoleji.com.tr; bilpendik@bilkoleji.com.tr; bilizmir@bilkoleji.com.tr</t>
+        </is>
+      </c>
       <c r="Q221" s="2" t="inlineStr"/>
       <c r="R221" s="2" t="inlineStr">
         <is>
@@ -20951,7 +21927,11 @@
       </c>
       <c r="X221" s="2" t="inlineStr"/>
       <c r="Y221" s="2" t="inlineStr"/>
-      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dijikolej.com/profile/935; https://dijikolej.com/profile/934</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -21027,7 +22007,11 @@
       </c>
       <c r="X222" s="2" t="inlineStr"/>
       <c r="Y222" s="2" t="inlineStr"/>
-      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.finalokullari.com.tr/bize-ulasin</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -21074,7 +22058,11 @@
       <c r="N223" s="2" t="inlineStr"/>
       <c r="O223" s="2" t="inlineStr"/>
       <c r="P223" s="2" t="inlineStr"/>
-      <c r="Q223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>0212 671 92 00</t>
+        </is>
+      </c>
       <c r="R223" s="2" t="inlineStr">
         <is>
           <t>KANZ Kindergarten is marketed as Turkey's largest baby-and-children brand operating kindergartens with 200-500 branches via master franchise. Figures are self-reported. Decision maker not confirmed via search; verify on website/registry before outreach. Potentially the largest pure kindergarten franchise in Turkey.</t>
@@ -21099,7 +22087,11 @@
       </c>
       <c r="X223" s="2" t="inlineStr"/>
       <c r="Y223" s="2" t="inlineStr"/>
-      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr">
+        <is>
+          <t>https://kanz.com.tr/i%CC%87leti%C5%9Fim; https://www.kobivadisi.com/ilan/kanz-kindergarten-anaokullari-master-franchise-i761; https://kindergartenacademy.com.tr/iletisim/</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -21145,8 +22137,16 @@
       <c r="M224" s="2" t="inlineStr"/>
       <c r="N224" s="2" t="inlineStr"/>
       <c r="O224" s="2" t="inlineStr"/>
-      <c r="P224" s="2" t="inlineStr"/>
-      <c r="Q224" s="2" t="inlineStr"/>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>info@kidseducationacademy.com; atasehir@kidseducationacademy.com; gop@kidseducationacademy.com; beylikduzu@kidseducationacademy.com; beykent@kidseducationacademy.com</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>+90 533 382 62 39 (HQ); Ataşehir +90 216 456 05 04</t>
+        </is>
+      </c>
       <c r="R224" s="2" t="inlineStr">
         <is>
           <t>Kids Education Academy is a Turkish anaokulu franchise with 20-40 active branches and a Gold Brand award, actively recruiting franchisees. Decision maker not confirmed via search; verify on website/registry before outreach. Pure-play kindergarten chain, good fit.</t>
@@ -21171,7 +22171,11 @@
       </c>
       <c r="X224" s="2" t="inlineStr"/>
       <c r="Y224" s="2" t="inlineStr"/>
-      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidseducationacademy.com/iletisim; https://www.kidseducationacademy.com/istanbul-beylikduzu</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -21221,8 +22225,16 @@
       <c r="M225" s="2" t="inlineStr"/>
       <c r="N225" s="2" t="inlineStr"/>
       <c r="O225" s="2" t="inlineStr"/>
-      <c r="P225" s="2" t="inlineStr"/>
-      <c r="Q225" s="2" t="inlineStr"/>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>mef@mef.k12.tr; mefkayitbirimi@mef.k12.tr</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>+90 212 362 26 33</t>
+        </is>
+      </c>
       <c r="R225" s="2" t="inlineStr">
         <is>
           <t>MEF Okulları is a premium private K-12 group in Istanbul with kindergarten sections. Decision maker not confirmed via search; verify on website/registry before outreach.</t>
@@ -21247,7 +22259,11 @@
       </c>
       <c r="X225" s="2" t="inlineStr"/>
       <c r="Y225" s="2" t="inlineStr"/>
-      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mef.k12.tr/iletisim/; https://www.mef.k12.tr/kayit-admissions/mef-anaokulu-kayit-sayfasi-mef-kindergarten-admissions-page/</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -21297,8 +22313,16 @@
       <c r="M226" s="2" t="inlineStr"/>
       <c r="N226" s="2" t="inlineStr"/>
       <c r="O226" s="2" t="inlineStr"/>
-      <c r="P226" s="2" t="inlineStr"/>
-      <c r="Q226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>info@ted.org.tr</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>+90 312 939 50 00</t>
+        </is>
+      </c>
       <c r="R226" s="2" t="inlineStr">
         <is>
           <t>TED operates a nationwide network of schools including anaokulu sections, with several Istanbul campuses. Non-profit association ownership. Decision maker not confirmed via search; verify on website/registry before outreach. Large multi-site target.</t>
@@ -21323,7 +22347,11 @@
       </c>
       <c r="X226" s="2" t="inlineStr"/>
       <c r="Y226" s="2" t="inlineStr"/>
-      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr">
+        <is>
+          <t>https://form.ted.org.tr/iletisim/; https://ted.org.tr/</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -21399,7 +22427,11 @@
       </c>
       <c r="X227" s="2" t="inlineStr"/>
       <c r="Y227" s="2" t="inlineStr"/>
-      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ibo.org/en/school/052334/; https://www.searchassociates.com/schools/albania/albanian-college-tirana-i/</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -21449,7 +22481,11 @@
       <c r="M228" s="2" t="inlineStr"/>
       <c r="N228" s="2" t="inlineStr"/>
       <c r="O228" s="2" t="inlineStr"/>
-      <c r="P228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>tirana@qsi.org; admissons@tirana.qsi.org</t>
+        </is>
+      </c>
       <c r="Q228" s="2" t="inlineStr"/>
       <c r="R228" s="2" t="inlineStr">
         <is>
@@ -21473,9 +22509,21 @@
           <t>other.json</t>
         </is>
       </c>
-      <c r="X228" s="2" t="inlineStr"/>
-      <c r="Y228" s="2" t="inlineStr"/>
-      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>jon-mudd@qsi.org (Jon Mudd, Director); meredith-hutson@tirana.qsi.org (Meredith Beasley-Hutson, Elementary Director of Instruction); egla-lila@tirana.qsi.org (Egla Lila, Admissions Coordinator/Registrar)</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr">
+        <is>
+          <t>first-last@tirana.qsi.org</t>
+        </is>
+      </c>
+      <c r="Z228" s="2" t="inlineStr">
+        <is>
+          <t>https://tirana.qsi.org/admissions/admissions-process; https://www.state.gov/tirana-international-school-special-needs-profile</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -21521,8 +22569,16 @@
       <c r="M229" s="2" t="inlineStr"/>
       <c r="N229" s="2" t="inlineStr"/>
       <c r="O229" s="2" t="inlineStr"/>
-      <c r="P229" s="2" t="inlineStr"/>
-      <c r="Q229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>office@caritas-wien.at</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 87812-0</t>
+        </is>
+      </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
           <t>Caritas Vienna runs kindergartens with inclusion focus. Hooks: church-group.</t>
@@ -21555,7 +22611,11 @@
       </c>
       <c r="X229" s="2" t="inlineStr"/>
       <c r="Y229" s="2" t="inlineStr"/>
-      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caritas-wien.at/impressum/; https://www.caritas-wien.at/ueber-uns/ueber-die-caritas-wien/kontakt/</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -21601,8 +22661,16 @@
       <c r="M230" s="2" t="inlineStr"/>
       <c r="N230" s="2" t="inlineStr"/>
       <c r="O230" s="2" t="inlineStr"/>
-      <c r="P230" s="2" t="inlineStr"/>
-      <c r="Q230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>bildung@diakonie.at</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 402 67 54</t>
+        </is>
+      </c>
       <c r="R230" s="2" t="inlineStr">
         <is>
           <t>Protestant Diakonie's education arm in eastern Austria. Hooks: church-group procurement.</t>
@@ -21635,7 +22703,11 @@
       </c>
       <c r="X230" s="2" t="inlineStr"/>
       <c r="Y230" s="2" t="inlineStr"/>
-      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lutherschule.at/impressum; https://www.evgym.at/impressum; https://evang.at/adressen/diakonie-bildung/</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -21681,8 +22753,16 @@
       <c r="M231" s="2" t="inlineStr"/>
       <c r="N231" s="2" t="inlineStr"/>
       <c r="O231" s="2" t="inlineStr"/>
-      <c r="P231" s="2" t="inlineStr"/>
-      <c r="Q231" s="2" t="inlineStr"/>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>office@diakoniewerk.at</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>+43 7235 65 505</t>
+        </is>
+      </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
           <t>Protestant social enterprise with childcare facilities. Low priority.</t>
@@ -21715,7 +22795,11 @@
       </c>
       <c r="X231" s="2" t="inlineStr"/>
       <c r="Y231" s="2" t="inlineStr"/>
-      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoservice.sozialministerium.gv.at/detail/evangelisches-diakoniewerk-gallneukirchen; https://shop.diakoniewerk.at/impressum</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -21761,8 +22845,16 @@
       <c r="M232" s="2" t="inlineStr"/>
       <c r="N232" s="2" t="inlineStr"/>
       <c r="O232" s="2" t="inlineStr"/>
-      <c r="P232" s="2" t="inlineStr"/>
-      <c r="Q232" s="2" t="inlineStr"/>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>office@kinderfreunde-steiermark.at</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>+43 316 82 55 12</t>
+        </is>
+      </c>
       <c r="R232" s="2" t="inlineStr">
         <is>
           <t>Regional Kinderfreunde organisations with own Geschäftsführung. Hooks: regional decisions.</t>
@@ -21795,7 +22887,11 @@
       </c>
       <c r="X232" s="2" t="inlineStr"/>
       <c r="Y232" s="2" t="inlineStr"/>
-      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr">
+        <is>
+          <t>https://kinderfreunde.at/impressum/www-kinderfreunde-steiermark-at; https://kinderfreunde.at/ueber-uns/team?fwhid=13</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -21842,7 +22938,11 @@
       <c r="N233" s="2" t="inlineStr"/>
       <c r="O233" s="2" t="inlineStr"/>
       <c r="P233" s="2" t="inlineStr"/>
-      <c r="Q233" s="2" t="inlineStr"/>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>+43 1 4066144</t>
+        </is>
+      </c>
       <c r="R233" s="2" t="inlineStr">
         <is>
           <t>Long-established private Vienna kindergarten network. Hooks: multi-site admin.</t>
@@ -21875,7 +22975,11 @@
       </c>
       <c r="X233" s="2" t="inlineStr"/>
       <c r="Y233" s="2" t="inlineStr"/>
-      <c r="Z233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.familieundberuf.at/unternehmen/kindergarten-alt-wien-muku; https://www.justiz.gv.at/file/2c92fd15896e3d9c018ad60c40a64320.de.0/Presseinformation%20Causa%20Gemeinn%C3%BCtziger%20Kindergarten%20Alt%20Wien.pdf?forcedownload=true</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -21921,8 +23025,16 @@
       <c r="M234" s="2" t="inlineStr"/>
       <c r="N234" s="2" t="inlineStr"/>
       <c r="O234" s="2" t="inlineStr"/>
-      <c r="P234" s="2" t="inlineStr"/>
-      <c r="Q234" s="2" t="inlineStr"/>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>rundumgeburt@nanaya.at</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>01 / 523 17 11</t>
+        </is>
+      </c>
       <c r="R234" s="2" t="inlineStr">
         <is>
           <t>Vienna private kindergarten chain with bilingual concept. Hooks: parent communication.</t>
@@ -21955,7 +23067,11 @@
       </c>
       <c r="X234" s="2" t="inlineStr"/>
       <c r="Y234" s="2" t="inlineStr"/>
-      <c r="Z234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nanaya.at/impressum</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -22001,8 +23117,16 @@
       <c r="M235" s="2" t="inlineStr"/>
       <c r="N235" s="2" t="inlineStr"/>
       <c r="O235" s="2" t="inlineStr"/>
-      <c r="P235" s="2" t="inlineStr"/>
-      <c r="Q235" s="2" t="inlineStr"/>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>office@volkshilfe-ooe.at</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>0732 / 3405 - 0</t>
+        </is>
+      </c>
       <c r="R235" s="2" t="inlineStr">
         <is>
           <t>Volkshilfe runs childcare mainly in Upper Austria and Vienna. Hooks: regional GF.</t>
@@ -22035,7 +23159,11 @@
       </c>
       <c r="X235" s="2" t="inlineStr"/>
       <c r="Y235" s="2" t="inlineStr"/>
-      <c r="Z235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.volkshilfe-ooe.at/; https://www.volkshilfe-ooe.at/ueber-uns/wo-du-uns-findest/</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -22081,8 +23209,16 @@
       </c>
       <c r="N236" s="2" t="inlineStr"/>
       <c r="O236" s="2" t="inlineStr"/>
-      <c r="P236" s="2" t="inlineStr"/>
-      <c r="Q236" s="2" t="inlineStr"/>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>ais@ais-antwerp.be; admissions@ais-antwerp.be</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>+32 3 543 93 26</t>
+        </is>
+      </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
           <t>Antwerp International School – Early Childhood: international school early years. Included as a notable independent or international early-years provider in BE. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -22111,7 +23247,11 @@
       </c>
       <c r="X236" s="2" t="inlineStr"/>
       <c r="Y236" s="2" t="inlineStr"/>
-      <c r="Z236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ais-antwerp.be/contact/; https://www.ais-antwerp.be/admissions/faq/</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -22157,8 +23297,16 @@
       </c>
       <c r="N237" s="2" t="inlineStr"/>
       <c r="O237" s="2" t="inlineStr"/>
-      <c r="P237" s="2" t="inlineStr"/>
-      <c r="Q237" s="2" t="inlineStr"/>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>info@beps.com; admissions@beps.com</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>+32 (0) 2 648 43 11</t>
+        </is>
+      </c>
       <c r="R237" s="2" t="inlineStr">
         <is>
           <t>BEPS International School – Early Years: IB PYP school from age 2.5. Included as a notable independent or international early-years provider in BE. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -22187,7 +23335,11 @@
       </c>
       <c r="X237" s="2" t="inlineStr"/>
       <c r="Y237" s="2" t="inlineStr"/>
-      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beps.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -22233,8 +23385,16 @@
       </c>
       <c r="N238" s="2" t="inlineStr"/>
       <c r="O238" s="2" t="inlineStr"/>
-      <c r="P238" s="2" t="inlineStr"/>
-      <c r="Q238" s="2" t="inlineStr"/>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>kinderopvang@babilou.com; belgium@babilou.com</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>02 687 87 21</t>
+        </is>
+      </c>
       <c r="R238" s="2" t="inlineStr">
         <is>
           <t>Babilou Belgium: Belgian arm of Babilou Family with crèches in Brussels and Wallonia. Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22263,7 +23423,11 @@
       </c>
       <c r="X238" s="2" t="inlineStr"/>
       <c r="Y238" s="2" t="inlineStr"/>
-      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.babilou.be/en/contact/; https://expatsinbrussels.be/en/places/babilou-belgium</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -22385,8 +23549,16 @@
       </c>
       <c r="N240" s="2" t="inlineStr"/>
       <c r="O240" s="2" t="inlineStr"/>
-      <c r="P240" s="2" t="inlineStr"/>
-      <c r="Q240" s="2" t="inlineStr"/>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>petite.enfance-het.jonge.kind@brucity.be</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>0800 17 071</t>
+        </is>
+      </c>
       <c r="R240" s="2" t="inlineStr">
         <is>
           <t>Crèches de la Ville de Bruxelles: municipal crèches of the City of Brussels. Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22415,7 +23587,11 @@
       </c>
       <c r="X240" s="2" t="inlineStr"/>
       <c r="Y240" s="2" t="inlineStr"/>
-      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr">
+        <is>
+          <t>https://creches.brussels.be/fr/contact; https://www.bruxelles.be/directory-2169</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -22461,8 +23637,16 @@
       </c>
       <c r="N241" s="2" t="inlineStr"/>
       <c r="O241" s="2" t="inlineStr"/>
-      <c r="P241" s="2" t="inlineStr"/>
-      <c r="Q241" s="2" t="inlineStr"/>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>aufnahme@idsb.eu</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>+32 2 686 16 55</t>
+        </is>
+      </c>
       <c r="R241" s="2" t="inlineStr">
         <is>
           <t>Deutsche Schule Brüssel / Internationale Deutsche Schule Brüssel – Kindergarten: German-curriculum Kindergarten. Included as a notable independent or international early-years provider in BE. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -22491,7 +23675,11 @@
       </c>
       <c r="X241" s="2" t="inlineStr"/>
       <c r="Y241" s="2" t="inlineStr"/>
-      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr">
+        <is>
+          <t>https://deutscherkindergarten.org/kita/internationale-deutsche-schule-bruessel/; https://www.idsb.eu/</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -22537,8 +23725,16 @@
       </c>
       <c r="N242" s="2" t="inlineStr"/>
       <c r="O242" s="2" t="inlineStr"/>
-      <c r="P242" s="2" t="inlineStr"/>
-      <c r="Q242" s="2" t="inlineStr"/>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>info@felies.be</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>02/882.16.38</t>
+        </is>
+      </c>
       <c r="R242" s="2" t="inlineStr">
         <is>
           <t>Felies vzw: Flemish non-profit organiser of crèches (Felies, ex-Kinderdagverblijven of the Vlaamse Gemeenschap network). Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22567,7 +23763,11 @@
       </c>
       <c r="X242" s="2" t="inlineStr"/>
       <c r="Y242" s="2" t="inlineStr"/>
-      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr">
+        <is>
+          <t>https://felies.be/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -22613,8 +23813,16 @@
       </c>
       <c r="N243" s="2" t="inlineStr"/>
       <c r="O243" s="2" t="inlineStr"/>
-      <c r="P243" s="2" t="inlineStr"/>
-      <c r="Q243" s="2" t="inlineStr"/>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>DVO.wommelgem@samenferm.be; dvo.bilzen@samenferm.be</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>078 480 483</t>
+        </is>
+      </c>
       <c r="R243" s="2" t="inlineStr">
         <is>
           <t>Ferm Kinderopvang (ex Landelijke Kinderopvang): largest Flemish non-profit childcare organiser (kinderdagverblijven, gastouders, buitenschoolse opvang), part of Ferm (ex KVLV). Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22643,7 +23851,11 @@
       </c>
       <c r="X243" s="2" t="inlineStr"/>
       <c r="Y243" s="2" t="inlineStr"/>
-      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samenferm.be/contact; https://be.linkedin.com/company/samenferm; https://www.wommelgem.be/ferm-kinderopvang</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -22689,8 +23901,16 @@
       </c>
       <c r="N244" s="2" t="inlineStr"/>
       <c r="O244" s="2" t="inlineStr"/>
-      <c r="P244" s="2" t="inlineStr"/>
-      <c r="Q244" s="2" t="inlineStr"/>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>steralgemeen.zuid@infano.be; hr@infano.be</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>0484 58 07 27</t>
+        </is>
+      </c>
       <c r="R244" s="2" t="inlineStr">
         <is>
           <t>Infano vzw: large Flemish non-profit organiser of kinderdagverblijven and BKO. Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22719,7 +23939,11 @@
       </c>
       <c r="X244" s="2" t="inlineStr"/>
       <c r="Y244" s="2" t="inlineStr"/>
-      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.halle.be/menu/kinderopvang-en-onderwijs/kinderopvang/kinderopvang-3-12-jaar/infano-vzw; https://www.infano.be/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -22765,7 +23989,11 @@
       </c>
       <c r="N245" s="2" t="inlineStr"/>
       <c r="O245" s="2" t="inlineStr"/>
-      <c r="P245" s="2" t="inlineStr"/>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>admissions@isb.be</t>
+        </is>
+      </c>
       <c r="Q245" s="2" t="inlineStr"/>
       <c r="R245" s="2" t="inlineStr">
         <is>
@@ -22795,7 +24023,11 @@
       </c>
       <c r="X245" s="2" t="inlineStr"/>
       <c r="Y245" s="2" t="inlineStr"/>
-      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.isb.be/portal-help; https://2009-2017.state.gov/m/a/os/219843.htm</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -22841,8 +24073,16 @@
       </c>
       <c r="N246" s="2" t="inlineStr"/>
       <c r="O246" s="2" t="inlineStr"/>
-      <c r="P246" s="2" t="inlineStr"/>
-      <c r="Q246" s="2" t="inlineStr"/>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>info@vdkomma.be; pto@vdkomma.be; directeur@vdkomma.be</t>
+        </is>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>+32 15 71 50 55</t>
+        </is>
+      </c>
       <c r="R246" s="2" t="inlineStr">
         <is>
           <t>Komma vzw (kinderopvang): Flemish non-profit childcare organiser. Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22871,7 +24111,11 @@
       </c>
       <c r="X246" s="2" t="inlineStr"/>
       <c r="Y246" s="2" t="inlineStr"/>
-      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vdkomma.be/over-ons; https://www.zoominfo.com/c/komma-vzw/430038629</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -22917,8 +24161,16 @@
       </c>
       <c r="N247" s="2" t="inlineStr"/>
       <c r="O247" s="2" t="inlineStr"/>
-      <c r="P247" s="2" t="inlineStr"/>
-      <c r="Q247" s="2" t="inlineStr"/>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>creche.agimont@liege.be; creche.amercoeur@liege.be; creche.hocheporte@liege.be; creche.opera1@liege.be; creche.thieraliege@liege.be</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>04/238 53 29</t>
+        </is>
+      </c>
       <c r="R247" s="2" t="inlineStr">
         <is>
           <t>Le Lion / ONE-subsidised crèche networks (Province de Liège / Intercommunales): public inter-communal crèche operators in Wallonia (e.g., ISOSL, CPAS crèches). Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -22947,7 +24199,11 @@
       </c>
       <c r="X247" s="2" t="inlineStr"/>
       <c r="Y247" s="2" t="inlineStr"/>
-      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr">
+        <is>
+          <t>https://my.one.be/milieu-accueil/3121; https://my.one.be/milieu-accueil/3108; https://my.one.be/milieu-accueil/267791; https://www.liege.be/fr/vie-communale/services-communaux/enfance/creches-communales</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -23019,7 +24275,11 @@
       </c>
       <c r="X248" s="2" t="inlineStr"/>
       <c r="Y248" s="2" t="inlineStr"/>
-      <c r="Z248" s="2" t="inlineStr"/>
+      <c r="Z248" s="2" t="inlineStr">
+        <is>
+          <t>https://my.one.be/milieu-accueil/7322; https://aupetitbonheurottignies.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -23065,7 +24325,11 @@
       </c>
       <c r="N249" s="2" t="inlineStr"/>
       <c r="O249" s="2" t="inlineStr"/>
-      <c r="P249" s="2" t="inlineStr"/>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>familles@lpcr.fr</t>
+        </is>
+      </c>
       <c r="Q249" s="2" t="inlineStr"/>
       <c r="R249" s="2" t="inlineStr">
         <is>
@@ -23095,7 +24359,11 @@
       </c>
       <c r="X249" s="2" t="inlineStr"/>
       <c r="Y249" s="2" t="inlineStr"/>
-      <c r="Z249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lpcr.fr/parents/contact-parent/; https://www.lpcr.fr/contact-partenaire/</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -23141,7 +24409,11 @@
       </c>
       <c r="N250" s="2" t="inlineStr"/>
       <c r="O250" s="2" t="inlineStr"/>
-      <c r="P250" s="2" t="inlineStr"/>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>creche.lespetitspas@brucity.be; lespetitspas@troisponts.be</t>
+        </is>
+      </c>
       <c r="Q250" s="2" t="inlineStr"/>
       <c r="R250" s="2" t="inlineStr">
         <is>
@@ -23171,7 +24443,11 @@
       </c>
       <c r="X250" s="2" t="inlineStr"/>
       <c r="Y250" s="2" t="inlineStr"/>
-      <c r="Z250" s="2" t="inlineStr"/>
+      <c r="Z250" s="2" t="inlineStr">
+        <is>
+          <t>https://creches.brussels.be/nos-milieux-daccueil/les-petits-pas; https://my.one.be/milieu-accueil/6463</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -23217,8 +24493,16 @@
       </c>
       <c r="N251" s="2" t="inlineStr"/>
       <c r="O251" s="2" t="inlineStr"/>
-      <c r="P251" s="2" t="inlineStr"/>
-      <c r="Q251" s="2" t="inlineStr"/>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>new@littlegreenhouse.ch; gland@littlegreenhouse.ch; versoix@littlegreenhouse.ch; perly@littlegreenhouse.ch</t>
+        </is>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>+41 22 364 45 50</t>
+        </is>
+      </c>
       <c r="R251" s="2" t="inlineStr">
         <is>
           <t>Little Green House: bilingual private crèche group in Brussels (verify Belgian presence vs Luxembourg). Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -23245,9 +24529,17 @@
           <t>fr_benelux.json</t>
         </is>
       </c>
-      <c r="X251" s="2" t="inlineStr"/>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>new@littlegreenhouse.ch (Barbara Lax, Founder)</t>
+        </is>
+      </c>
       <c r="Y251" s="2" t="inlineStr"/>
-      <c r="Z251" s="2" t="inlineStr"/>
+      <c r="Z251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlegreenhouse.ch/contact/; https://www.zoominfo.com/c/little-green-house/425064736</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -23293,8 +24585,16 @@
       </c>
       <c r="N252" s="2" t="inlineStr"/>
       <c r="O252" s="2" t="inlineStr"/>
-      <c r="P252" s="2" t="inlineStr"/>
-      <c r="Q252" s="2" t="inlineStr"/>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>accueil@lyceefrancais.be; accueil.maternelle@lyceefrancais.be</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>+32 2 374 58 78; maternelle 02 379 08 42</t>
+        </is>
+      </c>
       <c r="R252" s="2" t="inlineStr">
         <is>
           <t>Lycée Français Vauban / Lycée français de Bruxelles Jean Monnet – maternelle: AEFE French lycée with maternelle. Included as a notable independent or international early-years provider in BE. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -23321,9 +24621,21 @@
           <t>fr_benelux.json</t>
         </is>
       </c>
-      <c r="X252" s="2" t="inlineStr"/>
-      <c r="Y252" s="2" t="inlineStr"/>
-      <c r="Z252" s="2" t="inlineStr"/>
+      <c r="X252" s="2" t="inlineStr">
+        <is>
+          <t>franck.bis@lyceefrancais.be (Franck Bis, Directeur maternelle et CP/CE1)</t>
+        </is>
+      </c>
+      <c r="Y252" s="2" t="inlineStr">
+        <is>
+          <t>first.last@lyceefrancais.be</t>
+        </is>
+      </c>
+      <c r="Z252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lyceefrancais-jmonnet.be/content/vos-contacts</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -23365,8 +24677,16 @@
       </c>
       <c r="N253" s="2" t="inlineStr"/>
       <c r="O253" s="2" t="inlineStr"/>
-      <c r="P253" s="2" t="inlineStr"/>
-      <c r="Q253" s="2" t="inlineStr"/>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>info@montessoribrussels.org</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>+32 27336355</t>
+        </is>
+      </c>
       <c r="R253" s="2" t="inlineStr">
         <is>
           <t>Montessori House Brussels: independent Montessori nursery (verify). Included as a notable independent or international early-years provider in BE. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -23395,7 +24715,11 @@
       </c>
       <c r="X253" s="2" t="inlineStr"/>
       <c r="Y253" s="2" t="inlineStr"/>
-      <c r="Z253" s="2" t="inlineStr"/>
+      <c r="Z253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montessoribrussels.org/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -23589,7 +24913,11 @@
       </c>
       <c r="N256" s="2" t="inlineStr"/>
       <c r="O256" s="2" t="inlineStr"/>
-      <c r="P256" s="2" t="inlineStr"/>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>groepsopvang@antwerpen.be; regie.kinderopvang@antwerpen.be; contactpuntkinderopvang@antwerpen.be; Kinderopvang.Klantendienst@antwerpen.be</t>
+        </is>
+      </c>
       <c r="Q256" s="2" t="inlineStr"/>
       <c r="R256" s="2" t="inlineStr">
         <is>
@@ -23619,7 +24947,11 @@
       </c>
       <c r="X256" s="2" t="inlineStr"/>
       <c r="Y256" s="2" t="inlineStr"/>
-      <c r="Z256" s="2" t="inlineStr"/>
+      <c r="Z256" s="2" t="inlineStr">
+        <is>
+          <t>https://antwerpen.be/nl/overzicht/stedelijke-kinderopvang/contact/contacteer-stedelijke-kinderopvang-antwerpen; https://www.antwerpen.be/contact/regie-kinderopvang</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -23665,8 +24997,16 @@
       </c>
       <c r="N257" s="2" t="inlineStr"/>
       <c r="O257" s="2" t="inlineStr"/>
-      <c r="P257" s="2" t="inlineStr"/>
-      <c r="Q257" s="2" t="inlineStr"/>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>dienst.kinderopvang@stad.gent; kinderdagverblijven@stad.gent; buitenschoolse.kinderopvang@stad.gent; jobs.kinderopvang@stad.gent; kindfacturatie@stad.gent</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>+32 9 268 20 80</t>
+        </is>
+      </c>
       <c r="R257" s="2" t="inlineStr">
         <is>
           <t>Stad Gent Kinderopvang: municipal crèche network of the City of Ghent. Belgian childcare is split between Flanders (Opgroeien / Kind en Gezin licensing, vergunde kinderopvang) and Wallonia-Brussels (ONE). Location counts, ownership and leadership could not be confirmed in this session because the web-search budget was exhausted; validate via the Opgroeien and ONE public registers and the Belgian KBO/BCE company register (Moniteur belge for board members).</t>
@@ -23695,7 +25035,11 @@
       </c>
       <c r="X257" s="2" t="inlineStr"/>
       <c r="Y257" s="2" t="inlineStr"/>
-      <c r="Z257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr">
+        <is>
+          <t>https://stad.gent/en/opening-hours-addresses/dienst-kinderopvang-stad-gent; https://stad.gent/nl/kinderopvang-onderwijs/kinderopvang/kinderdagverblijven-stad-gent; https://jobs.gent.be/kinderopvang</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -23771,7 +25115,11 @@
       </c>
       <c r="X258" s="2" t="inlineStr"/>
       <c r="Y258" s="2" t="inlineStr"/>
-      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr">
+        <is>
+          <t>https://wombat.be/contact; https://serviceswombat.com/contact-wombat/</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -23813,7 +25161,11 @@
       <c r="M259" s="2" t="inlineStr"/>
       <c r="N259" s="2" t="inlineStr"/>
       <c r="O259" s="2" t="inlineStr"/>
-      <c r="P259" s="2" t="inlineStr"/>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>admissions@aas-sofia.org</t>
+        </is>
+      </c>
       <c r="Q259" s="2" t="inlineStr"/>
       <c r="R259" s="2" t="inlineStr">
         <is>
@@ -23841,9 +25193,21 @@
           <t>cee.json</t>
         </is>
       </c>
-      <c r="X259" s="2" t="inlineStr"/>
-      <c r="Y259" s="2" t="inlineStr"/>
-      <c r="Z259" s="2" t="inlineStr"/>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>jvillers@aas-sofia.org (Julie Villers, Elementary School Principal)</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr">
+        <is>
+          <t>flast@aas-sofia.org</t>
+        </is>
+      </c>
+      <c r="Z259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aas-sofia.org/discover/leadership; https://www.aas-sofia.org/discover/contact-us; https://www.aas-sofia.org/connect/directory</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -23885,8 +25249,16 @@
       <c r="M260" s="2" t="inlineStr"/>
       <c r="N260" s="2" t="inlineStr"/>
       <c r="O260" s="2" t="inlineStr"/>
-      <c r="P260" s="2" t="inlineStr"/>
-      <c r="Q260" s="2" t="inlineStr"/>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>office@bssofia.bg</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>+359 886 510 510</t>
+        </is>
+      </c>
       <c r="R260" s="2" t="inlineStr">
         <is>
           <t>British School of Sofia runs a kindergarten and British-curriculum school. Management not verified this session.</t>
@@ -23915,7 +25287,11 @@
       </c>
       <c r="X260" s="2" t="inlineStr"/>
       <c r="Y260" s="2" t="inlineStr"/>
-      <c r="Z260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bssofia.bg/contacts/; https://www.bssofia.bg/british-kindergarten/</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -23957,7 +25333,11 @@
       <c r="M261" s="2" t="inlineStr"/>
       <c r="N261" s="2" t="inlineStr"/>
       <c r="O261" s="2" t="inlineStr"/>
-      <c r="P261" s="2" t="inlineStr"/>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>admission@stgeorgeschool.eu; st.george.school@stgeorgeschool.eu; st.george.preschool@stgeorgeschool.eu; examsofficer@stgeorgeschool.eu; events@stgeorgeschool.eu; courses@stgeorgeschool.eu; summer.camp@stgeorgeschool.eu; sport.complex@stgeorgeschool.eu</t>
+        </is>
+      </c>
       <c r="Q261" s="2" t="inlineStr"/>
       <c r="R261" s="2" t="inlineStr">
         <is>
@@ -23987,7 +25367,11 @@
       </c>
       <c r="X261" s="2" t="inlineStr"/>
       <c r="Y261" s="2" t="inlineStr"/>
-      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr">
+        <is>
+          <t>https://stgeorgeschool.eu/contacts/</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -24075,7 +25459,11 @@
       </c>
       <c r="X262" s="2" t="inlineStr"/>
       <c r="Y262" s="2" t="inlineStr"/>
-      <c r="Z262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr">
+        <is>
+          <t>https://otpp.com/en-ca/about-us/news-and-insights/2018/appointment-notice-jean-charles-douin/; https://www.otpp.com/en-ca/investments/our-global-team/equities-team/</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -24121,8 +25509,16 @@
       <c r="M263" s="2" t="inlineStr"/>
       <c r="N263" s="2" t="inlineStr"/>
       <c r="O263" s="2" t="inlineStr"/>
-      <c r="P263" s="2" t="inlineStr"/>
-      <c r="Q263" s="2" t="inlineStr"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>info@kibiz-zug.ch</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>+41 41 712 33 23</t>
+        </is>
+      </c>
       <c r="R263" s="2" t="inlineStr">
         <is>
           <t>Non-profit childcare organisation in Zug (note: 'KiBiz' in Germany is the NRW childcare law, not an operator). Hooks: cantonal subsidy reporting.</t>
@@ -24155,7 +25551,11 @@
       </c>
       <c r="X263" s="2" t="inlineStr"/>
       <c r="Y263" s="2" t="inlineStr"/>
-      <c r="Z263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr">
+        <is>
+          <t>https://kibiz-zug.ch/impressum; https://kibiz-zug.ch/kontakt</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -24281,8 +25681,16 @@
       <c r="M265" s="2" t="inlineStr"/>
       <c r="N265" s="2" t="inlineStr"/>
       <c r="O265" s="2" t="inlineStr"/>
-      <c r="P265" s="2" t="inlineStr"/>
-      <c r="Q265" s="2" t="inlineStr"/>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>info@kimikrippen.ch</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>+41 44 211 23 23</t>
+        </is>
+      </c>
       <c r="R265" s="2" t="inlineStr">
         <is>
           <t>Swiss Kita chain with company-Kita partnerships. Hooks: multi-canton admin.</t>
@@ -24315,7 +25723,11 @@
       </c>
       <c r="X265" s="2" t="inlineStr"/>
       <c r="Y265" s="2" t="inlineStr"/>
-      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kimikrippen.ch/impressum/</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -24361,8 +25773,16 @@
       <c r="M266" s="2" t="inlineStr"/>
       <c r="N266" s="2" t="inlineStr"/>
       <c r="O266" s="2" t="inlineStr"/>
-      <c r="P266" s="2" t="inlineStr"/>
-      <c r="Q266" s="2" t="inlineStr"/>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>info@kihz.ethz.ch</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>+41 44 634 40 90</t>
+        </is>
+      </c>
       <c r="R266" s="2" t="inlineStr">
         <is>
           <t>kihz - Stiftung Kinderbetreuung im Hochschulraum Zürich - runs Kitas for ETH Zurich and University of Zurich families. Hooks: university-employer reporting.</t>
@@ -24395,7 +25815,11 @@
       </c>
       <c r="X266" s="2" t="inlineStr"/>
       <c r="Y266" s="2" t="inlineStr"/>
-      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kihz.uzh.ch/en/contact; https://kihz.uzh.ch/assets/PDF/Deutsch/Stiftung-kihz-Organigramm.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -24441,8 +25865,16 @@
       <c r="M267" s="2" t="inlineStr"/>
       <c r="N267" s="2" t="inlineStr"/>
       <c r="O267" s="2" t="inlineStr"/>
-      <c r="P267" s="2" t="inlineStr"/>
-      <c r="Q267" s="2" t="inlineStr"/>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>new@littlegreenhouse.ch; gland@littlegreenhouse.ch; versoix@littlegreenhouse.ch; perly@littlegreenhouse.ch</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>+41 22 364 45 50</t>
+        </is>
+      </c>
       <c r="R267" s="2" t="inlineStr">
         <is>
           <t>Bilingual (DE/EN) Kita chain founded in Bern with expansion across Swiss cities. Hooks: bilingual parent communication.</t>
@@ -24473,9 +25905,17 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X267" s="2" t="inlineStr"/>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>new@littlegreenhouse.ch (Barbara Lax, Founder)</t>
+        </is>
+      </c>
       <c r="Y267" s="2" t="inlineStr"/>
-      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.littlegreenhouse.ch/contact/; https://www.zoominfo.com/c/little-green-house/425064736</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -24521,8 +25961,16 @@
       <c r="M268" s="2" t="inlineStr"/>
       <c r="N268" s="2" t="inlineStr"/>
       <c r="O268" s="2" t="inlineStr"/>
-      <c r="P268" s="2" t="inlineStr"/>
-      <c r="Q268" s="2" t="inlineStr"/>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>kitas@zuerich.ch</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>+41 44 412 69 32</t>
+        </is>
+      </c>
       <c r="R268" s="2" t="inlineStr">
         <is>
           <t>Largest single Kita operator in Zurich. Hooks: public tender.</t>
@@ -24555,7 +26003,11 @@
       </c>
       <c r="X268" s="2" t="inlineStr"/>
       <c r="Y268" s="2" t="inlineStr"/>
-      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr">
+        <is>
+          <t>https://adressverzeichnis.sozialearbeit.zhaw.ch/Detail/Index/Stadt_Zuerich,_Soziale_Einrichtungen_und_Betriebe-Geschaeftsbereich_Kinderbetreuung-Zuerich-1b72de10-bc44-e311-8b4f-005056a606f6</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -24601,8 +26053,16 @@
       <c r="M269" s="2" t="inlineStr"/>
       <c r="N269" s="2" t="inlineStr"/>
       <c r="O269" s="2" t="inlineStr"/>
-      <c r="P269" s="2" t="inlineStr"/>
-      <c r="Q269" s="2" t="inlineStr"/>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>info@gfz-zh.ch</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>044 253 65 10</t>
+        </is>
+      </c>
       <c r="R269" s="2" t="inlineStr">
         <is>
           <t>Historic Zurich foundation operating Kitas and family centres. Hooks: city-subsidy admin.</t>
@@ -24635,7 +26095,11 @@
       </c>
       <c r="X269" s="2" t="inlineStr"/>
       <c r="Y269" s="2" t="inlineStr"/>
-      <c r="Z269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr">
+        <is>
+          <t>https://gfz-zh.ch/impressum/; https://gfz-zh.ch/kontakt/</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -24681,8 +26145,16 @@
       <c r="M270" s="2" t="inlineStr"/>
       <c r="N270" s="2" t="inlineStr"/>
       <c r="O270" s="2" t="inlineStr"/>
-      <c r="P270" s="2" t="inlineStr"/>
-      <c r="Q270" s="2" t="inlineStr"/>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>info@familea.ch; frauenberatung@familea.ch; angebote@familea.ch; unikrippe@familea.ch</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>+41 61 260 82 00</t>
+        </is>
+      </c>
       <c r="R270" s="2" t="inlineStr">
         <is>
           <t>Basel's largest non-profit Kita operator, rooted in the 1901 Basler Frauenverein. Hooks: Basel subsidy system.</t>
@@ -24715,7 +26187,11 @@
       </c>
       <c r="X270" s="2" t="inlineStr"/>
       <c r="Y270" s="2" t="inlineStr"/>
-      <c r="Z270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.familea.ch/en/contact/; https://search.ch/tel/basel/freie-strasse-35/familea-geschaeftsstelle</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -24761,8 +26237,16 @@
       <c r="M271" s="2" t="inlineStr"/>
       <c r="N271" s="2" t="inlineStr"/>
       <c r="O271" s="2" t="inlineStr"/>
-      <c r="P271" s="2" t="inlineStr"/>
-      <c r="Q271" s="2" t="inlineStr"/>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>zuerich@profawo.ch</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>+41 44 254 60 50</t>
+        </is>
+      </c>
       <c r="R271" s="2" t="inlineStr">
         <is>
           <t>Family-service association offering Kitas and Nanny/Notfallbetreuung to corporate members. Hooks: corporate-client reporting.</t>
@@ -24795,7 +26279,11 @@
       </c>
       <c r="X271" s="2" t="inlineStr"/>
       <c r="Y271" s="2" t="inlineStr"/>
-      <c r="Z271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.local.ch/de/d/zuerich/8055/profawo-8uy8CuaLOl4b1y2erN0Hpg; https://www.profawo.ch/en/about-profawo/committee</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -24845,7 +26333,11 @@
       <c r="M272" s="2" t="inlineStr"/>
       <c r="N272" s="2" t="inlineStr"/>
       <c r="O272" s="2" t="inlineStr"/>
-      <c r="P272" s="2" t="inlineStr"/>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>info@academy.ac.cy; aajuniorschool@academy.ac.cy; juniorschool@academy.ac.cy</t>
+        </is>
+      </c>
       <c r="Q272" s="2" t="inlineStr"/>
       <c r="R272" s="2" t="inlineStr">
         <is>
@@ -24875,7 +26367,11 @@
       </c>
       <c r="X272" s="2" t="inlineStr"/>
       <c r="Y272" s="2" t="inlineStr"/>
-      <c r="Z272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.academy.ac.cy/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -24925,8 +26421,16 @@
       <c r="M273" s="2" t="inlineStr"/>
       <c r="N273" s="2" t="inlineStr"/>
       <c r="O273" s="2" t="inlineStr"/>
-      <c r="P273" s="2" t="inlineStr"/>
-      <c r="Q273" s="2" t="inlineStr"/>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>administration@heritageschool.ac.cy</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>+357 25367018</t>
+        </is>
+      </c>
       <c r="R273" s="2" t="inlineStr">
         <is>
           <t>Large English-medium private school in Limassol with nursery and pre-school. Single campus.</t>
@@ -24955,7 +26459,11 @@
       </c>
       <c r="X273" s="2" t="inlineStr"/>
       <c r="Y273" s="2" t="inlineStr"/>
-      <c r="Z273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.heritageschool.ac.cy/; https://cyprus-mail.com/schools-guide/heritage-private-school-and-institute/</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -25001,8 +26509,16 @@
       <c r="M274" s="2" t="inlineStr"/>
       <c r="N274" s="2" t="inlineStr"/>
       <c r="O274" s="2" t="inlineStr"/>
-      <c r="P274" s="2" t="inlineStr"/>
-      <c r="Q274" s="2" t="inlineStr"/>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>dejvice.bambino@skolka-bambino.cz; vinohrady.bambino@skolka-bambino.cz</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>+420 777 636 742; +420 602 631 326</t>
+        </is>
+      </c>
       <c r="R274" s="2" t="inlineStr">
         <is>
           <t>Bambíno is a Prague network of private nurseries and preschools with several branches, offering Czech-English programmes and extended hours. Branch count and management not verified this session.</t>
@@ -25031,7 +26547,11 @@
       </c>
       <c r="X274" s="2" t="inlineStr"/>
       <c r="Y274" s="2" t="inlineStr"/>
-      <c r="Z274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.skolkabambino.cz/en/bambino-contact</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -25077,8 +26597,16 @@
       <c r="M275" s="2" t="inlineStr"/>
       <c r="N275" s="2" t="inlineStr"/>
       <c r="O275" s="2" t="inlineStr"/>
-      <c r="P275" s="2" t="inlineStr"/>
-      <c r="Q275" s="2" t="inlineStr"/>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>info@helloteddy.cz</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>+420 733 530 656</t>
+        </is>
+      </c>
       <c r="R275" s="2" t="inlineStr">
         <is>
           <t>Hello Teddy operates English-immersion preschools in several Prague districts. Management not verified this session.</t>
@@ -25105,9 +26633,21 @@
           <t>cee.json</t>
         </is>
       </c>
-      <c r="X275" s="2" t="inlineStr"/>
-      <c r="Y275" s="2" t="inlineStr"/>
-      <c r="Z275" s="2" t="inlineStr"/>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>kubonova@helloteddy.cz (Radmila Kuboňová, Zástupkyně ředitelky pro MŠ); jurankova@helloskola.cz (Gabriela Juránková, Ředitelka školy (helloskola.cz))</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr">
+        <is>
+          <t>last@helloteddy.cz</t>
+        </is>
+      </c>
+      <c r="Z275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.helloskola.cz/materska-skolka/kontakty/; https://www.helloteddy.cz/cs/detska-skupina</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -25149,7 +26689,11 @@
       <c r="M276" s="2" t="inlineStr"/>
       <c r="N276" s="2" t="inlineStr"/>
       <c r="O276" s="2" t="inlineStr"/>
-      <c r="P276" s="2" t="inlineStr"/>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>admissions@isp.cz</t>
+        </is>
+      </c>
       <c r="Q276" s="2" t="inlineStr"/>
       <c r="R276" s="2" t="inlineStr">
         <is>
@@ -25179,7 +26723,11 @@
       </c>
       <c r="X276" s="2" t="inlineStr"/>
       <c r="Y276" s="2" t="inlineStr"/>
-      <c r="Z276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr">
+        <is>
+          <t>https://english-schools.org/czech/international-school-prague.htm; https://rocketreach.co/international-school-of-prague-email-format_b58fd14af762e8c0</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -25225,8 +26773,16 @@
       <c r="M277" s="2" t="inlineStr"/>
       <c r="N277" s="2" t="inlineStr"/>
       <c r="O277" s="2" t="inlineStr"/>
-      <c r="P277" s="2" t="inlineStr"/>
-      <c r="Q277" s="2" t="inlineStr"/>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>info@kindergarten.cz; kunratice@kindergarten.cz; cb@kindergarten.cz</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>776 003 003</t>
+        </is>
+      </c>
       <c r="R277" s="2" t="inlineStr">
         <is>
           <t>KinderGarten.cz is a Prague chain of bilingual English/Czech private preschools and nurseries with several branches in the city. It is one of the more visible private preschool brands in Prague. Details, branch count and management could not be verified this session.</t>
@@ -25255,7 +26811,11 @@
       </c>
       <c r="X277" s="2" t="inlineStr"/>
       <c r="Y277" s="2" t="inlineStr"/>
-      <c r="Z277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kindergarten.cz/kindergarten/kontakt; https://www.kindergarten.cz/anglicke-skolky/kunratice/kontakt</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -25301,8 +26861,16 @@
       <c r="M278" s="2" t="inlineStr"/>
       <c r="N278" s="2" t="inlineStr"/>
       <c r="O278" s="2" t="inlineStr"/>
-      <c r="P278" s="2" t="inlineStr"/>
-      <c r="Q278" s="2" t="inlineStr"/>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>info@meridianedu.cz</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>+420 775 581 801</t>
+        </is>
+      </c>
       <c r="R278" s="2" t="inlineStr">
         <is>
           <t>Meridian International School is a Prague international school with a kindergarten section (Cambridge programme). Management not confirmed this session.</t>
@@ -25331,7 +26899,11 @@
       </c>
       <c r="X278" s="2" t="inlineStr"/>
       <c r="Y278" s="2" t="inlineStr"/>
-      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>https://meridian.edupage.org/contact/; https://www.meridianedu.cz/</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -25377,7 +26949,11 @@
       <c r="M279" s="2" t="inlineStr"/>
       <c r="N279" s="2" t="inlineStr"/>
       <c r="O279" s="2" t="inlineStr"/>
-      <c r="P279" s="2" t="inlineStr"/>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>info@parklane-is.com; office.valdstejnska@parklane-is.com</t>
+        </is>
+      </c>
       <c r="Q279" s="2" t="inlineStr"/>
       <c r="R279" s="2" t="inlineStr">
         <is>
@@ -25405,9 +26981,21 @@
           <t>cee.json</t>
         </is>
       </c>
-      <c r="X279" s="2" t="inlineStr"/>
-      <c r="Y279" s="2" t="inlineStr"/>
-      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>denisa.krajsova@parklane-is.com (Denisa Krajsova, Prague 5 School Office); aryanova@parklane-is.com (A. Ryanova, Prague 6 School Registrar); karolina.schreiberova@parklane-is.com (Karolina Schreiberova, Prague 1 Admissions and PR Officer)</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr">
+        <is>
+          <t>first.last@parklane-is.com (also seen: initial+last)</t>
+        </is>
+      </c>
+      <c r="Z279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.parklane-is.cz/admissions/contact-details/; https://www.parklane-is.cz/contact-us/; https://www.parklane-is.cz/our-staff/</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -25521,8 +27109,16 @@
       <c r="M281" s="2" t="inlineStr"/>
       <c r="N281" s="2" t="inlineStr"/>
       <c r="O281" s="2" t="inlineStr"/>
-      <c r="P281" s="2" t="inlineStr"/>
-      <c r="Q281" s="2" t="inlineStr"/>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>ey@riversideschool.cz; admissions@riversideschool.cz</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>+420 245 005 095</t>
+        </is>
+      </c>
       <c r="R281" s="2" t="inlineStr">
         <is>
           <t>Riverside School is a British-curriculum international school in Prague with early-years classes. Head not confirmed this session.</t>
@@ -25551,7 +27147,11 @@
       </c>
       <c r="X281" s="2" t="inlineStr"/>
       <c r="Y281" s="2" t="inlineStr"/>
-      <c r="Z281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.riversideschool.cz/contact-us/contacts/</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -25601,7 +27201,11 @@
       <c r="M282" s="2" t="inlineStr"/>
       <c r="N282" s="2" t="inlineStr"/>
       <c r="O282" s="2" t="inlineStr"/>
-      <c r="P282" s="2" t="inlineStr"/>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>info@awo.org</t>
+        </is>
+      </c>
       <c r="Q282" s="2" t="inlineStr"/>
       <c r="R282" s="2" t="inlineStr">
         <is>
@@ -25633,9 +27237,21 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X282" s="2" t="inlineStr"/>
-      <c r="Y282" s="2" t="inlineStr"/>
-      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="X282" s="2" t="inlineStr">
+        <is>
+          <t>Judith.Adamczyk@awo.org (Dr. Judith Adamczyk, Referentin Bildung und Erziehung / Tageseinrichtungen für Kinder, AWO Bundesverband)</t>
+        </is>
+      </c>
+      <c r="Y282" s="2" t="inlineStr">
+        <is>
+          <t>First.Last@awo.org</t>
+        </is>
+      </c>
+      <c r="Z282" s="2" t="inlineStr">
+        <is>
+          <t>https://awo.org/projekt/kindertagesbetreuung/; https://awo.org/impressum/</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -25685,7 +27301,11 @@
       <c r="M283" s="2" t="inlineStr"/>
       <c r="N283" s="2" t="inlineStr"/>
       <c r="O283" s="2" t="inlineStr"/>
-      <c r="P283" s="2" t="inlineStr"/>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>ktk-bundesverband@caritas.de</t>
+        </is>
+      </c>
       <c r="Q283" s="2" t="inlineStr"/>
       <c r="R283" s="2" t="inlineStr">
         <is>
@@ -25719,7 +27339,11 @@
       </c>
       <c r="X283" s="2" t="inlineStr"/>
       <c r="Y283" s="2" t="inlineStr"/>
-      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ktk-bundesverband.de/impressum; https://www.ktk-bundesverband.de/derktkbundesverband/ihreansprechpartner; https://www.ktk-bundesverband.de/pressepositionenpublikationen/presse/neue-geschaeftsfuehrung-im-ktk-bundesverband-22679c91-8833-4535-b505-3af1b6af45e7</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -25765,8 +27389,16 @@
       <c r="M284" s="2" t="inlineStr"/>
       <c r="N284" s="2" t="inlineStr"/>
       <c r="O284" s="2" t="inlineStr"/>
-      <c r="P284" s="2" t="inlineStr"/>
-      <c r="Q284" s="2" t="inlineStr"/>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>info@kinderwelt-hamburg.de</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>040 – 20 00 03 – 0</t>
+        </is>
+      </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
           <t>Hamburg non-profit with c. 30 Kitas and a strong nature/'Weltentdecker' pedagogy. Hooks: Hamburg Kita-Gutschein administration.</t>
@@ -25799,7 +27431,11 @@
       </c>
       <c r="X284" s="2" t="inlineStr"/>
       <c r="Y284" s="2" t="inlineStr"/>
-      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr">
+        <is>
+          <t>https://kinderwelt-hamburg.de/impressum/; https://www.northdata.de/?id=6461253259100160</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -25849,8 +27485,16 @@
       <c r="M285" s="2" t="inlineStr"/>
       <c r="N285" s="2" t="inlineStr"/>
       <c r="O285" s="2" t="inlineStr"/>
-      <c r="P285" s="2" t="inlineStr"/>
-      <c r="Q285" s="2" t="inlineStr"/>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>DRK@DRK.de; Spenderservice@DRK.de</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>030 85404-0</t>
+        </is>
+      </c>
       <c r="R285" s="2" t="inlineStr">
         <is>
           <t>Decentralised welfare association; regional Kreisverbände decide. Hooks: regional targeting.</t>
@@ -25883,7 +27527,11 @@
       </c>
       <c r="X285" s="2" t="inlineStr"/>
       <c r="Y285" s="2" t="inlineStr"/>
-      <c r="Z285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.drk.de/das-drk/kontakt/; https://www.drk.de/das-drk/adressen/drk-generalsekretariat/?L=0</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -25933,8 +27581,16 @@
       <c r="M286" s="2" t="inlineStr"/>
       <c r="N286" s="2" t="inlineStr"/>
       <c r="O286" s="2" t="inlineStr"/>
-      <c r="P286" s="2" t="inlineStr"/>
-      <c r="Q286" s="2" t="inlineStr"/>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>info@beta-diakonie.de</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>030 280 91 510</t>
+        </is>
+      </c>
       <c r="R286" s="2" t="inlineStr">
         <is>
           <t>Protestant Kitas are run by parishes and growing regional Kita-Verbände (e.g. Ev. Kita-Verband Bayern, Kita-Werke in Hamburg, Diakonie Düsseldorf). Hooks: target regional Verbände.</t>
@@ -25967,7 +27623,11 @@
       </c>
       <c r="X286" s="2" t="inlineStr"/>
       <c r="Y286" s="2" t="inlineStr"/>
-      <c r="Z286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr">
+        <is>
+          <t>https://beta-diakonie.de/impressum/; https://www.beta-diakonie.de/kontakt/</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -26013,8 +27673,16 @@
       <c r="M287" s="2" t="inlineStr"/>
       <c r="N287" s="2" t="inlineStr"/>
       <c r="O287" s="2" t="inlineStr"/>
-      <c r="P287" s="2" t="inlineStr"/>
-      <c r="Q287" s="2" t="inlineStr"/>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>info@espira-kinderbetreuung.de; info@academedia.de</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>089 / 20 18 43 31 0</t>
+        </is>
+      </c>
       <c r="R287" s="2" t="inlineStr">
         <is>
           <t>AcadeMedia's northern German Kita brand. Hooks: see AcadeMedia entry.</t>
@@ -26047,7 +27715,11 @@
       </c>
       <c r="X287" s="2" t="inlineStr"/>
       <c r="Y287" s="2" t="inlineStr"/>
-      <c r="Z287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr">
+        <is>
+          <t>https://espira-kinderbetreuung.de/home/impressum/; https://www.joki-kinderbetreuung.de/impressum/</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -26181,8 +27853,16 @@
       <c r="M289" s="2" t="inlineStr"/>
       <c r="N289" s="2" t="inlineStr"/>
       <c r="O289" s="2" t="inlineStr"/>
-      <c r="P289" s="2" t="inlineStr"/>
-      <c r="Q289" s="2" t="inlineStr"/>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>info@jus-or.de</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>+49 3301 8341-0</t>
+        </is>
+      </c>
       <c r="R289" s="2" t="inlineStr">
         <is>
           <t>JuS is a large Brandenburg-based social enterprise operating Kitas (e.g. Kita Kinderland, Oranienburg), Horte and youth facilities. Estimate of site count not confirmed. Hooks: rural multi-site admin.</t>
@@ -26209,9 +27889,21 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X289" s="2" t="inlineStr"/>
-      <c r="Y289" s="2" t="inlineStr"/>
-      <c r="Z289" s="2" t="inlineStr"/>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>j.karrass@jus-or.de (Herr Karraß, Leitung Kommunikation, PR &amp; Markenentwicklung)</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr">
+        <is>
+          <t>f.last@domain</t>
+        </is>
+      </c>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jugendundsozialwerk.de/impressum/; https://www.jugendundsozialwerk.de/kontakt/; https://www.jugendundsozialwerk.de/ueber-uns/presse-und-medien/</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -26261,8 +27953,16 @@
       <c r="M290" s="2" t="inlineStr"/>
       <c r="N290" s="2" t="inlineStr"/>
       <c r="O290" s="2" t="inlineStr"/>
-      <c r="P290" s="2" t="inlineStr"/>
-      <c r="Q290" s="2" t="inlineStr"/>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>office@kita.bremen.de</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>+49 421 3615700</t>
+        </is>
+      </c>
       <c r="R290" s="2" t="inlineStr">
         <is>
           <t>Bremen's municipal operator; took over sites after pme Bremen insolvency 2025 context. Hooks: public procurement.</t>
@@ -26295,7 +27995,11 @@
       </c>
       <c r="X290" s="2" t="inlineStr"/>
       <c r="Y290" s="2" t="inlineStr"/>
-      <c r="Z290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kita.bremen.de/unser-betrieb/impressum-1478; https://www.kita.bremen.de/unser-betrieb/ansprechpersonen-9298</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -26341,8 +28045,16 @@
       <c r="M291" s="2" t="inlineStr"/>
       <c r="N291" s="2" t="inlineStr"/>
       <c r="O291" s="2" t="inlineStr"/>
-      <c r="P291" s="2" t="inlineStr"/>
-      <c r="Q291" s="2" t="inlineStr"/>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>geschaeftsstelle@kita-ggmbh-trier.de; geschaeftsfuehrung@kita-ggmbh-trier.de</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>0651 9998750</t>
+        </is>
+      </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
           <t>Diocesan Kita holding companies of the Bistum Trier with professional HQs. Hooks: central procurement.</t>
@@ -26375,7 +28087,11 @@
       </c>
       <c r="X291" s="2" t="inlineStr"/>
       <c r="Y291" s="2" t="inlineStr"/>
-      <c r="Z291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kita-ggmbh-trier.de/ueber-uns/uebersicht/geschaeftsfuehrung/index.html; https://www.kita-ggmbh-trier.de/ueber-uns/uebersicht/geschaeftsstelle/index.html</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -26462,16 +28178,8 @@
         </is>
       </c>
       <c r="X292" s="2" t="inlineStr"/>
-      <c r="Y292" s="2" t="inlineStr">
-        <is>
-          <t>first.last@domain</t>
-        </is>
-      </c>
-      <c r="Z292" s="2" t="inlineStr">
-        <is>
-          <t>https://www.familienservice.de/-/daniel_erler_ku-1</t>
-        </is>
-      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -26621,7 +28329,11 @@
       <c r="M294" s="2" t="inlineStr"/>
       <c r="N294" s="2" t="inlineStr"/>
       <c r="O294" s="2" t="inlineStr"/>
-      <c r="P294" s="2" t="inlineStr"/>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>info@kindergaerten-city.de</t>
+        </is>
+      </c>
       <c r="Q294" s="2" t="inlineStr"/>
       <c r="R294" s="2" t="inlineStr">
         <is>
@@ -26655,7 +28367,11 @@
       </c>
       <c r="X294" s="2" t="inlineStr"/>
       <c r="Y294" s="2" t="inlineStr"/>
-      <c r="Z294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>https://fragdenstaat.de/behoerde/49169/kindergarten-city-eigenbetrieb-von-berlin/</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -26705,8 +28421,16 @@
       <c r="M295" s="2" t="inlineStr"/>
       <c r="N295" s="2" t="inlineStr"/>
       <c r="O295" s="2" t="inlineStr"/>
-      <c r="P295" s="2" t="inlineStr"/>
-      <c r="Q295" s="2" t="inlineStr"/>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>presse@kigaeno.de</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>030 50 50 86-700</t>
+        </is>
+      </c>
       <c r="R295" s="2" t="inlineStr">
         <is>
           <t>Largest of Berlin's five municipal Kita Eigenbetriebe. Hooks: as above.</t>
@@ -26739,7 +28463,11 @@
       </c>
       <c r="X295" s="2" t="inlineStr"/>
       <c r="Y295" s="2" t="inlineStr"/>
-      <c r="Z295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kigaeno.de/impressum/; https://www.kigaeno.de/geschaeftsstelle/</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -26785,8 +28513,16 @@
       <c r="M296" s="2" t="inlineStr"/>
       <c r="N296" s="2" t="inlineStr"/>
       <c r="O296" s="2" t="inlineStr"/>
-      <c r="P296" s="2" t="inlineStr"/>
-      <c r="Q296" s="2" t="inlineStr"/>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>kinderland@kinderland2000.de</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>+49-2962-979393</t>
+        </is>
+      </c>
       <c r="R296" s="2" t="inlineStr">
         <is>
           <t>Kinderland 2000 is an East-German private Kita operator with 17 facilities across three Länder. Regional, owner-managed. Hooks: multi-Land compliance.</t>
@@ -26815,7 +28551,11 @@
       </c>
       <c r="X296" s="2" t="inlineStr"/>
       <c r="Y296" s="2" t="inlineStr"/>
-      <c r="Z296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kinderland2000.de/impressum/; https://www.kita24.org/stadt/sangerhausen/profil/kindertagesstaette-tausend-fuehler-kinderland-2000-ggmbh/</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -27049,7 +28789,11 @@
       <c r="M299" s="2" t="inlineStr"/>
       <c r="N299" s="2" t="inlineStr"/>
       <c r="O299" s="2" t="inlineStr"/>
-      <c r="P299" s="2" t="inlineStr"/>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>forstenried@joki-kinderbetreuung.de; harlaching@joki-kinderbetreuung.de; pasing@joki-kinderbetreuung.de; trudering@joki-kinderbetreuung.de</t>
+        </is>
+      </c>
       <c r="Q299" s="2" t="inlineStr"/>
       <c r="R299" s="2" t="inlineStr">
         <is>
@@ -27083,7 +28827,11 @@
       </c>
       <c r="X299" s="2" t="inlineStr"/>
       <c r="Y299" s="2" t="inlineStr"/>
-      <c r="Z299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.joki-kinderbetreuung.de/impressum/; https://www.info-sozial.de/datenbank/adressen.php?id=9754; https://stadt.muenchen.de/service/info/joki-kinderbetreuung-pasing-bilinguale-krippe-und-kindergarten/1085788/</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -27165,9 +28913,21 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X300" s="2" t="inlineStr"/>
-      <c r="Y300" s="2" t="inlineStr"/>
-      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="X300" s="2" t="inlineStr">
+        <is>
+          <t>Gabriele.Bischoff@stadt-frankfurt.de (Gabriele Bischoff, former Betriebsleiterin Kita Frankfurt (older profile))</t>
+        </is>
+      </c>
+      <c r="Y300" s="2" t="inlineStr">
+        <is>
+          <t>First.Last@stadt-frankfurt.de</t>
+        </is>
+      </c>
+      <c r="Z300" s="2" t="inlineStr">
+        <is>
+          <t>https://kitafrankfurt.de/impressum/; https://kitafrankfurt.de/unternehmen/die-betriebsleitung/</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -27213,8 +28973,16 @@
       <c r="M301" s="2" t="inlineStr"/>
       <c r="N301" s="2" t="inlineStr"/>
       <c r="O301" s="2" t="inlineStr"/>
-      <c r="P301" s="2" t="inlineStr"/>
-      <c r="Q301" s="2" t="inlineStr"/>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>bildungsstiftung@element-i.de; info@konzept-e.de</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>+49 711 656960-7078</t>
+        </is>
+      </c>
       <c r="R301" s="2" t="inlineStr">
         <is>
           <t>Founded by Waltraud Weegmann; runs element-i Kitas, schools and a Fachschule; active in Deutscher Kitaverband. Hooks: own pedagogy brand, digital learning documentation.</t>
@@ -27247,7 +29015,11 @@
       </c>
       <c r="X301" s="2" t="inlineStr"/>
       <c r="Y301" s="2" t="inlineStr"/>
-      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.element-i.de/impressum/; https://www.element-i-bildungsstiftung.de/impressum/; https://www.element-i-bildungsstiftung.de/kontakt/</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -27369,8 +29141,16 @@
       <c r="M303" s="2" t="inlineStr"/>
       <c r="N303" s="2" t="inlineStr"/>
       <c r="O303" s="2" t="inlineStr"/>
-      <c r="P303" s="2" t="inlineStr"/>
-      <c r="Q303" s="2" t="inlineStr"/>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>service@babilou-family.de</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
+          <t>0711 / 184 205 20</t>
+        </is>
+      </c>
       <c r="R303" s="2" t="inlineStr">
         <is>
           <t>Smaller Babilou brand named in Babilou Family Deutschland brand list. Hooks: see Babilou entry.</t>
@@ -27403,7 +29183,11 @@
       </c>
       <c r="X303" s="2" t="inlineStr"/>
       <c r="Y303" s="2" t="inlineStr"/>
-      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr">
+        <is>
+          <t>https://minimax-kita.com/Kontakt; https://www.denk-mit.de/de/minimax-kids</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -27537,7 +29321,11 @@
       <c r="M305" s="2" t="inlineStr"/>
       <c r="N305" s="2" t="inlineStr"/>
       <c r="O305" s="2" t="inlineStr"/>
-      <c r="P305" s="2" t="inlineStr"/>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>info@pfh-berlin.de; kinderschutz@pfh-berlin.de; bewerbungen@pfh-berlin.de; schulsekretariat@pfh-berlin.de</t>
+        </is>
+      </c>
       <c r="Q305" s="2" t="inlineStr"/>
       <c r="R305" s="2" t="inlineStr">
         <is>
@@ -27569,9 +29357,21 @@
           <t>dach.json</t>
         </is>
       </c>
-      <c r="X305" s="2" t="inlineStr"/>
-      <c r="Y305" s="2" t="inlineStr"/>
-      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="X305" s="2" t="inlineStr">
+        <is>
+          <t>oezlem.cinar@pfh-berlin.de (Özlem Cinar, Head of Public Relations and Communications); bettina.wilmes@pfh-berlin.de (Bettina Wilmes, Editorial / PR)</t>
+        </is>
+      </c>
+      <c r="Y305" s="2" t="inlineStr">
+        <is>
+          <t>first.last@pfh-berlin.de</t>
+        </is>
+      </c>
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pfh-berlin.de/de/artikelseite/impressum; https://www.pfh-berlin.de/de/ansprechpartnerInnen</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -27617,8 +29417,16 @@
       <c r="M306" s="2" t="inlineStr"/>
       <c r="N306" s="2" t="inlineStr"/>
       <c r="O306" s="2" t="inlineStr"/>
-      <c r="P306" s="2" t="inlineStr"/>
-      <c r="Q306" s="2" t="inlineStr"/>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>geschaeftsstelle@rudolf-ballin-stiftung.de; kokopelli@rudolf-ballin-stiftung.de</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>040-270702-0</t>
+        </is>
+      </c>
       <c r="R306" s="2" t="inlineStr">
         <is>
           <t>Hamburg foundation founded 1965 running Kitas and all-day school programmes. Hooks: Hamburg voucher admin.</t>
@@ -27651,7 +29459,11 @@
       </c>
       <c r="X306" s="2" t="inlineStr"/>
       <c r="Y306" s="2" t="inlineStr"/>
-      <c r="Z306" s="2" t="inlineStr"/>
+      <c r="Z306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bvnw.de/kindergaerten/rudolf-ballin-stiftung-e-v; https://www.wer-zu-wem.de/firma/ballin-stiftung.html; https://www.fruehehilfen-hamburg.de/angebot/-/profil/1580</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -27781,8 +29593,16 @@
       <c r="M308" s="2" t="inlineStr"/>
       <c r="N308" s="2" t="inlineStr"/>
       <c r="O308" s="2" t="inlineStr"/>
-      <c r="P308" s="2" t="inlineStr"/>
-      <c r="Q308" s="2" t="inlineStr"/>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>bundesverband@volkssolidaritaet.de</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
+          <t>+49 30 27 89 70</t>
+        </is>
+      </c>
       <c r="R308" s="2" t="inlineStr">
         <is>
           <t>Large East-German welfare association with many Kitas in Saxony, Brandenburg, Thuringia. Hooks: regional targeting.</t>
@@ -27815,7 +29635,11 @@
       </c>
       <c r="X308" s="2" t="inlineStr"/>
       <c r="Y308" s="2" t="inlineStr"/>
-      <c r="Z308" s="2" t="inlineStr"/>
+      <c r="Z308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.volkssolidaritaet.de/impressum/</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -27961,8 +29785,16 @@
       <c r="M310" s="2" t="inlineStr"/>
       <c r="N310" s="2" t="inlineStr"/>
       <c r="O310" s="2" t="inlineStr"/>
-      <c r="P310" s="2" t="inlineStr"/>
-      <c r="Q310" s="2" t="inlineStr"/>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>info@cis.dk; admissions@cis.dk</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>+45 39 46 33 00</t>
+        </is>
+      </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
           <t>Largest international school in Denmark with an Early Years programme in Nordhavn campus. Director not confirmed in this session.</t>
@@ -27987,7 +29819,11 @@
       </c>
       <c r="X310" s="2" t="inlineStr"/>
       <c r="Y310" s="2" t="inlineStr"/>
-      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.copenhageninternational.school/get-in-touch/contact-us/; https://www.copenhageninternational.school/learning/welcome-to-our-primary-school/early-years/</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -28029,8 +29865,16 @@
       <c r="M311" s="2" t="inlineStr"/>
       <c r="N311" s="2" t="inlineStr"/>
       <c r="O311" s="2" t="inlineStr"/>
-      <c r="P311" s="2" t="inlineStr"/>
-      <c r="Q311" s="2" t="inlineStr"/>
+      <c r="P311" s="2" t="inlineStr">
+        <is>
+          <t>admin@rygaards.com; admissions@rygaards.com; primary@rygaards.com</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
+          <t>+45 39 62 10 53</t>
+        </is>
+      </c>
       <c r="R311" s="2" t="inlineStr">
         <is>
           <t>Catholic international/Danish school in Hellerup with preschool/kindergarten classes. Not verified in this session.</t>
@@ -28055,7 +29899,11 @@
       </c>
       <c r="X311" s="2" t="inlineStr"/>
       <c r="Y311" s="2" t="inlineStr"/>
-      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr">
+        <is>
+          <t>https://rygaards.com/en/contact/; https://rygaards.com/en/welcome-to-the-international-primary-school/</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -28169,8 +30017,16 @@
       <c r="M313" s="2" t="inlineStr"/>
       <c r="N313" s="2" t="inlineStr"/>
       <c r="O313" s="2" t="inlineStr"/>
-      <c r="P313" s="2" t="inlineStr"/>
-      <c r="Q313" s="2" t="inlineStr"/>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>lasteaed@eraharidus.ee; sekretar@eraharidus.ee; vp@eraharidus.ee</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
+          <t>+372 58806209</t>
+        </is>
+      </c>
       <c r="R313" s="2" t="inlineStr">
         <is>
           <t>Edu Valem has operated a private kindergarten in Tallinn since 2004. Listed among Tallinn private kindergartens. Decision maker not confirmed via search; verify on website/registry before outreach. Longevity suggests stable enrolment. Low-mid priority.</t>
@@ -28195,7 +30051,11 @@
       </c>
       <c r="X313" s="2" t="inlineStr"/>
       <c r="Y313" s="2" t="inlineStr"/>
-      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr">
+        <is>
+          <t>https://lasteaed.eduvalem.eu/kontaktid/; https://lasteaed.eraharidus.ee/en/contacts/</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -28241,8 +30101,16 @@
       <c r="M314" s="2" t="inlineStr"/>
       <c r="N314" s="2" t="inlineStr"/>
       <c r="O314" s="2" t="inlineStr"/>
-      <c r="P314" s="2" t="inlineStr"/>
-      <c r="Q314" s="2" t="inlineStr"/>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>info@tela.ee</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
+          <t>+372 53831821</t>
+        </is>
+      </c>
       <c r="R314" s="2" t="inlineStr">
         <is>
           <t>Aarete Saar is a private kindergarten in Tallinn opened in 2012. It appears in Tallinn's private kindergarten listings. Website tela.ee and a Facebook page exist. Decision maker not confirmed via search; verify on website/registry before outreach. Single-site independent; low priority unless bundled with a Tallinn campaign.</t>
@@ -28267,7 +30135,11 @@
       </c>
       <c r="X314" s="2" t="inlineStr"/>
       <c r="Y314" s="2" t="inlineStr"/>
-      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.prosha.ee/et/lastehoid/</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -28317,8 +30189,16 @@
       <c r="M315" s="2" t="inlineStr"/>
       <c r="N315" s="2" t="inlineStr"/>
       <c r="O315" s="2" t="inlineStr"/>
-      <c r="P315" s="2" t="inlineStr"/>
-      <c r="Q315" s="2" t="inlineStr"/>
+      <c r="P315" s="2" t="inlineStr">
+        <is>
+          <t>aiake@aiake.edu.ee</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
+          <t>+372 5615 0396</t>
+        </is>
+      </c>
       <c r="R315" s="2" t="inlineStr">
         <is>
           <t>Aiake is a small private kindergarten run by the St Michael's Collegium foundation on the edge of Tallinn's Old Town. Part of a foundation that also runs schools. Decision maker not confirmed via search; verify on website/registry before outreach. Single site, small. Low priority individually but the foundation is a multi-institution owner.</t>
@@ -28341,9 +30221,21 @@
           <t>other.json</t>
         </is>
       </c>
-      <c r="X315" s="2" t="inlineStr"/>
-      <c r="Y315" s="2" t="inlineStr"/>
-      <c r="Z315" s="2" t="inlineStr"/>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>eve.padar@aiake.edu.ee (Eve Padar, Director (direktor))</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr">
+        <is>
+          <t>first.last@aiake.edu.ee</t>
+        </is>
+      </c>
+      <c r="Z315" s="2" t="inlineStr">
+        <is>
+          <t>https://aiake.edu.ee/; https://www.1182.ee/en/aiake-lasteaed-tallinnas</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -28469,8 +30361,16 @@
       <c r="M317" s="2" t="inlineStr"/>
       <c r="N317" s="2" t="inlineStr"/>
       <c r="O317" s="2" t="inlineStr"/>
-      <c r="P317" s="2" t="inlineStr"/>
-      <c r="Q317" s="2" t="inlineStr"/>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>info@babyerasmus.es</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
+          <t>+34 924 26 86 97</t>
+        </is>
+      </c>
       <c r="R317" s="2" t="inlineStr">
         <is>
           <t>Baby Erasmus opened in Badajoz in 2010 as the city's first English-immersion early years centre (0-6) with native teachers and all materials in English. It later launched a franchise model to replicate the immersion concept in other Spanish cities. The company remains small and founder-run. It is a relevant lead for bilingual early-years products but the franchise footprint is unverified.</t>
@@ -28499,7 +30399,11 @@
       </c>
       <c r="X317" s="2" t="inlineStr"/>
       <c r="Y317" s="2" t="inlineStr"/>
-      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BabyErasmus/; https://rocketreach.co/baby-erasmus-email-format_b406bda7fc234c5e</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -28587,11 +30491,7 @@
       </c>
       <c r="X318" s="2" t="inlineStr"/>
       <c r="Y318" s="2" t="inlineStr"/>
-      <c r="Z318" s="2" t="inlineStr">
-        <is>
-          <t>https://todoeduca.com/centros/escuela-infantil-la-pecera-ceuta/; https://elfarodeceuta.es/koala-soluciones-educativas-pecera-proyectos-ilusion/</t>
-        </is>
-      </c>
+      <c r="Z318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -28737,8 +30637,16 @@
       <c r="M320" s="2" t="inlineStr"/>
       <c r="N320" s="2" t="inlineStr"/>
       <c r="O320" s="2" t="inlineStr"/>
-      <c r="P320" s="2" t="inlineStr"/>
-      <c r="Q320" s="2" t="inlineStr"/>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>gruposorolla@gruposorolla.es</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
+          <t>+34 963732926</t>
+        </is>
+      </c>
       <c r="R320" s="2" t="inlineStr">
         <is>
           <t>Grupo Sorolla Educación is a Valencian teacher-owned cooperative running several schools (e.g. La Devesa, Martí Sorolla) with 0-3 and 3-6 sections. Group-level management coordinates purchasing and pedagogy across campuses.</t>
@@ -28767,7 +30675,11 @@
       </c>
       <c r="X320" s="2" t="inlineStr"/>
       <c r="Y320" s="2" t="inlineStr"/>
-      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr">
+        <is>
+          <t>https://gruposorollaeducacion.es/contacto/; https://anuarioceg.clubexcelencia.org/portfolio/grupo-sorolla-educacion-en-adelante-gse/</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -28885,7 +30797,11 @@
       <c r="M322" s="2" t="inlineStr"/>
       <c r="N322" s="2" t="inlineStr"/>
       <c r="O322" s="2" t="inlineStr"/>
-      <c r="P322" s="2" t="inlineStr"/>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>info@icsmadrid.org; admissions@icsmadrid.org; communications@icsmadrid.org; employment@icsmadrid.org</t>
+        </is>
+      </c>
       <c r="Q322" s="2" t="inlineStr"/>
       <c r="R322" s="2" t="inlineStr">
         <is>
@@ -28915,7 +30831,11 @@
       </c>
       <c r="X322" s="2" t="inlineStr"/>
       <c r="Y322" s="2" t="inlineStr"/>
-      <c r="Z322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nordangliaeducation.com/ics-madrid/contact-us</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -29057,7 +30977,11 @@
       <c r="M324" s="2" t="inlineStr"/>
       <c r="N324" s="2" t="inlineStr"/>
       <c r="O324" s="2" t="inlineStr"/>
-      <c r="P324" s="2" t="inlineStr"/>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>rgpd-enequip@enequip.es</t>
+        </is>
+      </c>
       <c r="Q324" s="2" t="inlineStr"/>
       <c r="R324" s="2" t="inlineStr">
         <is>
@@ -29087,7 +31011,11 @@
       </c>
       <c r="X324" s="2" t="inlineStr"/>
       <c r="Y324" s="2" t="inlineStr"/>
-      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr">
+        <is>
+          <t>https://enequip.es/es/aviso-legal/informacion-adicional-para-clientes/; https://prospeo.io/c/enequip-revenue</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -29277,7 +31205,11 @@
       </c>
       <c r="N327" s="2" t="inlineStr"/>
       <c r="O327" s="2" t="inlineStr"/>
-      <c r="P327" s="2" t="inlineStr"/>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>info@montessori-paris.com</t>
+        </is>
+      </c>
       <c r="Q327" s="2" t="inlineStr"/>
       <c r="R327" s="2" t="inlineStr">
         <is>
@@ -29307,7 +31239,11 @@
       </c>
       <c r="X327" s="2" t="inlineStr"/>
       <c r="Y327" s="2" t="inlineStr"/>
-      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montessori-paris.com/wi-school; https://www.montessori-paris.com/</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -29425,8 +31361,16 @@
       </c>
       <c r="N329" s="2" t="inlineStr"/>
       <c r="O329" s="2" t="inlineStr"/>
-      <c r="P329" s="2" t="inlineStr"/>
-      <c r="Q329" s="2" t="inlineStr"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>inscription@emi-paris.com</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 87 66 52 00</t>
+        </is>
+      </c>
       <c r="R329" s="2" t="inlineStr">
         <is>
           <t>Cours Molière / Ecole Montessori Internationale de Paris: independent Montessori kindergarten (verify). Included as a notable independent or international early-years provider in FR. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -29455,7 +31399,11 @@
       </c>
       <c r="X329" s="2" t="inlineStr"/>
       <c r="Y329" s="2" t="inlineStr"/>
-      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ecole-montessori-internationale.fr/equipe-paris-5; https://www.fabert.com/etablissement-prive/1589/COURS-MOLIERE.html; https://www.ecolemoliere.org/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -29577,8 +31525,16 @@
       </c>
       <c r="N331" s="2" t="inlineStr"/>
       <c r="O331" s="2" t="inlineStr"/>
-      <c r="P331" s="2" t="inlineStr"/>
-      <c r="Q331" s="2" t="inlineStr"/>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>info@ejm.net; secretariat-lille@ejm.net</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>01 44 37 00 80</t>
+        </is>
+      </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
           <t>Ecole Jeannine Manuel – maternelle: bilingual school with maternelle. Included as a notable independent or international early-years provider in FR. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -29607,7 +31563,11 @@
       </c>
       <c r="X331" s="2" t="inlineStr"/>
       <c r="Y331" s="2" t="inlineStr"/>
-      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr">
+        <is>
+          <t>https://ecolejeanninemanuel.org/en/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -29649,8 +31609,16 @@
       </c>
       <c r="N332" s="2" t="inlineStr"/>
       <c r="O332" s="2" t="inlineStr"/>
-      <c r="P332" s="2" t="inlineStr"/>
-      <c r="Q332" s="2" t="inlineStr"/>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>contact@montessori-littlematernelle.com; montessorilyonlumiere@gmail.com; kamanamontessori@yahoo.com</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>09 83 45 98 58 (Junior Academy, directrice Sarah Latrèche)</t>
+        </is>
+      </c>
       <c r="R332" s="2" t="inlineStr">
         <is>
           <t>Ecole Montessori Bilingue de Lyon: independent bilingual Montessori kindergarten (verify). Included as a notable independent or international early-years provider in FR. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -29679,7 +31647,11 @@
       </c>
       <c r="X332" s="2" t="inlineStr"/>
       <c r="Y332" s="2" t="inlineStr"/>
-      <c r="Z332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fabert.com/etablissement-prive/48721/JUNIOR-ACADEMY-ECOLE-MONTESSORI-BILINGUE.html; https://sites.google.com/site/montessorilittlematernelle/contact; https://kamana-montessori-lyon.fr/</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -29861,8 +31833,16 @@
       <c r="M335" s="2" t="inlineStr"/>
       <c r="N335" s="2" t="inlineStr"/>
       <c r="O335" s="2" t="inlineStr"/>
-      <c r="P335" s="2" t="inlineStr"/>
-      <c r="Q335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>contact.toulouse@kangouroukids.fr</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 82 95 26 91</t>
+        </is>
+      </c>
       <c r="R335" s="2" t="inlineStr">
         <is>
           <t>Kangourou Kids is a national childcare franchise cited among micro-crèche operators in 2025 market overviews. Its core is home-based childcare agencies, with a micro-crèche activity added. Details of 2025 network size and leadership were not confirmed in this session. Hook: franchise HQ as multiplier if micro-crèche activity is material.</t>
@@ -29891,7 +31871,11 @@
       </c>
       <c r="X335" s="2" t="inlineStr"/>
       <c r="Y335" s="2" t="inlineStr"/>
-      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kangouroukids.fr/nos-agences/toulouse; https://annuaire-entreprises.data.gouv.fr/etablissement/75243968700043</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -30177,8 +32161,16 @@
       </c>
       <c r="N339" s="2" t="inlineStr"/>
       <c r="O339" s="2" t="inlineStr"/>
-      <c r="P339" s="2" t="inlineStr"/>
-      <c r="Q339" s="2" t="inlineStr"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>0783549J@ac-versailles.fr</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>+33 (0)1 39 10 94 11</t>
+        </is>
+      </c>
       <c r="R339" s="2" t="inlineStr">
         <is>
           <t>Lycée International de Saint-Germain-en-Laye – maternelle: public international school with maternelle sections (multiple national sections). Included as a notable independent or international early-years provider in FR. The head-of-early-years name could NOT be confirmed in this session (web-search budget exhausted after 21 searches), so it is left null per the no-fabrication rule; confirm on the school's 'leadership' page or LinkedIn before outreach. These settings typically have discretionary budgets, English-speaking parent communities and heavy use of parent communication apps, making them fast-cycle prospects.</t>
@@ -30205,9 +32197,21 @@
           <t>fr_benelux.json</t>
         </is>
       </c>
-      <c r="X339" s="2" t="inlineStr"/>
-      <c r="Y339" s="2" t="inlineStr"/>
-      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>cecile.gagneur@ac-versailles.fr (Cécile Gagneur, Directrice, école primaire (incl. maternelle)); Laura.deleu1@ac-versailles.fr (Laura Deleu, Administration, école primaire)</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr">
+        <is>
+          <t>first.last@ac-versailles.fr</t>
+        </is>
+      </c>
+      <c r="Z339" s="2" t="inlineStr">
+        <is>
+          <t>https://lycee-international-stgermain.com/coordonnees-de-lecole/</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -30261,7 +32265,11 @@
       <c r="M340" s="2" t="inlineStr"/>
       <c r="N340" s="2" t="inlineStr"/>
       <c r="O340" s="2" t="inlineStr"/>
-      <c r="P340" s="2" t="inlineStr"/>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>contact@zazzen.fr; sap@zazzen.fr; creche@zazzen.fr</t>
+        </is>
+      </c>
       <c r="Q340" s="2" t="inlineStr"/>
       <c r="R340" s="2" t="inlineStr">
         <is>
@@ -30291,7 +32299,11 @@
       </c>
       <c r="X340" s="2" t="inlineStr"/>
       <c r="Y340" s="2" t="inlineStr"/>
-      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zazzen.fr/mentions-legales; http://famille.zazzen.fr/nous-contacter</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -30817,7 +32829,11 @@
       <c r="M347" s="2" t="inlineStr"/>
       <c r="N347" s="2" t="inlineStr"/>
       <c r="O347" s="2" t="inlineStr"/>
-      <c r="P347" s="2" t="inlineStr"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>march@chdn.co.uk</t>
+        </is>
+      </c>
       <c r="Q347" s="2" t="inlineStr"/>
       <c r="R347" s="2" t="inlineStr">
         <is>
@@ -30847,7 +32863,11 @@
       </c>
       <c r="X347" s="2" t="inlineStr"/>
       <c r="Y347" s="2" t="inlineStr"/>
-      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chdn.co.uk/contact-us/; https://www.chdn.co.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -30897,8 +32917,16 @@
       <c r="M348" s="2" t="inlineStr"/>
       <c r="N348" s="2" t="inlineStr"/>
       <c r="O348" s="2" t="inlineStr"/>
-      <c r="P348" s="2" t="inlineStr"/>
-      <c r="Q348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>elmscot@elmscot.co.uk; chester@elmscot.co.uk; woodlands@elmscot.co.uk</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>0161 980 0488</t>
+        </is>
+      </c>
       <c r="R348" s="2" t="inlineStr">
         <is>
           <t>Cheshire premium group (Elmscot Day Nurseries, Nursery of the Year winner previously). Verify.</t>
@@ -30927,7 +32955,11 @@
       </c>
       <c r="X348" s="2" t="inlineStr"/>
       <c r="Y348" s="2" t="inlineStr"/>
-      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.elmscot.co.uk/contact-us/; https://www.elmscot.co.uk/chester/; https://www.elmscot.co.uk/nurseries/woodlands/</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -31729,7 +33761,11 @@
       </c>
       <c r="N358" s="2" t="inlineStr"/>
       <c r="O358" s="2" t="inlineStr"/>
-      <c r="P358" s="2" t="inlineStr"/>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@oakleycapital.com; communications@oakleycapital.com; investorrelations@oakleycapital.com; oakley@greenbrookadvisory.com</t>
+        </is>
+      </c>
       <c r="Q358" s="2" t="inlineStr"/>
       <c r="R358" s="2" t="inlineStr">
         <is>
@@ -31759,7 +33795,11 @@
       </c>
       <c r="X358" s="2" t="inlineStr"/>
       <c r="Y358" s="2" t="inlineStr"/>
-      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oakleycapital.com/contact/; https://leadiq.com/c/oakley-capital/5a1d7c55240000240055dc3b/email-format</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -39095,11 +41135,7 @@
       </c>
       <c r="X454" s="2" t="inlineStr"/>
       <c r="Y454" s="2" t="inlineStr"/>
-      <c r="Z454" s="2" t="inlineStr">
-        <is>
-          <t>https://www.proff.no/selskap/akasia-s%C3%A6dalen-barnehage/bergen/pleie-og-omsorgstjenester/IGBAFW610K7/; https://akasiabarnehage.no/; https://www.bergen.kommune.no/api/rest/filer/V70665766</t>
-        </is>
-      </c>
+      <c r="Z454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -39607,11 +41643,7 @@
       </c>
       <c r="X460" s="2" t="inlineStr"/>
       <c r="Y460" s="2" t="inlineStr"/>
-      <c r="Z460" s="2" t="inlineStr">
-        <is>
-          <t>https://fus.no/prestagardskogen; https://fus.no/prestagardskogen/ansatte-i-barnehagen; https://proff.no/selskap/prestagardskogen-fus-barnehage-as/stord/pleie-og-omsorgstjenester/IF5EMC010K7</t>
-        </is>
-      </c>
+      <c r="Z460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -47063,11 +49095,7 @@
       </c>
       <c r="X553" s="2" t="inlineStr"/>
       <c r="Y553" s="2" t="inlineStr"/>
-      <c r="Z553" s="2" t="inlineStr">
-        <is>
-          <t>https://www.buscocolegio.com/canarias/santa-cruz-de-tenerife/granadilla-de-abona/escuela-educacion-infantil-sanipeques; https://koalaescuelas.es/sanipeques/</t>
-        </is>
-      </c>
+      <c r="Z553" s="2" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -53201,7 +55229,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>contact@dibberfamily.com</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>hans.sundby@dibber.com; h.sundby@dibber.com; hans@dibber.com</t>
@@ -53377,7 +55409,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>kontor@laringsverkstedet.no</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
           <t>adam.darnemyr@laringsverkstedet.no; a.darnemyr@laringsverkstedet.no; adam@laringsverkstedet.no</t>
@@ -53471,7 +55507,11 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>biuro@kids-co.pl; marketing.kids@kids-co.pl</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>karina.trafna@kids-co.pl; k.trafna@kids-co.pl; karina@kids-co.pl</t>
@@ -54625,8 +56665,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>kim.herbert@happydaysnurseries.com (Kim Herbert, Chief Executive Officer)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>first.last@domain</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -55156,7 +57204,11 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>contact@kindergarden.nl</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>nicole.krabbenborg@kindergarden.nl; n.krabbenborg@kindergarden.nl; nicole@kindergarden.nl</t>
@@ -55749,7 +57801,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>comms.team@brighthorizons.com</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
           <t>stephen.kramer@brighthorizons.com; s.kramer@brighthorizons.com; stephen@brighthorizons.com</t>
@@ -55766,8 +57822,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>iserpa@brighthorizons.com (Ilene Serpa, VP of Communications (2015 press release))</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>flast@brighthorizons.com</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -56068,7 +58132,11 @@
           <t>ES</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>info@kidsandus.es; lasrosas@kidsandus.es</t>
+        </is>
+      </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
           <t>ana.guisasola@kidsandus.es; a.guisasola@kidsandus.es; ana@kidsandus.es</t>
@@ -56113,7 +58181,11 @@
           <t>FR</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>media@antin-ip.com; shareholders@antin-ip.com; antinip@brunswickgroup.com</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>alain.rauscher@antin-ip.com; a.rauscher@antin-ip.com; alain@antin-ip.com</t>
@@ -56996,7 +59068,11 @@
           <t>NL</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>klantrelaties@kion.nl; communicatie@kion.nl; stage@kion.nl</t>
+        </is>
+      </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
           <t>jan.brink@kion.nl; j.brink@kion.nl; jan@kion.nl</t>
@@ -57172,7 +59248,11 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>akademia.reduta@gmail.com; akademiamarcholta@gmail.com; akademia.kurzei1@gmail.com</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
           <t>sabina.madej@akademiamalycheinsteinow.pl; s.madej@akademiamalycheinsteinow.pl; sabina@akademiamalycheinsteinow.pl</t>
@@ -57401,7 +59481,11 @@
           <t>PL</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>british@thebritishschool.pl</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
           <t>john.brett@nordangliaeducation.com; j.brett@nordangliaeducation.com; john@nordangliaeducation.com</t>
@@ -57644,11 +59728,7 @@
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr"/>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>first.last@domain</t>
-        </is>
-      </c>
+      <c r="K115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
